--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L210"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הילה רוח – זאת השנה שלי</v>
+        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%99%d7%9c%d7%94-%d7%a8%d7%95%d7%97-%d7%96%d7%90%d7%aa-%d7%94%d7%a9%d7%a0%d7%94-%d7%a9%d7%9c%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409582&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-15</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הילה רוח שרה שיר שנשמע כמו הבטחה לעצמה, לא הכרזה חגיגית אלא ניסיון להאמין.הבלדה המלודית-השקטה מושרת ברכות כמעט מלוחשת היא לא רק אסתטיקה: היא המנגנון הפסיכולוגי של הדוברת. זאת לא צעקה של ביטחון  זאת לחישה של אומץ. "אני יש לי</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הילה רוח – זאת השנה שלי</v>
+        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>בן ארצי ואהרון רזאל – תודה</v>
+        <v>נאור בן דוד - כמו בימים קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%95%d7%90%d7%94%d7%a8%d7%95%d7%9f-%d7%a8%d7%96%d7%90%d7%9c-%d7%aa%d7%95%d7%93%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409581&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-15</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>“תודה” הוא שיר הודיה  אבל לא נאיבי.. זו אינה שמחה פשוטה, אלא הודיה שעברה דרך כאב, ספק ושבר. הדואט בין שני קולות שמגיעים מעולמות מעט שונים  – חילוני־פואטי (בן ארצי) ואמוני מובהק (אהרן רזאל) —יוצר מרחב שמחבר בין רוחניות אישית</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -498,7 +498,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>בן ארצי ואהרון רזאל – תודה</v>
+        <v>נאור בן דוד - כמו בימים קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דניאל גרנט – מיס דייזי</v>
+        <v>ליאן אמסלם - יכולה לבד קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14</v>
+        <v>2026-02-15</v>
       </c>
       <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%92%d7%a8%d7%a0%d7%98-%d7%9e%d7%99%d7%a1-%d7%93%d7%99%d7%99%d7%96%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409580&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-15</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>זה לא ראפ על הצלחה – זה ראפ על הזמן שבין ההצלחות. השיר של דניאל גרנט עוסק באזור הכי פחות מדובר בקריירה: לא ההתחלה, לא הפריצה, אלא השנים האפורות באמצע, כשהכול כבר כמעט קרה… ואז נעצר. הבית הראשון מציג ביוגרפיה</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -536,7 +536,7 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דניאל גרנט – מיס דייזי</v>
+        <v>ליאן אמסלם - יכולה לבד קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רז פרסטן – ביג</v>
+        <v>הדר מעוז - גולה סאנגם קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-15</v>
       </c>
       <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%96-%d7%a4%d7%a8%d7%a1%d7%98%d7%9f-%d7%91%d7%99%d7%92/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409579&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-15</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>"ביג” של רז פרסטן הוא רוק מהיר, מחוספס וכמעט פאנקי-פוסט-פאנק.  הליבה הטקסטואלית נשמעת כהצהרת דור. הוא לא מדבר על הצלחה.  הוא מדבר על התנאים להיות בכלל נשמע. הלהקה מצהירה בדף המידע כי שואבת השראה מלהקת כ-Turnstile ומ –  של Fontaines</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -574,7 +574,7 @@
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>רז פרסטן – ביג</v>
+        <v>הדר מעוז - גולה סאנגם קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נועם קלינשטיין – אותו דבר</v>
+        <v>דניאל חן - התמונות שבאלבום קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-15</v>
       </c>
       <c r="C6" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%9d-%d7%a7%d7%9c%d7%99%d7%a0%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%90%d7%95%d7%aa%d7%95-%d7%93%d7%91%d7%a8/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409578&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-15</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>נועם קלינשטיין שרה שיר פופ קצבי אולד-סקול עם דרייב של נסיעה (“driving pop”) — כלומר שיר שנשען על גרוב רציף, מרכז הרמוני יציב וקולות ליווי נשיים שעוטפים ולא שוברים את הזרימה. זה לא שיר פרידה קלאסי אלא שיר אחרי הפרידה..</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -612,7 +612,7 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נועם קלינשטיין – אותו דבר</v>
+        <v>דניאל חן - התמונות שבאלבום קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>משה כורסיה – עומד מולך היום</v>
+        <v>דניאל בן משיח - ממעמקים קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-15</v>
       </c>
       <c r="C7" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%9b%d7%95%d7%a8%d7%a1%d7%99%d7%94-%d7%a2%d7%95%d7%9e%d7%93-%d7%9e%d7%95%d7%9c%d7%9a-%d7%94%d7%99%d7%95%d7%9d/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409577&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-15</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>זהו שיר תפילה במבנה של בלדה מודרנית. לא תפילה ליטורגית, אלא אישית, חשופה, כמעט יומיומית. השיר מתאר אדם שהתעייף מלהחזיק דימוי חזק כלפי חוץ,  ומבקש בפעם הראשונה לא להוכיח, אלא להשתייך. משה כורסיה מספר כי הרקע לשיר – התמודדות עם</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -650,7 +650,7 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>משה כורסיה – עומד מולך היום</v>
+        <v>דניאל בן משיח - ממעמקים קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>נתן כהן – ותגיד לי אתה</v>
+        <v>בן ישכרוב - מזל קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-15</v>
       </c>
       <c r="C8" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9f-%d7%9b%d7%94%d7%9f-%d7%95%d7%aa%d7%92%d7%99%d7%93-%d7%9c%d7%99-%d7%90%d7%aa%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409576&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-15</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>נתן כהן, שבלט ב"הנשמות הטהורות" ביכולת לכתוב ולהלחין שירים עם פשטות פיוטית ("אחכה לך", "אחרי שהסירות"), ממשיך כאן קו סגנוני מוכר. השיר מדבר על זמן של עייפות תרבותית.על עולם שבו הטבע מתייבש לאט, הילדים משחקים כאילו כלום, האוויר כבד, והמבוגר</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -688,7 +688,7 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>נתן כהן – ותגיד לי אתה</v>
+        <v>בן ישכרוב - מזל קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>נוגה פרידמן – עזרה</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-11</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%92%d7%94-%d7%a4%d7%a8%d7%99%d7%93%d7%9e%d7%9f-%d7%a2%d7%96%d7%a8%d7%94/</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-15</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>"עזרה" ששרה נוגה פרידמן הוא שיר שקשה לנתח אותו מבלי לזכור את נסיבות כתיבתו,  אבל כוחו האמיתי הוא בכך שהוא עומד גם בלי הביוגרפיה. האובדן האישי של בן זוגה, עידו רוזנטל ז"ל, נוכח בשיר, אך הוא לא מתואר. אין אזכור</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>5:31</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>נוגה פרידמן – עזרה</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אליה אבוקרט - אמא יקרה קאבר</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409575&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-15</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>2:49</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Mýa</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אליה אבוקרט - אמא יקרה קאבר</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אופק המלאך - אין מילים איתך קאבר</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409574&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-15</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>3:03</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Michael Bolton</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אופק המלאך - אין מילים איתך קאבר</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אופיר נגר - Aramam Cover</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409573&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-15</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>2:59</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אופיר נגר - Aramam Cover</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אבישי עוזיאל - אין לי אותך קאבר</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409572&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-15</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>2:41</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אבישי עוזיאל - אין לי אותך קאבר</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>דודו טסה – אי</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%93%d7%95-%d7%98%d7%a1%d7%94-%d7%90%d7%99/</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-15</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>מי מוציא היום אלבום של 18 שירים? התשובה: דודו טסה. הוא עזב את הכאוס המקומי, יצא לאי ביוון עם עלמה זוהר ויונתן דסקל, והנה התוצאה. שווה היה להתנתק. הנה מה שהאי הוליד. שווה מאוד להקשיב. האלבום נפתח ב"עמנואל" – לא</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>2:59</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>ENHYPEN</v>
       </c>
       <c r="I14" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>דודו טסה – אי</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>עברי לידר - אין לך מילה</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24444&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-15</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>19:24</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>3:59</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I15" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>עברי לידר - אין לך מילה</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>יובל בנאי - אודיסאוס של הרכבת התחתית</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24445&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-15</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>19:23</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>7:48</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I16" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>יובל בנאי - אודיסאוס של הרכבת התחתית</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>מתי כספי ז''ל הזמר, מענקי המוזיקה שלנו הלך הלילה לעולמו - יהי זכרו ברוך</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-02-14</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24443&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-15</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>07:49</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>3:10</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I17" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>מתי כספי ז''ל הזמר, מענקי המוזיקה שלנו הלך הלילה לעולמו - יהי זכרו ברוך</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>הפטריקים - הפרויקט של דודי לוי ואבטיפוס - להיטי הזהב</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-02-13</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24448&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-15</v>
@@ -1059,16 +1059,16 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>00:30</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>5:57</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I18" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>הפטריקים - הפרויקט של דודי לוי ואבטיפוס - להיטי הזהב</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-15</v>
@@ -1097,10 +1097,10 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>5:31</v>
+        <v>2:25</v>
       </c>
       <c r="H19" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-15</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:49</v>
+        <v>3:19</v>
       </c>
       <c r="H20" t="str">
-        <v>Mýa</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-15</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:03</v>
+        <v>3:38</v>
       </c>
       <c r="H21" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-15</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:59</v>
+        <v>4:05</v>
       </c>
       <c r="H22" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-15</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:41</v>
+        <v>5:46</v>
       </c>
       <c r="H23" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-15</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:59</v>
+        <v>3:25</v>
       </c>
       <c r="H24" t="str">
-        <v>ENHYPEN</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-15</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:59</v>
+        <v>5:11</v>
       </c>
       <c r="H25" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-15</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>7:48</v>
+        <v>2:55</v>
       </c>
       <c r="H26" t="str">
-        <v>The Doobie Brothers</v>
+        <v>The Warning</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-15</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:10</v>
+        <v>4:54</v>
       </c>
       <c r="H27" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Offspring</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-15</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>5:57</v>
+        <v>5:01</v>
       </c>
       <c r="H28" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-15</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:25</v>
+        <v>3:55</v>
       </c>
       <c r="H29" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>HAUSER</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>Jillian Jacquline - Another Lover (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-15</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:19</v>
+        <v>3:43</v>
       </c>
       <c r="H30" t="str">
-        <v>Michael Bolton</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-15</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:38</v>
+        <v>2:53</v>
       </c>
       <c r="H31" t="str">
-        <v>mgk</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-15</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>4:05</v>
+        <v>3:30</v>
       </c>
       <c r="H32" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-15</v>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>5:46</v>
+        <v>3:37</v>
       </c>
       <c r="H33" t="str">
-        <v>Jacob Collier</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-15</v>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:25</v>
+        <v>4:10</v>
       </c>
       <c r="H34" t="str">
-        <v>Victor Ray</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-15</v>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>5:11</v>
+        <v>3:06</v>
       </c>
       <c r="H35" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B36" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-15</v>
@@ -1746,10 +1746,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:55</v>
+        <v>3:17</v>
       </c>
       <c r="H36" t="str">
-        <v>The Warning</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B37" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-15</v>
@@ -1784,10 +1784,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:54</v>
+        <v>3:21</v>
       </c>
       <c r="H37" t="str">
-        <v>The Offspring</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B38" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-15</v>
@@ -1822,10 +1822,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>5:01</v>
+        <v>6:58</v>
       </c>
       <c r="H38" t="str">
-        <v>Caitlyn Smith</v>
+        <v>Eric Church</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B39" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-15</v>
@@ -1860,10 +1860,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:55</v>
+        <v>3:29</v>
       </c>
       <c r="H39" t="str">
-        <v>HAUSER</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-15</v>
@@ -1898,10 +1898,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:43</v>
+        <v>3:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-15</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:53</v>
+        <v>3:51</v>
       </c>
       <c r="H41" t="str">
-        <v>Ultra Records</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-15</v>
@@ -1974,10 +1974,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:30</v>
+        <v>3:10</v>
       </c>
       <c r="H42" t="str">
-        <v>Anja Kotar</v>
+        <v>elijah woods</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B43" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-15</v>
@@ -2012,10 +2012,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:37</v>
+        <v>3:26</v>
       </c>
       <c r="H43" t="str">
-        <v>Michael Bolton</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B44" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-15</v>
@@ -2050,10 +2050,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:10</v>
+        <v>2:51</v>
       </c>
       <c r="H44" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B45" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-15</v>
@@ -2088,10 +2088,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H45" t="str">
-        <v>Alan Walker</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-15</v>
@@ -2126,10 +2126,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:17</v>
+        <v>3:06</v>
       </c>
       <c r="H46" t="str">
-        <v>Bruno Mars</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-15</v>
@@ -2164,10 +2164,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:21</v>
+        <v>3:04</v>
       </c>
       <c r="H47" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B48" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-15</v>
@@ -2202,10 +2202,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>6:58</v>
+        <v>3:03</v>
       </c>
       <c r="H48" t="str">
-        <v>Eric Church</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-15</v>
@@ -2240,10 +2240,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:29</v>
+        <v>2:38</v>
       </c>
       <c r="H49" t="str">
-        <v>Meghan Trainor</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-15</v>
@@ -2278,10 +2278,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H50" t="str">
-        <v>Ally Salort</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-15</v>
@@ -2316,10 +2316,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:51</v>
+        <v>2:32</v>
       </c>
       <c r="H51" t="str">
-        <v>Will Swinton</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B52" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-15</v>
@@ -2354,10 +2354,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:10</v>
+        <v>3:32</v>
       </c>
       <c r="H52" t="str">
-        <v>elijah woods</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-15</v>
@@ -2392,10 +2392,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H53" t="str">
-        <v>Jackson Dean</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B54" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-15</v>
@@ -2430,10 +2430,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:51</v>
+        <v>3:38</v>
       </c>
       <c r="H54" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B55" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-15</v>
@@ -2471,7 +2471,7 @@
         <v>3:26</v>
       </c>
       <c r="H55" t="str">
-        <v>Neil Sedaka</v>
+        <v>Nickless</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-15</v>
@@ -2506,10 +2506,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:06</v>
+        <v>3:57</v>
       </c>
       <c r="H56" t="str">
-        <v>Sofia Camara</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-15</v>
@@ -2544,10 +2544,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:04</v>
+        <v>3:08</v>
       </c>
       <c r="H57" t="str">
-        <v>Russell Dickerson</v>
+        <v>elijah woods</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-15</v>
@@ -2582,10 +2582,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:03</v>
+        <v>3:53</v>
       </c>
       <c r="H58" t="str">
-        <v>Celine Dion</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-15</v>
@@ -2620,10 +2620,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:38</v>
+        <v>3:10</v>
       </c>
       <c r="H59" t="str">
-        <v>Bebe Rexha</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-15</v>
@@ -2658,7 +2658,7 @@
         <v>2 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:29</v>
+        <v>2:58</v>
       </c>
       <c r="H60" t="str">
         <v>Caroline Jones</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-15</v>
@@ -2696,10 +2696,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:32</v>
+        <v>2:44</v>
       </c>
       <c r="H61" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B62" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-15</v>
@@ -2734,10 +2734,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:32</v>
+        <v>3:25</v>
       </c>
       <c r="H62" t="str">
-        <v>Ingrid Andress</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-15</v>
@@ -2772,10 +2772,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:51</v>
+        <v>4:08</v>
       </c>
       <c r="H63" t="str">
-        <v>MusicByKnox</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B64" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-15</v>
@@ -2810,10 +2810,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:38</v>
+        <v>3:09</v>
       </c>
       <c r="H64" t="str">
-        <v>Ella Langley</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Nickless - As I Am</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-15</v>
@@ -2848,10 +2848,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:26</v>
+        <v>3:11</v>
       </c>
       <c r="H65" t="str">
-        <v>Nickless</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B66" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-15</v>
@@ -2886,10 +2886,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:57</v>
+        <v>3:02</v>
       </c>
       <c r="H66" t="str">
-        <v>Caroline Jones</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B67" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-15</v>
@@ -2924,10 +2924,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:08</v>
+        <v>4:20</v>
       </c>
       <c r="H67" t="str">
-        <v>elijah woods</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B68" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-15</v>
@@ -2962,10 +2962,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:53</v>
+        <v>4:09</v>
       </c>
       <c r="H68" t="str">
-        <v>August Ponthier</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-15</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:10</v>
+        <v>4:34</v>
       </c>
       <c r="H69" t="str">
-        <v>Charli xcx</v>
+        <v>We Three</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B70" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-15</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:58</v>
+        <v>3:29</v>
       </c>
       <c r="H70" t="str">
-        <v>Caroline Jones</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-15</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:44</v>
+        <v>2:51</v>
       </c>
       <c r="H71" t="str">
-        <v>Leah Kate</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-15</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:25</v>
+        <v>2:56</v>
       </c>
       <c r="H72" t="str">
-        <v>Troye Sivan</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-15</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:08</v>
+        <v>3:25</v>
       </c>
       <c r="H73" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>P!NK</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-15</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:09</v>
+        <v>2:33</v>
       </c>
       <c r="H74" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bazzi</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-15</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:11</v>
+        <v>4:18</v>
       </c>
       <c r="H75" t="str">
-        <v>The Happy Fits</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B76" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-15</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:02</v>
+        <v>2:08</v>
       </c>
       <c r="H76" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-15</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:20</v>
+        <v>3:56</v>
       </c>
       <c r="H77" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>bleachers</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-15</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:09</v>
+        <v>3:27</v>
       </c>
       <c r="H78" t="str">
-        <v>Quinn XCII</v>
+        <v>The Academic</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-15</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:34</v>
+        <v>2:39</v>
       </c>
       <c r="H79" t="str">
-        <v>We Three</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-15</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:29</v>
+        <v>3:54</v>
       </c>
       <c r="H80" t="str">
-        <v>A Thousand Horses</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-15</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:51</v>
+        <v>3:47</v>
       </c>
       <c r="H81" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B82" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-15</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:56</v>
+        <v>4:07</v>
       </c>
       <c r="H82" t="str">
-        <v>Constant Smiles</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-15</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:25</v>
+        <v>5:00</v>
       </c>
       <c r="H83" t="str">
-        <v>P!NK</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B84" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-15</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:33</v>
+        <v>3:27</v>
       </c>
       <c r="H84" t="str">
-        <v>Bazzi</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-15</v>
@@ -3608,10 +3608,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:18</v>
+        <v>3:25</v>
       </c>
       <c r="H85" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B86" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-15</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:08</v>
+        <v>10:57</v>
       </c>
       <c r="H86" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B87" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-15</v>
@@ -3684,10 +3684,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:56</v>
+        <v>4:14</v>
       </c>
       <c r="H87" t="str">
-        <v>bleachers</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-15</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:27</v>
+        <v>3:26</v>
       </c>
       <c r="H88" t="str">
-        <v>The Academic</v>
+        <v>mgk</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B89" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-15</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:39</v>
+        <v>5:59</v>
       </c>
       <c r="H89" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-15</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:54</v>
+        <v>2:46</v>
       </c>
       <c r="H90" t="str">
-        <v>Michael Bolton</v>
+        <v>Perrie</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-15</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:47</v>
+        <v>3:39</v>
       </c>
       <c r="H91" t="str">
-        <v>Caroline Jones</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B92" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-15</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:07</v>
+        <v>3:58</v>
       </c>
       <c r="H92" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-15</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>5:00</v>
+        <v>2:26</v>
       </c>
       <c r="H93" t="str">
-        <v>Michael Bolton</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B94" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-15</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:27</v>
+        <v>3:04</v>
       </c>
       <c r="H94" t="str">
-        <v>Little Big Town</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-15</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:25</v>
+        <v>6:00</v>
       </c>
       <c r="H95" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B96" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-15</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>10:57</v>
+        <v>4:20</v>
       </c>
       <c r="H96" t="str">
-        <v>JavaJazzFest</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B97" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-15</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:14</v>
+        <v>4:27</v>
       </c>
       <c r="H97" t="str">
-        <v>Robert Grace</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B98" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-15</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:26</v>
       </c>
       <c r="H98" t="str">
-        <v>mgk</v>
+        <v>Netflix</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B99" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-15</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>5:59</v>
+        <v>3:29</v>
       </c>
       <c r="H99" t="str">
-        <v>Victor Ray</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-15</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:46</v>
+        <v>2:59</v>
       </c>
       <c r="H100" t="str">
-        <v>Perrie</v>
+        <v>mgk</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B101" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-15</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:39</v>
+        <v>2:51</v>
       </c>
       <c r="H101" t="str">
-        <v>Michael Bolton</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B102" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-15</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:58</v>
+        <v>4:13</v>
       </c>
       <c r="H102" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B103" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-15</v>
@@ -4289,13 +4289,13 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G103" t="str">
-        <v>2:26</v>
+        <v>4:41</v>
       </c>
       <c r="H103" t="str">
-        <v>Mimi Webb</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B104" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-15</v>
@@ -4327,13 +4327,13 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:04</v>
+        <v>7:03</v>
       </c>
       <c r="H104" t="str">
-        <v>Olivia Dean</v>
+        <v>Take That</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,18 +4345,18 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B105" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-15</v>
@@ -4365,13 +4365,13 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G105" t="str">
-        <v>6:00</v>
+        <v>4:37</v>
       </c>
       <c r="H105" t="str">
-        <v>Taylor Swift</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4383,18 +4383,18 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B106" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-15</v>
@@ -4403,13 +4403,13 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G106" t="str">
-        <v>4:20</v>
+        <v>3:54</v>
       </c>
       <c r="H106" t="str">
-        <v>Michael Bolton</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4421,18 +4421,18 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B107" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-15</v>
@@ -4441,13 +4441,13 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G107" t="str">
-        <v>4:27</v>
+        <v>3:06</v>
       </c>
       <c r="H107" t="str">
-        <v>Mariah Carey</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4459,18 +4459,18 @@
         <v/>
       </c>
       <c r="L107" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B108" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-15</v>
@@ -4479,13 +4479,13 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G108" t="str">
-        <v>3:26</v>
+        <v>3:21</v>
       </c>
       <c r="H108" t="str">
-        <v>Netflix</v>
+        <v>George Birge</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4497,18 +4497,18 @@
         <v/>
       </c>
       <c r="L108" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>Always Everywhere</v>
       </c>
       <c r="B109" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-15</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>8 days ago</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="G109" t="str">
-        <v>3:29</v>
+        <v>3:03</v>
       </c>
       <c r="H109" t="str">
-        <v>Michael Bolton</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
       </c>
       <c r="L109" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>Always Everywhere - Charli xcx</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Be Her</v>
       </c>
       <c r="B110" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-15</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>9 days ago</v>
+        <v>Dandelion</v>
       </c>
       <c r="G110" t="str">
-        <v>2:59</v>
+        <v>3:37</v>
       </c>
       <c r="H110" t="str">
-        <v>mgk</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L110" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>other side.</v>
       </c>
       <c r="B111" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-15</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>9 days ago</v>
+        <v>Icon</v>
       </c>
       <c r="G111" t="str">
-        <v>2:51</v>
+        <v>3:15</v>
       </c>
       <c r="H111" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L111" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B112" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-15</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>9 days ago</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>4:13</v>
+        <v>3:22</v>
       </c>
       <c r="H112" t="str">
-        <v>Michael Bolton</v>
+        <v>John Summit</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L112" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B113" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-15</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>9 days ago</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G113" t="str">
-        <v>4:41</v>
+        <v>3:00</v>
       </c>
       <c r="H113" t="str">
-        <v>NICK JONAS</v>
+        <v>CORTIS</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L113" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B114" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-15</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>9 days ago</v>
+        <v>Trying Times</v>
       </c>
       <c r="G114" t="str">
-        <v>7:03</v>
+        <v>3:40</v>
       </c>
       <c r="H114" t="str">
-        <v>Take That</v>
+        <v>James Blake</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L114" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Let Me</v>
       </c>
       <c r="B115" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-15</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>9 days ago</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>4:37</v>
+        <v>4:51</v>
       </c>
       <c r="H115" t="str">
-        <v>Cliff Richard</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L115" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B116" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-15</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>9 days ago</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:54</v>
+        <v>2:43</v>
       </c>
       <c r="H116" t="str">
-        <v>Bryan Adams</v>
+        <v>Perrie</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L116" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B117" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-15</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>9 days ago</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G117" t="str">
-        <v>3:06</v>
+        <v>4:03</v>
       </c>
       <c r="H117" t="str">
-        <v>Anna Graves</v>
+        <v>MUNA</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L117" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B118" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-15</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>9 days ago</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:21</v>
+        <v>3:18</v>
       </c>
       <c r="H118" t="str">
-        <v>George Birge</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L118" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Always Everywhere</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-15</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Wuthering Heights</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:03</v>
+        <v>3:06</v>
       </c>
       <c r="H119" t="str">
-        <v>Charli xcx</v>
+        <v>Central Cee</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L119" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Be Her</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-15</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Dandelion</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:37</v>
+        <v>3:59</v>
       </c>
       <c r="H120" t="str">
-        <v>Ella Langley</v>
+        <v>Arcángel</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L120" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>other side.</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-15</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Icon</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:15</v>
+        <v>4:20</v>
       </c>
       <c r="H121" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Fred again..</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L121" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SHADOWS</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-15</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>SHADOWS - Single</v>
+        <v>Cerulean</v>
       </c>
       <c r="G122" t="str">
-        <v>3:22</v>
+        <v>3:52</v>
       </c>
       <c r="H122" t="str">
-        <v>John Summit</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L122" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>Be By You</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-15</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G123" t="str">
-        <v>3:00</v>
+        <v>3:17</v>
       </c>
       <c r="H123" t="str">
-        <v>CORTIS</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L123" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>you and forever</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-15</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Trying Times</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G124" t="str">
-        <v>3:40</v>
+        <v>3:54</v>
       </c>
       <c r="H124" t="str">
-        <v>James Blake</v>
+        <v>Bleachers</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L124" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Let Me</v>
+        <v>ROOMS</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-15</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Let Me - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:51</v>
+        <v>3:52</v>
       </c>
       <c r="H125" t="str">
-        <v>Victoria Monét</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L125" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Woman In Love</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-15</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Woman In Love - Single</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:43</v>
+        <v>3:16</v>
       </c>
       <c r="H126" t="str">
-        <v>Perrie</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L126" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Dancing On The Wall</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-15</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Dancing On The Wall</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G127" t="str">
-        <v>4:03</v>
+        <v>3:11</v>
       </c>
       <c r="H127" t="str">
-        <v>MUNA</v>
+        <v>Junior H</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L127" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-15</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:18</v>
+        <v>3:09</v>
       </c>
       <c r="H128" t="str">
-        <v>ATEEZ</v>
+        <v>Maluma</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L128" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-15</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G129" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H129" t="str">
-        <v>Central Cee</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L129" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Mírame Baby</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-15</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G130" t="str">
-        <v>3:59</v>
+        <v>3:21</v>
       </c>
       <c r="H130" t="str">
-        <v>Arcángel</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L130" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Thorns</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-15</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:20</v>
+        <v>3:10</v>
       </c>
       <c r="H131" t="str">
-        <v>Fred again..</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L131" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Two Hearts</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-15</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Cerulean</v>
+        <v>Honora</v>
       </c>
       <c r="G132" t="str">
-        <v>3:52</v>
+        <v>4:10</v>
       </c>
       <c r="H132" t="str">
-        <v>Danny L Harle</v>
+        <v>Flea</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L132" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Be By You</v>
+        <v>JUICY</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-15</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>The Way I Am</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:17</v>
+        <v>3:31</v>
       </c>
       <c r="H133" t="str">
-        <v>Luke Combs</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L133" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>you and forever</v>
+        <v>All They Type</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-15</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>everyone for ten minutes</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:54</v>
+        <v>2:52</v>
       </c>
       <c r="H134" t="str">
-        <v>Bleachers</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L134" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ROOMS</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-15</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>ROOMS - Single</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H135" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L135" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>City</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-15</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>My Lover</v>
       </c>
       <c r="G136" t="str">
         <v>3:16</v>
       </c>
       <c r="H136" t="str">
-        <v>Bruno Mars</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L136" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-15</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G137" t="str">
-        <v>3:11</v>
+        <v>2:25</v>
       </c>
       <c r="H137" t="str">
-        <v>Junior H</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L137" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Con el Corazón</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-15</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:09</v>
+        <v>2:50</v>
       </c>
       <c r="H138" t="str">
-        <v>Maluma</v>
+        <v>Knox</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L138" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Get In Girl</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-15</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Toy With Me</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G139" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="H139" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L139" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>London Foolishly</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-15</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:21</v>
+        <v>3:38</v>
       </c>
       <c r="H140" t="str">
-        <v>Nick Jonas</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L140" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Thorns</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-15</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Thorns - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:10</v>
+        <v>2:57</v>
       </c>
       <c r="H141" t="str">
-        <v>Jelly Roll</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L141" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Thinkin Bout You</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-15</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Honora</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>4:10</v>
+        <v>2:58</v>
       </c>
       <c r="H142" t="str">
-        <v>Flea</v>
+        <v>IVE</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L142" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>JUICY</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-15</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>JUICY - Single</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:31</v>
+        <v>3:15</v>
       </c>
       <c r="H143" t="str">
-        <v>Lenny Tavárez</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L143" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>All They Type</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-15</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>All They Type - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G144" t="str">
-        <v>2:52</v>
+        <v>5:21</v>
       </c>
       <c r="H144" t="str">
-        <v>Keke Palmer</v>
+        <v>Don Broco</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L144" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>More Than A Lover</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-15</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H145" t="str">
-        <v>Mary J. Blige</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L145" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>City</v>
+        <v>for your love</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-15</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>My Lover</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:16</v>
+        <v>3:05</v>
       </c>
       <c r="H146" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L146" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Eyes Closed</v>
+        <v>Somebody</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-15</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:25</v>
+        <v>3:23</v>
       </c>
       <c r="H147" t="str">
-        <v>Mimi Webb</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L147" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Go For Broke</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-15</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Go For Broke - Single</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:50</v>
+        <v>1:55</v>
       </c>
       <c r="H148" t="str">
-        <v>Knox</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L148" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>On and On</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-15</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G149" t="str">
-        <v>3:10</v>
+        <v>3:43</v>
       </c>
       <c r="H149" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L149" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Kentucky Too Long</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-15</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G150" t="str">
-        <v>3:38</v>
+        <v>2:44</v>
       </c>
       <c r="H150" t="str">
-        <v>Charley Crockett</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L150" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-15</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>2:57</v>
+        <v>2:46</v>
       </c>
       <c r="H151" t="str">
-        <v>Mon Rovîa</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L151" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>BANG BANG</v>
+        <v>Somebody</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-15</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G152" t="str">
-        <v>2:58</v>
+        <v>2:49</v>
       </c>
       <c r="H152" t="str">
-        <v>IVE</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L152" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-15</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:15</v>
+        <v>3:28</v>
       </c>
       <c r="H153" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L153" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Nightmare Tripping</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-15</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Nightmare Tripping</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>5:21</v>
+        <v>3:01</v>
       </c>
       <c r="H154" t="str">
-        <v>Don Broco</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L154" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-15</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G155" t="str">
-        <v>3:26</v>
+        <v>4:04</v>
       </c>
       <c r="H155" t="str">
-        <v>Knocked Loose</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L155" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>for your love</v>
+        <v>Beatback</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-15</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>for your love - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G156" t="str">
-        <v>3:05</v>
+        <v>2:19</v>
       </c>
       <c r="H156" t="str">
-        <v>Cruz Beckham</v>
+        <v>Fcukers</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L156" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Somebody</v>
+        <v>GANG</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-15</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Somebody - Single</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:23</v>
+        <v>3:44</v>
       </c>
       <c r="H157" t="str">
-        <v>Jamie Foxx</v>
+        <v>Tink</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L157" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>a love song for u</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-15</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>1:55</v>
+        <v>1:40</v>
       </c>
       <c r="H158" t="str">
-        <v>BKTHERULA</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L158" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>On and On</v>
+        <v>See Through</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-15</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Work of Heart</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G159" t="str">
-        <v>3:43</v>
+        <v>2:38</v>
       </c>
       <c r="H159" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L159" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Push My Luck</v>
+        <v>be the girl!</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-15</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G160" t="str">
-        <v>2:44</v>
+        <v>5:33</v>
       </c>
       <c r="H160" t="str">
-        <v>Cold War Kids</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L160" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Memphis Players</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-15</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:46</v>
+        <v>3:33</v>
       </c>
       <c r="H161" t="str">
-        <v>Anish Kumar</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L161" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Somebody</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-15</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:49</v>
+        <v>3:40</v>
       </c>
       <c r="H162" t="str">
-        <v>Good Neighbours</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L162" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>If I Didn't Know You</v>
+        <v>ARCADE</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-15</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:28</v>
+        <v>2:52</v>
       </c>
       <c r="H163" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Deb Never</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L163" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Seven Seas</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-15</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Seven Seas - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>3:01</v>
+        <v>2:16</v>
       </c>
       <c r="H164" t="str">
-        <v>Dirty Heads</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L164" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>1000 Ways</v>
+        <v>you special.</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-15</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>A Love For Strangers</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:04</v>
+        <v>2:08</v>
       </c>
       <c r="H165" t="str">
-        <v>Chet Faker</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L165" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Beatback</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-15</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Ö</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:19</v>
+        <v>3:38</v>
       </c>
       <c r="H166" t="str">
-        <v>Fcukers</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L166" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>GANG</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-15</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>GANG - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:44</v>
+        <v>3:31</v>
       </c>
       <c r="H167" t="str">
-        <v>Tink</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L167" t="str">
-        <v>GANG - Tink</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>a love song for u</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-15</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>a love song for u - EP</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>1:40</v>
+        <v>2:43</v>
       </c>
       <c r="H168" t="str">
-        <v>Eem Triplin</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L168" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>See Through</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-15</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G169" t="str">
-        <v>2:38</v>
+        <v>4:43</v>
       </c>
       <c r="H169" t="str">
-        <v>Story of the Year</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L169" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>be the girl!</v>
+        <v>To B Honest</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-15</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>the apple tree under the sea</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G170" t="str">
-        <v>5:33</v>
+        <v>4:30</v>
       </c>
       <c r="H170" t="str">
-        <v>hemlocke springs</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L170" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-15</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G171" t="str">
-        <v>3:33</v>
+        <v>2:41</v>
       </c>
       <c r="H171" t="str">
-        <v>Erin LeCount</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L171" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>Koneko</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-15</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:40</v>
+        <v>4:08</v>
       </c>
       <c r="H172" t="str">
-        <v>Kid Sistr</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L172" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>ARCADE</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-15</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>ARCADE - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:52</v>
+        <v>2:58</v>
       </c>
       <c r="H173" t="str">
-        <v>Deb Never</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L173" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Girls Just Wanna</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-15</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Girlhood - EP</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:16</v>
+        <v>3:13</v>
       </c>
       <c r="H174" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L174" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>you special.</v>
+        <v>Pop Off</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-15</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>you special. - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:08</v>
+        <v>3:16</v>
       </c>
       <c r="H175" t="str">
-        <v>YFN Lucci</v>
+        <v>GRiZ</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L175" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Bass Dhol</v>
+        <v>dreams</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-15</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:38</v>
+        <v>3:31</v>
       </c>
       <c r="H176" t="str">
-        <v>Ahadadream</v>
+        <v>Azzecca</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L176" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-15</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:31</v>
+        <v>2:55</v>
       </c>
       <c r="H177" t="str">
-        <v>Charles Kelley</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L177" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>If I See Her Again</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-15</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:43</v>
+        <v>2:52</v>
       </c>
       <c r="H178" t="str">
-        <v>Maddox Batson</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L178" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-15</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Under The Sun</v>
+        <v>Masquerade</v>
       </c>
       <c r="G179" t="str">
-        <v>4:43</v>
+        <v>2:58</v>
       </c>
       <c r="H179" t="str">
-        <v>Sun-El Musician</v>
+        <v>Cardinals</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L179" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>To B Honest</v>
+        <v>Steady</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-15</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>To Whom This May Concern</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:30</v>
+        <v>3:26</v>
       </c>
       <c r="H180" t="str">
-        <v>Jill Scott</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L180" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>lil xan goes to washington</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-15</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>the beltway is burning</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G181" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H181" t="str">
-        <v>Ekko Astral</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L181" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Koneko</v>
+        <v>Nada Más</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-15</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Kurage - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>4:08</v>
+        <v>2:19</v>
       </c>
       <c r="H182" t="str">
-        <v>Liana Flores</v>
+        <v>Tombochio</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L182" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Cupid's Call</v>
+        <v>Friends Again</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-15</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:58</v>
+        <v>3:38</v>
       </c>
       <c r="H183" t="str">
-        <v>Dizzy Fae</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L183" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Come Back 2 Me</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-15</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:13</v>
+        <v>3:22</v>
       </c>
       <c r="H184" t="str">
-        <v>Chloé Caillet</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L184" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Pop Off</v>
+        <v>desire.</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-15</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Pop Off - Single</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G185" t="str">
-        <v>3:16</v>
+        <v>3:15</v>
       </c>
       <c r="H185" t="str">
-        <v>GRiZ</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L185" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>dreams</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-15</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>dreams - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G186" t="str">
-        <v>3:31</v>
+        <v>3:12</v>
       </c>
       <c r="H186" t="str">
-        <v>Azzecca</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L186" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Love Hate Love</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-15</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:55</v>
+        <v>4:00</v>
       </c>
       <c r="H187" t="str">
-        <v>Owen Riegling</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L187" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Do It All Alone</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-15</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G188" t="str">
-        <v>2:52</v>
+        <v>2:46</v>
       </c>
       <c r="H188" t="str">
-        <v>Rend Collective</v>
+        <v>Anjimile</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L188" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>She Makes Me Real</v>
+        <v>Man's World</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-15</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Masquerade</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G189" t="str">
-        <v>2:58</v>
+        <v>2:42</v>
       </c>
       <c r="H189" t="str">
-        <v>Cardinals</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L189" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Steady</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-15</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H190" t="str">
-        <v>Bella Kay</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L190" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DIRTY TECH</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-15</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>PLAY ME</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G191" t="str">
-        <v>2:20</v>
+        <v>2:51</v>
       </c>
       <c r="H191" t="str">
-        <v>Kim Gordon</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L191" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Nada Más</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-15</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Nada Más - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:19</v>
+        <v>5:23</v>
       </c>
       <c r="H192" t="str">
-        <v>Tombochio</v>
+        <v>BUNT.</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L192" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Friends Again</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-15</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Friends Again - Single</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:38</v>
+        <v>3:07</v>
       </c>
       <c r="H193" t="str">
-        <v>Baby Rose</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L193" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>W.T.A.</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-15</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>W.T.A. - Single</v>
+        <v>The Elephant</v>
       </c>
       <c r="G194" t="str">
-        <v>3:22</v>
+        <v>3:28</v>
       </c>
       <c r="H194" t="str">
-        <v>Isaia Huron</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L194" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>desire.</v>
+        <v>Yes</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-15</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>November Scorpio</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G195" t="str">
-        <v>3:15</v>
+        <v>3:21</v>
       </c>
       <c r="H195" t="str">
-        <v>Tiana Major9</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L195" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-15</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:12</v>
+        <v>2:52</v>
       </c>
       <c r="H196" t="str">
-        <v>August Ponthier</v>
+        <v>WesGhost</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L196" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Killer Whale</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-15</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G197" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H197" t="str">
-        <v>Hayden Everett</v>
+        <v>Converge</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L197" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Waits for Me</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-15</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>You’re Free to Go</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G198" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H198" t="str">
-        <v>Anjimile</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L198" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Man's World</v>
+        <v>Angel Eyes</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-15</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Mud Blood Bone</v>
+        <v>God Forgives - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:42</v>
+        <v>2:14</v>
       </c>
       <c r="H199" t="str">
-        <v>Cat Clyde</v>
+        <v>Guilt Trip</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
       </c>
       <c r="L199" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Angel Eyes - Guilt Trip</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>In the Middle of It</v>
+        <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-15</v>
@@ -7975,410 +7975,30 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G200" t="str">
-        <v>3:13</v>
+        <v>3:17</v>
       </c>
       <c r="H200" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Melvins</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
       <c r="L200" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Truth Of Pursuit</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Fleeting - EP</v>
-      </c>
-      <c r="G201" t="str">
-        <v>2:51</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Sarah Kinsley</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>5:23</v>
-      </c>
-      <c r="H202" t="str">
-        <v>BUNT.</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
-      </c>
-      <c r="L202" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>I've Never Met Her</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>I've Never Met Her - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>3:07</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Ally Salort</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
-      </c>
-      <c r="L203" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>BACKWARDS, INTO U</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>The Elephant</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:28</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Ledbyher</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
-      </c>
-      <c r="L204" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Just A Few Folk</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:21</v>
-      </c>
-      <c r="H205" t="str">
-        <v>JP Cooper</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Yes - JP Cooper</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>CHOKEHOLD</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>CHOKEHOLD - Single</v>
-      </c>
-      <c r="G206" t="str">
-        <v>2:52</v>
-      </c>
-      <c r="H206" t="str">
-        <v>WesGhost</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
-      </c>
-      <c r="L206" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Bad Faith</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Love Is Not Enough</v>
-      </c>
-      <c r="G207" t="str">
-        <v>2:48</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Converge</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Bad Faith - Converge</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Gimme Some Moore</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Good God / Baad Man</v>
-      </c>
-      <c r="G208" t="str">
-        <v>4:00</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Corrosion of Conformity</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Angel Eyes</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>God Forgives - Single</v>
-      </c>
-      <c r="G209" t="str">
-        <v>2:14</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Guilt Trip</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
-      </c>
-      <c r="L209" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Tossing Coins Into The Fountain Of F**k</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G210" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
-      </c>
-      <c r="L210" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L210"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
+        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409582&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409588&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-15</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
+        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נאור בן דוד - כמו בימים קאבר</v>
+        <v>תאי חבאני - הגולה קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409581&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409587&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-15</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נאור בן דוד - כמו בימים קאבר</v>
+        <v>תאי חבאני - הגולה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאן אמסלם - יכולה לבד קאבר</v>
+        <v>שרון זריהן - רק איתך קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409580&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409586&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-15</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאן אמסלם - יכולה לבד קאבר</v>
+        <v>שרון זריהן - רק איתך קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>הדר מעוז - גולה סאנגם קאבר</v>
+        <v>שילת ויצמן - הנך יפה קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409579&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409585&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-15</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>הדר מעוז - גולה סאנגם קאבר</v>
+        <v>שילת ויצמן - הנך יפה קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>דניאל חן - התמונות שבאלבום קאבר</v>
+        <v>שי חזן - חי איך שבא לי קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409578&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409584&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-15</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>דניאל חן - התמונות שבאלבום קאבר</v>
+        <v>שי חזן - חי איך שבא לי קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דניאל בן משיח - ממעמקים קאבר</v>
+        <v>צוריאל - הפרח בגני קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409577&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409583&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-15</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דניאל בן משיח - ממעמקים קאבר</v>
+        <v>צוריאל - הפרח בגני קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>בן ישכרוב - מזל קאבר</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409576&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-15</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>5:31</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>בן ישכרוב - מזל קאבר</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-15</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>5:31</v>
+        <v>2:49</v>
       </c>
       <c r="H9" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Mýa</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-15</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:49</v>
+        <v>3:03</v>
       </c>
       <c r="H10" t="str">
-        <v>Mýa</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-15</v>
@@ -796,10 +796,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:03</v>
+        <v>2:59</v>
       </c>
       <c r="H11" t="str">
-        <v>Michael Bolton</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-15</v>
@@ -834,10 +834,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H12" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B13" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-15</v>
@@ -872,10 +872,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H13" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B14" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-15</v>
@@ -910,10 +910,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:59</v>
+        <v>3:59</v>
       </c>
       <c r="H14" t="str">
-        <v>ENHYPEN</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-15</v>
@@ -948,10 +948,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:59</v>
+        <v>7:48</v>
       </c>
       <c r="H15" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-15</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>7:48</v>
+        <v>3:10</v>
       </c>
       <c r="H16" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-15</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:10</v>
+        <v>5:57</v>
       </c>
       <c r="H17" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-15</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:57</v>
+        <v>2:25</v>
       </c>
       <c r="H18" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-15</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:25</v>
+        <v>3:19</v>
       </c>
       <c r="H19" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-15</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:19</v>
+        <v>3:38</v>
       </c>
       <c r="H20" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-15</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:38</v>
+        <v>4:05</v>
       </c>
       <c r="H21" t="str">
-        <v>mgk</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-15</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:05</v>
+        <v>5:46</v>
       </c>
       <c r="H22" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-15</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:46</v>
+        <v>3:25</v>
       </c>
       <c r="H23" t="str">
-        <v>Jacob Collier</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-15</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:25</v>
+        <v>5:11</v>
       </c>
       <c r="H24" t="str">
-        <v>Victor Ray</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-15</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>5:11</v>
+        <v>2:55</v>
       </c>
       <c r="H25" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>The Warning</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-15</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:55</v>
+        <v>4:54</v>
       </c>
       <c r="H26" t="str">
-        <v>The Warning</v>
+        <v>The Offspring</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-15</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:54</v>
+        <v>5:01</v>
       </c>
       <c r="H27" t="str">
-        <v>The Offspring</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-15</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>5:01</v>
+        <v>3:55</v>
       </c>
       <c r="H28" t="str">
-        <v>Caitlyn Smith</v>
+        <v>HAUSER</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Jillian Jacquline - Another Lover (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-15</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:55</v>
+        <v>3:43</v>
       </c>
       <c r="H29" t="str">
-        <v>HAUSER</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-15</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H30" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-15</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:53</v>
+        <v>3:30</v>
       </c>
       <c r="H31" t="str">
-        <v>Ultra Records</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-15</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:30</v>
+        <v>3:37</v>
       </c>
       <c r="H32" t="str">
-        <v>Anja Kotar</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-15</v>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:37</v>
+        <v>4:10</v>
       </c>
       <c r="H33" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-15</v>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:10</v>
+        <v>3:06</v>
       </c>
       <c r="H34" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-15</v>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H35" t="str">
-        <v>Alan Walker</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B36" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-15</v>
@@ -1746,10 +1746,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H36" t="str">
-        <v>Bruno Mars</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B37" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-15</v>
@@ -1784,10 +1784,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:21</v>
+        <v>6:58</v>
       </c>
       <c r="H37" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Eric Church</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B38" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-15</v>
@@ -1822,10 +1822,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>6:58</v>
+        <v>3:29</v>
       </c>
       <c r="H38" t="str">
-        <v>Eric Church</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-15</v>
@@ -1860,10 +1860,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:29</v>
+        <v>3:14</v>
       </c>
       <c r="H39" t="str">
-        <v>Meghan Trainor</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-15</v>
@@ -1898,10 +1898,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:14</v>
+        <v>3:51</v>
       </c>
       <c r="H40" t="str">
-        <v>Ally Salort</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-15</v>
@@ -1936,10 +1936,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:51</v>
+        <v>3:10</v>
       </c>
       <c r="H41" t="str">
-        <v>Will Swinton</v>
+        <v>elijah woods</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B42" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-15</v>
@@ -1974,10 +1974,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:10</v>
+        <v>3:26</v>
       </c>
       <c r="H42" t="str">
-        <v>elijah woods</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B43" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-15</v>
@@ -2012,10 +2012,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H43" t="str">
-        <v>Jackson Dean</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B44" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-15</v>
@@ -2050,10 +2050,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H44" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-15</v>
@@ -2088,10 +2088,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H45" t="str">
-        <v>Neil Sedaka</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-15</v>
@@ -2126,10 +2126,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:06</v>
+        <v>3:04</v>
       </c>
       <c r="H46" t="str">
-        <v>Sofia Camara</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B47" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-15</v>
@@ -2164,10 +2164,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H47" t="str">
-        <v>Russell Dickerson</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-15</v>
@@ -2202,10 +2202,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:03</v>
+        <v>2:38</v>
       </c>
       <c r="H48" t="str">
-        <v>Celine Dion</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-15</v>
@@ -2240,10 +2240,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:38</v>
+        <v>3:29</v>
       </c>
       <c r="H49" t="str">
-        <v>Bebe Rexha</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B50" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-15</v>
@@ -2278,10 +2278,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:29</v>
+        <v>2:32</v>
       </c>
       <c r="H50" t="str">
-        <v>Caroline Jones</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-15</v>
@@ -2316,10 +2316,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:32</v>
+        <v>3:32</v>
       </c>
       <c r="H51" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-15</v>
@@ -2354,10 +2354,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:32</v>
+        <v>2:51</v>
       </c>
       <c r="H52" t="str">
-        <v>Ingrid Andress</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B53" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-15</v>
@@ -2392,10 +2392,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:51</v>
+        <v>3:38</v>
       </c>
       <c r="H53" t="str">
-        <v>MusicByKnox</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B54" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-15</v>
@@ -2430,10 +2430,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H54" t="str">
-        <v>Ella Langley</v>
+        <v>Nickless</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-15</v>
@@ -2468,10 +2468,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:26</v>
+        <v>3:57</v>
       </c>
       <c r="H55" t="str">
-        <v>Nickless</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-15</v>
@@ -2506,10 +2506,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:57</v>
+        <v>3:08</v>
       </c>
       <c r="H56" t="str">
-        <v>Caroline Jones</v>
+        <v>elijah woods</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-15</v>
@@ -2544,10 +2544,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:08</v>
+        <v>3:53</v>
       </c>
       <c r="H57" t="str">
-        <v>elijah woods</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-15</v>
@@ -2582,10 +2582,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:53</v>
+        <v>3:10</v>
       </c>
       <c r="H58" t="str">
-        <v>August Ponthier</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-15</v>
@@ -2620,10 +2620,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:10</v>
+        <v>2:58</v>
       </c>
       <c r="H59" t="str">
-        <v>Charli xcx</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-15</v>
@@ -2658,10 +2658,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:58</v>
+        <v>2:44</v>
       </c>
       <c r="H60" t="str">
-        <v>Caroline Jones</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B61" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-15</v>
@@ -2696,10 +2696,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:44</v>
+        <v>3:25</v>
       </c>
       <c r="H61" t="str">
-        <v>Leah Kate</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-15</v>
@@ -2734,10 +2734,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:25</v>
+        <v>4:08</v>
       </c>
       <c r="H62" t="str">
-        <v>Troye Sivan</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B63" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-15</v>
@@ -2772,10 +2772,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:08</v>
+        <v>3:09</v>
       </c>
       <c r="H63" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-15</v>
@@ -2810,10 +2810,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H64" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B65" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-15</v>
@@ -2848,10 +2848,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:11</v>
+        <v>3:02</v>
       </c>
       <c r="H65" t="str">
-        <v>The Happy Fits</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B66" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-15</v>
@@ -2886,10 +2886,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:02</v>
+        <v>4:20</v>
       </c>
       <c r="H66" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-15</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:20</v>
+        <v>4:09</v>
       </c>
       <c r="H67" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-15</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:09</v>
+        <v>4:34</v>
       </c>
       <c r="H68" t="str">
-        <v>Quinn XCII</v>
+        <v>We Three</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B69" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-15</v>
@@ -3000,10 +3000,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:34</v>
+        <v>3:29</v>
       </c>
       <c r="H69" t="str">
-        <v>We Three</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-15</v>
@@ -3038,10 +3038,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:29</v>
+        <v>2:51</v>
       </c>
       <c r="H70" t="str">
-        <v>A Thousand Horses</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-15</v>
@@ -3076,10 +3076,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H71" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B72" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-15</v>
@@ -3114,10 +3114,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:56</v>
+        <v>3:25</v>
       </c>
       <c r="H72" t="str">
-        <v>Constant Smiles</v>
+        <v>P!NK</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B73" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-15</v>
@@ -3152,10 +3152,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:25</v>
+        <v>2:33</v>
       </c>
       <c r="H73" t="str">
-        <v>P!NK</v>
+        <v>Bazzi</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B74" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-15</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:33</v>
+        <v>4:18</v>
       </c>
       <c r="H74" t="str">
-        <v>Bazzi</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-15</v>
@@ -3228,7 +3228,7 @@
         <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:18</v>
+        <v>2:08</v>
       </c>
       <c r="H75" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-15</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:08</v>
+        <v>3:56</v>
       </c>
       <c r="H76" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>bleachers</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-15</v>
@@ -3304,10 +3304,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:56</v>
+        <v>3:27</v>
       </c>
       <c r="H77" t="str">
-        <v>bleachers</v>
+        <v>The Academic</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-15</v>
@@ -3342,10 +3342,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:27</v>
+        <v>2:39</v>
       </c>
       <c r="H78" t="str">
-        <v>The Academic</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-15</v>
@@ -3380,10 +3380,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:39</v>
+        <v>3:54</v>
       </c>
       <c r="H79" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B80" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-15</v>
@@ -3418,10 +3418,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:54</v>
+        <v>3:47</v>
       </c>
       <c r="H80" t="str">
-        <v>Michael Bolton</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B81" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-15</v>
@@ -3456,10 +3456,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:47</v>
+        <v>4:07</v>
       </c>
       <c r="H81" t="str">
-        <v>Caroline Jones</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-15</v>
@@ -3494,10 +3494,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:07</v>
+        <v>5:00</v>
       </c>
       <c r="H82" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B83" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-15</v>
@@ -3532,10 +3532,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>5:00</v>
+        <v>3:27</v>
       </c>
       <c r="H83" t="str">
-        <v>Michael Bolton</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B84" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-15</v>
@@ -3570,10 +3570,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:27</v>
+        <v>3:25</v>
       </c>
       <c r="H84" t="str">
-        <v>Little Big Town</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B85" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-15</v>
@@ -3608,10 +3608,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:25</v>
+        <v>10:57</v>
       </c>
       <c r="H85" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B86" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-15</v>
@@ -3646,10 +3646,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>10:57</v>
+        <v>4:14</v>
       </c>
       <c r="H86" t="str">
-        <v>JavaJazzFest</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-15</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:14</v>
+        <v>3:26</v>
       </c>
       <c r="H87" t="str">
-        <v>Robert Grace</v>
+        <v>mgk</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B88" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-15</v>
@@ -3722,10 +3722,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:26</v>
+        <v>5:59</v>
       </c>
       <c r="H88" t="str">
-        <v>mgk</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B89" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-15</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:59</v>
+        <v>2:46</v>
       </c>
       <c r="H89" t="str">
-        <v>Victor Ray</v>
+        <v>Perrie</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B90" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-15</v>
@@ -3798,10 +3798,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:46</v>
+        <v>3:39</v>
       </c>
       <c r="H90" t="str">
-        <v>Perrie</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-15</v>
@@ -3836,10 +3836,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:39</v>
+        <v>3:58</v>
       </c>
       <c r="H91" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-15</v>
@@ -3874,10 +3874,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:58</v>
+        <v>2:26</v>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B93" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-15</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:26</v>
+        <v>3:04</v>
       </c>
       <c r="H93" t="str">
-        <v>Mimi Webb</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-15</v>
@@ -3950,10 +3950,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:04</v>
+        <v>6:00</v>
       </c>
       <c r="H94" t="str">
-        <v>Olivia Dean</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-15</v>
@@ -3988,10 +3988,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>6:00</v>
+        <v>4:20</v>
       </c>
       <c r="H95" t="str">
-        <v>Taylor Swift</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B96" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-15</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:20</v>
+        <v>4:27</v>
       </c>
       <c r="H96" t="str">
-        <v>Michael Bolton</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B97" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-15</v>
@@ -4064,10 +4064,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:27</v>
+        <v>3:26</v>
       </c>
       <c r="H97" t="str">
-        <v>Mariah Carey</v>
+        <v>Netflix</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-15</v>
@@ -4102,10 +4102,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H98" t="str">
-        <v>Netflix</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-15</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:29</v>
+        <v>2:59</v>
       </c>
       <c r="H99" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B100" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-15</v>
@@ -4178,10 +4178,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:59</v>
+        <v>2:51</v>
       </c>
       <c r="H100" t="str">
-        <v>mgk</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B101" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-15</v>
@@ -4216,10 +4216,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:51</v>
+        <v>4:13</v>
       </c>
       <c r="H101" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B102" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-15</v>
@@ -4254,10 +4254,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>4:13</v>
+        <v>4:41</v>
       </c>
       <c r="H102" t="str">
-        <v>Michael Bolton</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B103" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-15</v>
@@ -4292,10 +4292,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G103" t="str">
-        <v>4:41</v>
+        <v>7:03</v>
       </c>
       <c r="H103" t="str">
-        <v>NICK JONAS</v>
+        <v>Take That</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B104" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-15</v>
@@ -4330,10 +4330,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G104" t="str">
-        <v>7:03</v>
+        <v>4:37</v>
       </c>
       <c r="H104" t="str">
-        <v>Take That</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,18 +4345,18 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B105" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-15</v>
@@ -4368,10 +4368,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G105" t="str">
-        <v>4:37</v>
+        <v>3:54</v>
       </c>
       <c r="H105" t="str">
-        <v>Cliff Richard</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4383,18 +4383,18 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B106" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-15</v>
@@ -4406,10 +4406,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:54</v>
+        <v>3:06</v>
       </c>
       <c r="H106" t="str">
-        <v>Bryan Adams</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4421,18 +4421,18 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B107" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-15</v>
@@ -4444,10 +4444,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H107" t="str">
-        <v>Anna Graves</v>
+        <v>George Birge</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4459,18 +4459,18 @@
         <v/>
       </c>
       <c r="L107" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Always Everywhere</v>
       </c>
       <c r="B108" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-15</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>9 days ago</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="G108" t="str">
-        <v>3:21</v>
+        <v>3:03</v>
       </c>
       <c r="H108" t="str">
-        <v>George Birge</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
       </c>
       <c r="L108" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Always Everywhere - Charli xcx</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Always Everywhere</v>
+        <v>Be Her</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-15</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Wuthering Heights</v>
+        <v>Dandelion</v>
       </c>
       <c r="G109" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H109" t="str">
-        <v>Charli xcx</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L109" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Be Her</v>
+        <v>other side.</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-15</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Dandelion</v>
+        <v>Icon</v>
       </c>
       <c r="G110" t="str">
-        <v>3:37</v>
+        <v>3:15</v>
       </c>
       <c r="H110" t="str">
-        <v>Ella Langley</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L110" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>other side.</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-15</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Icon</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H111" t="str">
-        <v>Brent Faiyaz</v>
+        <v>John Summit</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L111" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SHADOWS</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-15</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>SHADOWS - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G112" t="str">
-        <v>3:22</v>
+        <v>3:00</v>
       </c>
       <c r="H112" t="str">
-        <v>John Summit</v>
+        <v>CORTIS</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L112" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-15</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G113" t="str">
-        <v>3:00</v>
+        <v>3:40</v>
       </c>
       <c r="H113" t="str">
-        <v>CORTIS</v>
+        <v>James Blake</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L113" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Let Me</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-15</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Trying Times</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:40</v>
+        <v>4:51</v>
       </c>
       <c r="H114" t="str">
-        <v>James Blake</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L114" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Let Me</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-15</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Let Me - Single</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>4:51</v>
+        <v>2:43</v>
       </c>
       <c r="H115" t="str">
-        <v>Victoria Monét</v>
+        <v>Perrie</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L115" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Woman In Love</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-15</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G116" t="str">
-        <v>2:43</v>
+        <v>4:03</v>
       </c>
       <c r="H116" t="str">
-        <v>Perrie</v>
+        <v>MUNA</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L116" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-15</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>4:03</v>
+        <v>3:18</v>
       </c>
       <c r="H117" t="str">
-        <v>MUNA</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L117" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-15</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:18</v>
+        <v>3:06</v>
       </c>
       <c r="H118" t="str">
-        <v>ATEEZ</v>
+        <v>Central Cee</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L118" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-15</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:06</v>
+        <v>3:59</v>
       </c>
       <c r="H119" t="str">
-        <v>Central Cee</v>
+        <v>Arcángel</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L119" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Mírame Baby</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-15</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:59</v>
+        <v>4:20</v>
       </c>
       <c r="H120" t="str">
-        <v>Arcángel</v>
+        <v>Fred again..</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L120" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-15</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Cerulean</v>
       </c>
       <c r="G121" t="str">
-        <v>4:20</v>
+        <v>3:52</v>
       </c>
       <c r="H121" t="str">
-        <v>Fred again..</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L121" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Two Hearts</v>
+        <v>Be By You</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-15</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Cerulean</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G122" t="str">
-        <v>3:52</v>
+        <v>3:17</v>
       </c>
       <c r="H122" t="str">
-        <v>Danny L Harle</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L122" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Be By You</v>
+        <v>you and forever</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-15</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>The Way I Am</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G123" t="str">
-        <v>3:17</v>
+        <v>3:54</v>
       </c>
       <c r="H123" t="str">
-        <v>Luke Combs</v>
+        <v>Bleachers</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L123" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>you and forever</v>
+        <v>ROOMS</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-15</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>everyone for ten minutes</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:54</v>
+        <v>3:52</v>
       </c>
       <c r="H124" t="str">
-        <v>Bleachers</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L124" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ROOMS</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-15</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ROOMS - Single</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:52</v>
+        <v>3:16</v>
       </c>
       <c r="H125" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L125" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-15</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G126" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H126" t="str">
-        <v>Bruno Mars</v>
+        <v>Junior H</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L126" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-15</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:11</v>
+        <v>3:09</v>
       </c>
       <c r="H127" t="str">
-        <v>Junior H</v>
+        <v>Maluma</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L127" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Con el Corazón</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-15</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G128" t="str">
-        <v>3:09</v>
+        <v>3:26</v>
       </c>
       <c r="H128" t="str">
-        <v>Maluma</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L128" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Get In Girl</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-15</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Toy With Me</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:26</v>
+        <v>3:21</v>
       </c>
       <c r="H129" t="str">
-        <v>Meghan Trainor</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L129" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>London Foolishly</v>
+        <v>Thorns</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-15</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H130" t="str">
-        <v>Nick Jonas</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L130" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Thorns</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-15</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Thorns - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G131" t="str">
-        <v>3:10</v>
+        <v>4:10</v>
       </c>
       <c r="H131" t="str">
-        <v>Jelly Roll</v>
+        <v>Flea</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L131" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thinkin Bout You</v>
+        <v>JUICY</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-15</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Honora</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:10</v>
+        <v>3:31</v>
       </c>
       <c r="H132" t="str">
-        <v>Flea</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L132" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>JUICY</v>
+        <v>All They Type</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-15</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>JUICY - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:31</v>
+        <v>2:52</v>
       </c>
       <c r="H133" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L133" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>All They Type</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-15</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>All They Type - Single</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:52</v>
+        <v>4:05</v>
       </c>
       <c r="H134" t="str">
-        <v>Keke Palmer</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L134" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>More Than A Lover</v>
+        <v>City</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-15</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>My Lover</v>
       </c>
       <c r="G135" t="str">
-        <v>4:05</v>
+        <v>3:16</v>
       </c>
       <c r="H135" t="str">
-        <v>Mary J. Blige</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L135" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>City</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-15</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>My Lover</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G136" t="str">
-        <v>3:16</v>
+        <v>2:25</v>
       </c>
       <c r="H136" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L136" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Eyes Closed</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-15</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:25</v>
+        <v>2:50</v>
       </c>
       <c r="H137" t="str">
-        <v>Mimi Webb</v>
+        <v>Knox</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L137" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Go For Broke</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-15</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Go For Broke - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G138" t="str">
-        <v>2:50</v>
+        <v>3:10</v>
       </c>
       <c r="H138" t="str">
-        <v>Knox</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L138" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-15</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:10</v>
+        <v>3:38</v>
       </c>
       <c r="H139" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L139" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Kentucky Too Long</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-15</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:38</v>
+        <v>2:57</v>
       </c>
       <c r="H140" t="str">
-        <v>Charley Crockett</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L140" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-15</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:57</v>
+        <v>2:58</v>
       </c>
       <c r="H141" t="str">
-        <v>Mon Rovîa</v>
+        <v>IVE</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L141" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>BANG BANG</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-15</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>BANG BANG - Single</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:58</v>
+        <v>3:15</v>
       </c>
       <c r="H142" t="str">
-        <v>IVE</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L142" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-15</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G143" t="str">
-        <v>3:15</v>
+        <v>5:21</v>
       </c>
       <c r="H143" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>Don Broco</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L143" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Nightmare Tripping</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-15</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Nightmare Tripping</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>5:21</v>
+        <v>3:26</v>
       </c>
       <c r="H144" t="str">
-        <v>Don Broco</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L144" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>for your love</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-15</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:26</v>
+        <v>3:05</v>
       </c>
       <c r="H145" t="str">
-        <v>Knocked Loose</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L145" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>for your love</v>
+        <v>Somebody</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-15</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>for your love - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:05</v>
+        <v>3:23</v>
       </c>
       <c r="H146" t="str">
-        <v>Cruz Beckham</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L146" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Somebody</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-15</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Somebody - Single</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:23</v>
+        <v>1:55</v>
       </c>
       <c r="H147" t="str">
-        <v>Jamie Foxx</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L147" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>On and On</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-15</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G148" t="str">
-        <v>1:55</v>
+        <v>3:43</v>
       </c>
       <c r="H148" t="str">
-        <v>BKTHERULA</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L148" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>On and On</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-15</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Work of Heart</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>3:43</v>
+        <v>2:44</v>
       </c>
       <c r="H149" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L149" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Push My Luck</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-15</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G150" t="str">
-        <v>2:44</v>
+        <v>2:46</v>
       </c>
       <c r="H150" t="str">
-        <v>Cold War Kids</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L150" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Memphis Players</v>
+        <v>Somebody</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-15</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G151" t="str">
-        <v>2:46</v>
+        <v>2:49</v>
       </c>
       <c r="H151" t="str">
-        <v>Anish Kumar</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L151" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Somebody</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-15</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:49</v>
+        <v>3:28</v>
       </c>
       <c r="H152" t="str">
-        <v>Good Neighbours</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L152" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-15</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H153" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L153" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Seven Seas</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-15</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Seven Seas - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G154" t="str">
-        <v>3:01</v>
+        <v>4:04</v>
       </c>
       <c r="H154" t="str">
-        <v>Dirty Heads</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L154" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>1000 Ways</v>
+        <v>Beatback</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-15</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>A Love For Strangers</v>
+        <v>Ö</v>
       </c>
       <c r="G155" t="str">
-        <v>4:04</v>
+        <v>2:19</v>
       </c>
       <c r="H155" t="str">
-        <v>Chet Faker</v>
+        <v>Fcukers</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L155" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Beatback</v>
+        <v>GANG</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-15</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Ö</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:19</v>
+        <v>3:44</v>
       </c>
       <c r="H156" t="str">
-        <v>Fcukers</v>
+        <v>Tink</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L156" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>GANG</v>
+        <v>a love song for u</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-15</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>GANG - Single</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>3:44</v>
+        <v>1:40</v>
       </c>
       <c r="H157" t="str">
-        <v>Tink</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L157" t="str">
-        <v>GANG - Tink</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>a love song for u</v>
+        <v>See Through</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-15</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>a love song for u - EP</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G158" t="str">
-        <v>1:40</v>
+        <v>2:38</v>
       </c>
       <c r="H158" t="str">
-        <v>Eem Triplin</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L158" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>See Through</v>
+        <v>be the girl!</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-15</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G159" t="str">
-        <v>2:38</v>
+        <v>5:33</v>
       </c>
       <c r="H159" t="str">
-        <v>Story of the Year</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L159" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>be the girl!</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-15</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>the apple tree under the sea</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>5:33</v>
+        <v>3:33</v>
       </c>
       <c r="H160" t="str">
-        <v>hemlocke springs</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L160" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-15</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:33</v>
+        <v>3:40</v>
       </c>
       <c r="H161" t="str">
-        <v>Erin LeCount</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L161" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>ARCADE</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-15</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:40</v>
+        <v>2:52</v>
       </c>
       <c r="H162" t="str">
-        <v>Kid Sistr</v>
+        <v>Deb Never</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L162" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>ARCADE</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-15</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>ARCADE - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>2:52</v>
+        <v>2:16</v>
       </c>
       <c r="H163" t="str">
-        <v>Deb Never</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L163" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Girls Just Wanna</v>
+        <v>you special.</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-15</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Girlhood - EP</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:16</v>
+        <v>2:08</v>
       </c>
       <c r="H164" t="str">
-        <v>Morgan St. Jean</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L164" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>you special.</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-15</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>you special. - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:08</v>
+        <v>3:38</v>
       </c>
       <c r="H165" t="str">
-        <v>YFN Lucci</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L165" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Bass Dhol</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-15</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:38</v>
+        <v>3:31</v>
       </c>
       <c r="H166" t="str">
-        <v>Ahadadream</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L166" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-15</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:31</v>
+        <v>2:43</v>
       </c>
       <c r="H167" t="str">
-        <v>Charles Kelley</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L167" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>If I See Her Again</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-15</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G168" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H168" t="str">
-        <v>Maddox Batson</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L168" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>To B Honest</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-15</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Under The Sun</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G169" t="str">
-        <v>4:43</v>
+        <v>4:30</v>
       </c>
       <c r="H169" t="str">
-        <v>Sun-El Musician</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L169" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>To B Honest</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-15</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>To Whom This May Concern</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G170" t="str">
-        <v>4:30</v>
+        <v>2:41</v>
       </c>
       <c r="H170" t="str">
-        <v>Jill Scott</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L170" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>lil xan goes to washington</v>
+        <v>Koneko</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-15</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>the beltway is burning</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:41</v>
+        <v>4:08</v>
       </c>
       <c r="H171" t="str">
-        <v>Ekko Astral</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L171" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Koneko</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-15</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Kurage - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:08</v>
+        <v>2:58</v>
       </c>
       <c r="H172" t="str">
-        <v>Liana Flores</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L172" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Cupid's Call</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-15</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:58</v>
+        <v>3:13</v>
       </c>
       <c r="H173" t="str">
-        <v>Dizzy Fae</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L173" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Pop Off</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-15</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:13</v>
+        <v>3:16</v>
       </c>
       <c r="H174" t="str">
-        <v>Chloé Caillet</v>
+        <v>GRiZ</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L174" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Pop Off</v>
+        <v>dreams</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-15</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Pop Off - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:16</v>
+        <v>3:31</v>
       </c>
       <c r="H175" t="str">
-        <v>GRiZ</v>
+        <v>Azzecca</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L175" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>dreams</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-15</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>dreams - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:31</v>
+        <v>2:55</v>
       </c>
       <c r="H176" t="str">
-        <v>Azzecca</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L176" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Love Hate Love</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-15</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:55</v>
+        <v>2:52</v>
       </c>
       <c r="H177" t="str">
-        <v>Owen Riegling</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L177" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Do It All Alone</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-15</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G178" t="str">
-        <v>2:52</v>
+        <v>2:58</v>
       </c>
       <c r="H178" t="str">
-        <v>Rend Collective</v>
+        <v>Cardinals</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L178" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>She Makes Me Real</v>
+        <v>Steady</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-15</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Masquerade</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:58</v>
+        <v>3:26</v>
       </c>
       <c r="H179" t="str">
-        <v>Cardinals</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L179" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Steady</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-15</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G180" t="str">
-        <v>3:26</v>
+        <v>2:20</v>
       </c>
       <c r="H180" t="str">
-        <v>Bella Kay</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L180" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>DIRTY TECH</v>
+        <v>Nada Más</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-15</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>PLAY ME</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:20</v>
+        <v>2:19</v>
       </c>
       <c r="H181" t="str">
-        <v>Kim Gordon</v>
+        <v>Tombochio</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L181" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Nada Más</v>
+        <v>Friends Again</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-15</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Nada Más - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:19</v>
+        <v>3:38</v>
       </c>
       <c r="H182" t="str">
-        <v>Tombochio</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L182" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Friends Again</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-15</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Friends Again - Single</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:38</v>
+        <v>3:22</v>
       </c>
       <c r="H183" t="str">
-        <v>Baby Rose</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L183" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>W.T.A.</v>
+        <v>desire.</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-15</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>W.T.A. - Single</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G184" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H184" t="str">
-        <v>Isaia Huron</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L184" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>desire.</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-15</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>November Scorpio</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G185" t="str">
-        <v>3:15</v>
+        <v>3:12</v>
       </c>
       <c r="H185" t="str">
-        <v>Tiana Major9</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L185" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-15</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:12</v>
+        <v>4:00</v>
       </c>
       <c r="H186" t="str">
-        <v>August Ponthier</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L186" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Killer Whale</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-15</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Killer Whale - Single</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G187" t="str">
-        <v>4:00</v>
+        <v>2:46</v>
       </c>
       <c r="H187" t="str">
-        <v>Hayden Everett</v>
+        <v>Anjimile</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L187" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Waits for Me</v>
+        <v>Man's World</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-15</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>You’re Free to Go</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G188" t="str">
-        <v>2:46</v>
+        <v>2:42</v>
       </c>
       <c r="H188" t="str">
-        <v>Anjimile</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L188" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Man's World</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-15</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Mud Blood Bone</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:42</v>
+        <v>3:13</v>
       </c>
       <c r="H189" t="str">
-        <v>Cat Clyde</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L189" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>In the Middle of It</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-15</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G190" t="str">
-        <v>3:13</v>
+        <v>2:51</v>
       </c>
       <c r="H190" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L190" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-15</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Fleeting - EP</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:51</v>
+        <v>5:23</v>
       </c>
       <c r="H191" t="str">
-        <v>Sarah Kinsley</v>
+        <v>BUNT.</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L191" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-15</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>5:23</v>
+        <v>3:07</v>
       </c>
       <c r="H192" t="str">
-        <v>BUNT.</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L192" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>I've Never Met Her</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-15</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>The Elephant</v>
       </c>
       <c r="G193" t="str">
-        <v>3:07</v>
+        <v>3:28</v>
       </c>
       <c r="H193" t="str">
-        <v>Ally Salort</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L193" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>Yes</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-15</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>The Elephant</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G194" t="str">
-        <v>3:28</v>
+        <v>3:21</v>
       </c>
       <c r="H194" t="str">
-        <v>Ledbyher</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L194" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Yes</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-15</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Just A Few Folk</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:21</v>
+        <v>2:52</v>
       </c>
       <c r="H195" t="str">
-        <v>JP Cooper</v>
+        <v>WesGhost</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L195" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-15</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G196" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H196" t="str">
-        <v>WesGhost</v>
+        <v>Converge</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L196" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Bad Faith</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-15</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Love Is Not Enough</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G197" t="str">
-        <v>2:48</v>
+        <v>4:00</v>
       </c>
       <c r="H197" t="str">
-        <v>Converge</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L197" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Angel Eyes</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-15</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Good God / Baad Man</v>
+        <v>God Forgives - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:00</v>
+        <v>2:14</v>
       </c>
       <c r="H198" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Guilt Trip</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
       </c>
       <c r="L198" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Angel Eyes - Guilt Trip</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Angel Eyes</v>
+        <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-15</v>
@@ -7937,68 +7937,30 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>God Forgives - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G199" t="str">
-        <v>2:14</v>
+        <v>3:17</v>
       </c>
       <c r="H199" t="str">
-        <v>Guilt Trip</v>
+        <v>Melvins</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
       <c r="L199" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Tossing Coins Into The Fountain Of F**k</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G200" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
-      </c>
-      <c r="L200" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,31 +436,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409588&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>5:31</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,36 +469,36 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תאי חבאני - הגולה קאבר</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409587&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>2:49</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Mýa</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,36 +507,36 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>תאי חבאני - הגולה קאבר</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שרון זריהן - רק איתך קאבר</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409586&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>3:03</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Michael Bolton</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שרון זריהן - רק איתך קאבר</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שילת ויצמן - הנך יפה קאבר</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409585&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>2:59</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,36 +583,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שילת ויצמן - הנך יפה קאבר</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שי חזן - חי איך שבא לי קאבר</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409584&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>2:41</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,36 +621,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>שי חזן - חי איך שבא לי קאבר</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>צוריאל - הפרח בגני קאבר</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-15</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409583&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>2:59</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>ENHYPEN</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>צוריאל - הפרח בגני קאבר</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -682,7 +682,7 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>5:31</v>
+        <v>3:59</v>
       </c>
       <c r="H8" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:49</v>
+        <v>7:48</v>
       </c>
       <c r="H9" t="str">
-        <v>Mýa</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:03</v>
+        <v>3:10</v>
       </c>
       <c r="H10" t="str">
-        <v>Michael Bolton</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:59</v>
+        <v>5:57</v>
       </c>
       <c r="H11" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:41</v>
+        <v>2:25</v>
       </c>
       <c r="H12" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:59</v>
+        <v>3:19</v>
       </c>
       <c r="H13" t="str">
-        <v>ENHYPEN</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:59</v>
+        <v>3:38</v>
       </c>
       <c r="H14" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>7:48</v>
+        <v>4:05</v>
       </c>
       <c r="H15" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:10</v>
+        <v>5:46</v>
       </c>
       <c r="H16" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>5:57</v>
+        <v>3:25</v>
       </c>
       <c r="H17" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:25</v>
+        <v>5:11</v>
       </c>
       <c r="H18" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:19</v>
+        <v>2:55</v>
       </c>
       <c r="H19" t="str">
-        <v>Michael Bolton</v>
+        <v>The Warning</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:38</v>
+        <v>4:54</v>
       </c>
       <c r="H20" t="str">
-        <v>mgk</v>
+        <v>The Offspring</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:05</v>
+        <v>5:01</v>
       </c>
       <c r="H21" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:46</v>
+        <v>3:55</v>
       </c>
       <c r="H22" t="str">
-        <v>Jacob Collier</v>
+        <v>HAUSER</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Jillian Jacquline - Another Lover (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:25</v>
+        <v>3:43</v>
       </c>
       <c r="H23" t="str">
-        <v>Victor Ray</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>5:11</v>
+        <v>2:53</v>
       </c>
       <c r="H24" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:55</v>
+        <v>3:30</v>
       </c>
       <c r="H25" t="str">
-        <v>The Warning</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:54</v>
+        <v>3:37</v>
       </c>
       <c r="H26" t="str">
-        <v>The Offspring</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>5:01</v>
+        <v>4:10</v>
       </c>
       <c r="H27" t="str">
-        <v>Caitlyn Smith</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:55</v>
+        <v>3:06</v>
       </c>
       <c r="H28" t="str">
-        <v>HAUSER</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:43</v>
+        <v>3:17</v>
       </c>
       <c r="H29" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:53</v>
+        <v>3:21</v>
       </c>
       <c r="H30" t="str">
-        <v>Ultra Records</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:30</v>
+        <v>6:58</v>
       </c>
       <c r="H31" t="str">
-        <v>Anja Kotar</v>
+        <v>Eric Church</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,21 +1571,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:37</v>
+        <v>3:29</v>
       </c>
       <c r="H32" t="str">
-        <v>Michael Bolton</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,21 +1609,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:10</v>
+        <v>3:14</v>
       </c>
       <c r="H33" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,21 +1647,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:06</v>
+        <v>3:51</v>
       </c>
       <c r="H34" t="str">
-        <v>Alan Walker</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,21 +1685,21 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:17</v>
+        <v>3:10</v>
       </c>
       <c r="H35" t="str">
-        <v>Bruno Mars</v>
+        <v>elijah woods</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,21 +1723,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B36" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1746,10 +1746,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H36" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,21 +1761,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B37" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1784,10 +1784,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>6:58</v>
+        <v>2:51</v>
       </c>
       <c r="H37" t="str">
-        <v>Eric Church</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,21 +1799,21 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B38" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1822,10 +1822,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H38" t="str">
-        <v>Meghan Trainor</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,21 +1837,21 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1860,10 +1860,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:14</v>
+        <v>3:06</v>
       </c>
       <c r="H39" t="str">
-        <v>Ally Salort</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,21 +1875,21 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1898,10 +1898,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:51</v>
+        <v>3:04</v>
       </c>
       <c r="H40" t="str">
-        <v>Will Swinton</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,21 +1913,21 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B41" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1936,10 +1936,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:10</v>
+        <v>3:03</v>
       </c>
       <c r="H41" t="str">
-        <v>elijah woods</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,21 +1951,21 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1974,10 +1974,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:26</v>
+        <v>2:38</v>
       </c>
       <c r="H42" t="str">
-        <v>Jackson Dean</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,21 +1989,21 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2012,10 +2012,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:51</v>
+        <v>3:29</v>
       </c>
       <c r="H43" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B44" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2050,10 +2050,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:26</v>
+        <v>2:32</v>
       </c>
       <c r="H44" t="str">
-        <v>Neil Sedaka</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,21 +2065,21 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2088,10 +2088,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:06</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Sofia Camara</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,21 +2103,21 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2126,10 +2126,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:04</v>
+        <v>2:51</v>
       </c>
       <c r="H46" t="str">
-        <v>Russell Dickerson</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2164,10 +2164,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:03</v>
+        <v>3:38</v>
       </c>
       <c r="H47" t="str">
-        <v>Celine Dion</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,21 +2179,21 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B48" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2202,10 +2202,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:38</v>
+        <v>3:26</v>
       </c>
       <c r="H48" t="str">
-        <v>Bebe Rexha</v>
+        <v>Nickless</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,21 +2217,21 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2240,7 +2240,7 @@
         <v>2 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:29</v>
+        <v>3:57</v>
       </c>
       <c r="H49" t="str">
         <v>Caroline Jones</v>
@@ -2255,21 +2255,21 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2278,10 +2278,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:32</v>
+        <v>3:08</v>
       </c>
       <c r="H50" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>elijah woods</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,21 +2293,21 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2316,10 +2316,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:32</v>
+        <v>3:53</v>
       </c>
       <c r="H51" t="str">
-        <v>Ingrid Andress</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,21 +2331,21 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2354,10 +2354,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:51</v>
+        <v>3:10</v>
       </c>
       <c r="H52" t="str">
-        <v>MusicByKnox</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,21 +2369,21 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2392,10 +2392,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H53" t="str">
-        <v>Ella Langley</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,21 +2407,21 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2430,10 +2430,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H54" t="str">
-        <v>Nickless</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2468,10 +2468,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:57</v>
+        <v>3:25</v>
       </c>
       <c r="H55" t="str">
-        <v>Caroline Jones</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2506,10 +2506,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:08</v>
+        <v>4:08</v>
       </c>
       <c r="H56" t="str">
-        <v>elijah woods</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B57" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2544,10 +2544,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:53</v>
+        <v>3:09</v>
       </c>
       <c r="H57" t="str">
-        <v>August Ponthier</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:10</v>
+        <v>3:11</v>
       </c>
       <c r="H58" t="str">
-        <v>Charli xcx</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B59" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:58</v>
+        <v>3:02</v>
       </c>
       <c r="H59" t="str">
-        <v>Caroline Jones</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B60" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:44</v>
+        <v>4:20</v>
       </c>
       <c r="H60" t="str">
-        <v>Leah Kate</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H61" t="str">
-        <v>Troye Sivan</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:08</v>
+        <v>4:34</v>
       </c>
       <c r="H62" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>We Three</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B63" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:09</v>
+        <v>3:29</v>
       </c>
       <c r="H63" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:11</v>
+        <v>2:51</v>
       </c>
       <c r="H64" t="str">
-        <v>The Happy Fits</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:02</v>
+        <v>2:56</v>
       </c>
       <c r="H65" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:20</v>
+        <v>3:25</v>
       </c>
       <c r="H66" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>P!NK</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B67" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2924,10 +2924,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:09</v>
+        <v>2:33</v>
       </c>
       <c r="H67" t="str">
-        <v>Quinn XCII</v>
+        <v>Bazzi</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B68" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:34</v>
+        <v>4:18</v>
       </c>
       <c r="H68" t="str">
-        <v>We Three</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B69" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:29</v>
+        <v>2:08</v>
       </c>
       <c r="H69" t="str">
-        <v>A Thousand Horses</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:51</v>
+        <v>3:56</v>
       </c>
       <c r="H70" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>bleachers</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:56</v>
+        <v>3:27</v>
       </c>
       <c r="H71" t="str">
-        <v>Constant Smiles</v>
+        <v>The Academic</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:25</v>
+        <v>2:39</v>
       </c>
       <c r="H72" t="str">
-        <v>P!NK</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B73" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:33</v>
+        <v>3:54</v>
       </c>
       <c r="H73" t="str">
-        <v>Bazzi</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,21 +3167,21 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B74" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3190,10 +3190,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:18</v>
+        <v>3:47</v>
       </c>
       <c r="H74" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B75" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3228,10 +3228,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:08</v>
+        <v>4:07</v>
       </c>
       <c r="H75" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3266,10 +3266,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:56</v>
+        <v>5:00</v>
       </c>
       <c r="H76" t="str">
-        <v>bleachers</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B77" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3307,7 +3307,7 @@
         <v>3:27</v>
       </c>
       <c r="H77" t="str">
-        <v>The Academic</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:39</v>
+        <v>3:25</v>
       </c>
       <c r="H78" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,21 +3357,21 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B79" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3380,10 +3380,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:54</v>
+        <v>10:57</v>
       </c>
       <c r="H79" t="str">
-        <v>Michael Bolton</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B80" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:47</v>
+        <v>4:14</v>
       </c>
       <c r="H80" t="str">
-        <v>Caroline Jones</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:07</v>
+        <v>3:26</v>
       </c>
       <c r="H81" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>mgk</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B82" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:00</v>
+        <v>5:59</v>
       </c>
       <c r="H82" t="str">
-        <v>Michael Bolton</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:27</v>
+        <v>2:46</v>
       </c>
       <c r="H83" t="str">
-        <v>Little Big Town</v>
+        <v>Perrie</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:25</v>
+        <v>3:39</v>
       </c>
       <c r="H84" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>10:57</v>
+        <v>3:58</v>
       </c>
       <c r="H85" t="str">
-        <v>JavaJazzFest</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:14</v>
+        <v>2:26</v>
       </c>
       <c r="H86" t="str">
-        <v>Robert Grace</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B87" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H87" t="str">
-        <v>mgk</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>5:59</v>
+        <v>6:00</v>
       </c>
       <c r="H88" t="str">
-        <v>Victor Ray</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:46</v>
+        <v>4:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Perrie</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B90" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:39</v>
+        <v>4:27</v>
       </c>
       <c r="H90" t="str">
-        <v>Michael Bolton</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B91" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:58</v>
+        <v>3:26</v>
       </c>
       <c r="H91" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Netflix</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:26</v>
+        <v>3:29</v>
       </c>
       <c r="H92" t="str">
-        <v>Mimi Webb</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:04</v>
+        <v>2:59</v>
       </c>
       <c r="H93" t="str">
-        <v>Olivia Dean</v>
+        <v>mgk</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B94" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>6:00</v>
+        <v>2:51</v>
       </c>
       <c r="H94" t="str">
-        <v>Taylor Swift</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,30 +3965,30 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:20</v>
+        <v>4:13</v>
       </c>
       <c r="H95" t="str">
         <v>Michael Bolton</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B96" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:27</v>
+        <v>4:41</v>
       </c>
       <c r="H96" t="str">
-        <v>Mariah Carey</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:26</v>
+        <v>7:03</v>
       </c>
       <c r="H97" t="str">
-        <v>Netflix</v>
+        <v>Take That</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B98" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:29</v>
+        <v>4:37</v>
       </c>
       <c r="H98" t="str">
-        <v>Michael Bolton</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,21 +4117,21 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B99" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4140,10 +4140,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:59</v>
+        <v>3:54</v>
       </c>
       <c r="H99" t="str">
-        <v>mgk</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,21 +4155,21 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B100" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4178,10 +4178,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:51</v>
+        <v>3:06</v>
       </c>
       <c r="H100" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,21 +4193,21 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B101" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4216,10 +4216,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:13</v>
+        <v>3:21</v>
       </c>
       <c r="H101" t="str">
-        <v>Michael Bolton</v>
+        <v>George Birge</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,3736 +4231,3508 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Always Everywhere</v>
       </c>
       <c r="B102" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>9 days ago</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="G102" t="str">
-        <v>4:41</v>
+        <v>3:03</v>
       </c>
       <c r="H102" t="str">
-        <v>NICK JONAS</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
       </c>
       <c r="L102" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Always Everywhere - Charli xcx</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Be Her</v>
       </c>
       <c r="B103" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>9 days ago</v>
+        <v>Dandelion</v>
       </c>
       <c r="G103" t="str">
-        <v>7:03</v>
+        <v>3:37</v>
       </c>
       <c r="H103" t="str">
-        <v>Take That</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L103" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>other side.</v>
       </c>
       <c r="B104" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>9 days ago</v>
+        <v>Icon</v>
       </c>
       <c r="G104" t="str">
-        <v>4:37</v>
+        <v>3:15</v>
       </c>
       <c r="H104" t="str">
-        <v>Cliff Richard</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L104" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B105" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>9 days ago</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:54</v>
+        <v>3:22</v>
       </c>
       <c r="H105" t="str">
-        <v>Bryan Adams</v>
+        <v>John Summit</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L105" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B106" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>9 days ago</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G106" t="str">
-        <v>3:06</v>
+        <v>3:00</v>
       </c>
       <c r="H106" t="str">
-        <v>Anna Graves</v>
+        <v>CORTIS</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L106" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B107" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>9 days ago</v>
+        <v>Trying Times</v>
       </c>
       <c r="G107" t="str">
-        <v>3:21</v>
+        <v>3:40</v>
       </c>
       <c r="H107" t="str">
-        <v>George Birge</v>
+        <v>James Blake</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L107" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Always Everywhere</v>
+        <v>Let Me</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Wuthering Heights</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:03</v>
+        <v>4:51</v>
       </c>
       <c r="H108" t="str">
-        <v>Charli xcx</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L108" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Be Her</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Dandelion</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:37</v>
+        <v>2:43</v>
       </c>
       <c r="H109" t="str">
-        <v>Ella Langley</v>
+        <v>Perrie</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L109" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>other side.</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Icon</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G110" t="str">
-        <v>3:15</v>
+        <v>4:03</v>
       </c>
       <c r="H110" t="str">
-        <v>Brent Faiyaz</v>
+        <v>MUNA</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L110" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SHADOWS</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>SHADOWS - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:22</v>
+        <v>3:18</v>
       </c>
       <c r="H111" t="str">
-        <v>John Summit</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L111" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:00</v>
+        <v>3:06</v>
       </c>
       <c r="H112" t="str">
-        <v>CORTIS</v>
+        <v>Central Cee</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L112" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Trying Times</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:40</v>
+        <v>3:59</v>
       </c>
       <c r="H113" t="str">
-        <v>James Blake</v>
+        <v>Arcángel</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L113" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Let Me</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Let Me - Single</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:51</v>
+        <v>4:20</v>
       </c>
       <c r="H114" t="str">
-        <v>Victoria Monét</v>
+        <v>Fred again..</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L114" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Woman In Love</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Cerulean</v>
       </c>
       <c r="G115" t="str">
-        <v>2:43</v>
+        <v>3:52</v>
       </c>
       <c r="H115" t="str">
-        <v>Perrie</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L115" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Be By You</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Dancing On The Wall</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G116" t="str">
-        <v>4:03</v>
+        <v>3:17</v>
       </c>
       <c r="H116" t="str">
-        <v>MUNA</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L116" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>you and forever</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G117" t="str">
-        <v>3:18</v>
+        <v>3:54</v>
       </c>
       <c r="H117" t="str">
-        <v>ATEEZ</v>
+        <v>Bleachers</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L117" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>ROOMS</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:06</v>
+        <v>3:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Central Cee</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L118" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Mírame Baby</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:59</v>
+        <v>3:16</v>
       </c>
       <c r="H119" t="str">
-        <v>Arcángel</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L119" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G120" t="str">
-        <v>4:20</v>
+        <v>3:11</v>
       </c>
       <c r="H120" t="str">
-        <v>Fred again..</v>
+        <v>Junior H</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L120" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Two Hearts</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Cerulean</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:52</v>
+        <v>3:09</v>
       </c>
       <c r="H121" t="str">
-        <v>Danny L Harle</v>
+        <v>Maluma</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L121" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Be By You</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>The Way I Am</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G122" t="str">
-        <v>3:17</v>
+        <v>3:26</v>
       </c>
       <c r="H122" t="str">
-        <v>Luke Combs</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L122" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>you and forever</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G123" t="str">
-        <v>3:54</v>
+        <v>3:21</v>
       </c>
       <c r="H123" t="str">
-        <v>Bleachers</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L123" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ROOMS</v>
+        <v>Thorns</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>ROOMS - Single</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:52</v>
+        <v>3:10</v>
       </c>
       <c r="H124" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L124" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G125" t="str">
-        <v>3:16</v>
+        <v>4:10</v>
       </c>
       <c r="H125" t="str">
-        <v>Bruno Mars</v>
+        <v>Flea</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L125" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>JUICY</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:11</v>
+        <v>3:31</v>
       </c>
       <c r="H126" t="str">
-        <v>Junior H</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L126" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Con el Corazón</v>
+        <v>All They Type</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:09</v>
+        <v>2:52</v>
       </c>
       <c r="H127" t="str">
-        <v>Maluma</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L127" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Get In Girl</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Toy With Me</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:26</v>
+        <v>4:05</v>
       </c>
       <c r="H128" t="str">
-        <v>Meghan Trainor</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L128" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>London Foolishly</v>
+        <v>City</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>My Lover</v>
       </c>
       <c r="G129" t="str">
-        <v>3:21</v>
+        <v>3:16</v>
       </c>
       <c r="H129" t="str">
-        <v>Nick Jonas</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L129" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Thorns</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Thorns - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G130" t="str">
-        <v>3:10</v>
+        <v>2:25</v>
       </c>
       <c r="H130" t="str">
-        <v>Jelly Roll</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L130" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Honora</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:10</v>
+        <v>2:50</v>
       </c>
       <c r="H131" t="str">
-        <v>Flea</v>
+        <v>Knox</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L131" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>JUICY</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>JUICY - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G132" t="str">
-        <v>3:31</v>
+        <v>3:10</v>
       </c>
       <c r="H132" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L132" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>All They Type</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>All They Type - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:52</v>
+        <v>3:38</v>
       </c>
       <c r="H133" t="str">
-        <v>Keke Palmer</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L133" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>More Than A Lover</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>4:05</v>
+        <v>2:57</v>
       </c>
       <c r="H134" t="str">
-        <v>Mary J. Blige</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L134" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>City</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>My Lover</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:16</v>
+        <v>2:58</v>
       </c>
       <c r="H135" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>IVE</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L135" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Eyes Closed</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:25</v>
+        <v>3:15</v>
       </c>
       <c r="H136" t="str">
-        <v>Mimi Webb</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L136" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Go For Broke</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G137" t="str">
-        <v>2:50</v>
+        <v>5:21</v>
       </c>
       <c r="H137" t="str">
-        <v>Knox</v>
+        <v>Don Broco</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L137" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:10</v>
+        <v>3:26</v>
       </c>
       <c r="H138" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L138" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Kentucky Too Long</v>
+        <v>for your love</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:38</v>
+        <v>3:05</v>
       </c>
       <c r="H139" t="str">
-        <v>Charley Crockett</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L139" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Somebody</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:57</v>
+        <v>3:23</v>
       </c>
       <c r="H140" t="str">
-        <v>Mon Rovîa</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L140" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>BANG BANG</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BANG BANG - Single</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:58</v>
+        <v>1:55</v>
       </c>
       <c r="H141" t="str">
-        <v>IVE</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L141" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>On and On</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G142" t="str">
-        <v>3:15</v>
+        <v>3:43</v>
       </c>
       <c r="H142" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L142" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Nightmare Tripping</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Nightmare Tripping</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G143" t="str">
-        <v>5:21</v>
+        <v>2:44</v>
       </c>
       <c r="H143" t="str">
-        <v>Don Broco</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L143" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>3:26</v>
+        <v>2:46</v>
       </c>
       <c r="H144" t="str">
-        <v>Knocked Loose</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L144" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>for your love</v>
+        <v>Somebody</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>for your love - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G145" t="str">
-        <v>3:05</v>
+        <v>2:49</v>
       </c>
       <c r="H145" t="str">
-        <v>Cruz Beckham</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L145" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Somebody</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Somebody - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:23</v>
+        <v>3:28</v>
       </c>
       <c r="H146" t="str">
-        <v>Jamie Foxx</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L146" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>1:55</v>
+        <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>BKTHERULA</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L147" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>On and On</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Work of Heart</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G148" t="str">
-        <v>3:43</v>
+        <v>4:04</v>
       </c>
       <c r="H148" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L148" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Push My Luck</v>
+        <v>Beatback</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Ö</v>
       </c>
       <c r="G149" t="str">
-        <v>2:44</v>
+        <v>2:19</v>
       </c>
       <c r="H149" t="str">
-        <v>Cold War Kids</v>
+        <v>Fcukers</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L149" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Memphis Players</v>
+        <v>GANG</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:46</v>
+        <v>3:44</v>
       </c>
       <c r="H150" t="str">
-        <v>Anish Kumar</v>
+        <v>Tink</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L150" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Somebody</v>
+        <v>a love song for u</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>2:49</v>
+        <v>1:40</v>
       </c>
       <c r="H151" t="str">
-        <v>Good Neighbours</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L151" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>If I Didn't Know You</v>
+        <v>See Through</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G152" t="str">
-        <v>3:28</v>
+        <v>2:38</v>
       </c>
       <c r="H152" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L152" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Seven Seas</v>
+        <v>be the girl!</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Seven Seas - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G153" t="str">
-        <v>3:01</v>
+        <v>5:33</v>
       </c>
       <c r="H153" t="str">
-        <v>Dirty Heads</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L153" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>1000 Ways</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>A Love For Strangers</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:04</v>
+        <v>3:33</v>
       </c>
       <c r="H154" t="str">
-        <v>Chet Faker</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L154" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Beatback</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Ö</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:19</v>
+        <v>3:40</v>
       </c>
       <c r="H155" t="str">
-        <v>Fcukers</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L155" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>GANG</v>
+        <v>ARCADE</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>GANG - Single</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:44</v>
+        <v>2:52</v>
       </c>
       <c r="H156" t="str">
-        <v>Tink</v>
+        <v>Deb Never</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L156" t="str">
-        <v>GANG - Tink</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>a love song for u</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>a love song for u - EP</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>1:40</v>
+        <v>2:16</v>
       </c>
       <c r="H157" t="str">
-        <v>Eem Triplin</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L157" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>See Through</v>
+        <v>you special.</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:38</v>
+        <v>2:08</v>
       </c>
       <c r="H158" t="str">
-        <v>Story of the Year</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L158" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>be the girl!</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>the apple tree under the sea</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>5:33</v>
+        <v>3:38</v>
       </c>
       <c r="H159" t="str">
-        <v>hemlocke springs</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L159" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:33</v>
+        <v>3:31</v>
       </c>
       <c r="H160" t="str">
-        <v>Erin LeCount</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L160" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:40</v>
+        <v>2:43</v>
       </c>
       <c r="H161" t="str">
-        <v>Kid Sistr</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L161" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>ARCADE</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>ARCADE - Single</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G162" t="str">
-        <v>2:52</v>
+        <v>4:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Deb Never</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L162" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Girls Just Wanna</v>
+        <v>To B Honest</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Girlhood - EP</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G163" t="str">
-        <v>2:16</v>
+        <v>4:30</v>
       </c>
       <c r="H163" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L163" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>you special.</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>you special. - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G164" t="str">
-        <v>2:08</v>
+        <v>2:41</v>
       </c>
       <c r="H164" t="str">
-        <v>YFN Lucci</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L164" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Bass Dhol</v>
+        <v>Koneko</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:38</v>
+        <v>4:08</v>
       </c>
       <c r="H165" t="str">
-        <v>Ahadadream</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L165" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:31</v>
+        <v>2:58</v>
       </c>
       <c r="H166" t="str">
-        <v>Charles Kelley</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L166" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>If I See Her Again</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:43</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>Maddox Batson</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L167" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>Pop Off</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Under The Sun</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:43</v>
+        <v>3:16</v>
       </c>
       <c r="H168" t="str">
-        <v>Sun-El Musician</v>
+        <v>GRiZ</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L168" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>To B Honest</v>
+        <v>dreams</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>To Whom This May Concern</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:30</v>
+        <v>3:31</v>
       </c>
       <c r="H169" t="str">
-        <v>Jill Scott</v>
+        <v>Azzecca</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L169" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>lil xan goes to washington</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>the beltway is burning</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:41</v>
+        <v>2:55</v>
       </c>
       <c r="H170" t="str">
-        <v>Ekko Astral</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L170" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Koneko</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Kurage - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>4:08</v>
+        <v>2:52</v>
       </c>
       <c r="H171" t="str">
-        <v>Liana Flores</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L171" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Cupid's Call</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G172" t="str">
         <v>2:58</v>
       </c>
       <c r="H172" t="str">
-        <v>Dizzy Fae</v>
+        <v>Cardinals</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L172" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Steady</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H173" t="str">
-        <v>Chloé Caillet</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L173" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Pop Off</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Pop Off - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G174" t="str">
-        <v>3:16</v>
+        <v>2:20</v>
       </c>
       <c r="H174" t="str">
-        <v>GRiZ</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L174" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>dreams</v>
+        <v>Nada Más</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>dreams - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:31</v>
+        <v>2:19</v>
       </c>
       <c r="H175" t="str">
-        <v>Azzecca</v>
+        <v>Tombochio</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L175" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Love Hate Love</v>
+        <v>Friends Again</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:55</v>
+        <v>3:38</v>
       </c>
       <c r="H176" t="str">
-        <v>Owen Riegling</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L176" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Do It All Alone</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:52</v>
+        <v>3:22</v>
       </c>
       <c r="H177" t="str">
-        <v>Rend Collective</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L177" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>She Makes Me Real</v>
+        <v>desire.</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Masquerade</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G178" t="str">
-        <v>2:58</v>
+        <v>3:15</v>
       </c>
       <c r="H178" t="str">
-        <v>Cardinals</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L178" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Steady</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G179" t="str">
-        <v>3:26</v>
+        <v>3:12</v>
       </c>
       <c r="H179" t="str">
-        <v>Bella Kay</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L179" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>DIRTY TECH</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>PLAY ME</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:20</v>
+        <v>4:00</v>
       </c>
       <c r="H180" t="str">
-        <v>Kim Gordon</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L180" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Nada Más</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Nada Más - Single</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G181" t="str">
-        <v>2:19</v>
+        <v>2:46</v>
       </c>
       <c r="H181" t="str">
-        <v>Tombochio</v>
+        <v>Anjimile</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L181" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Friends Again</v>
+        <v>Man's World</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Friends Again - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G182" t="str">
-        <v>3:38</v>
+        <v>2:42</v>
       </c>
       <c r="H182" t="str">
-        <v>Baby Rose</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L182" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>W.T.A.</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>W.T.A. - Single</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:22</v>
+        <v>3:13</v>
       </c>
       <c r="H183" t="str">
-        <v>Isaia Huron</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L183" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>desire.</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>November Scorpio</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>3:15</v>
+        <v>2:51</v>
       </c>
       <c r="H184" t="str">
-        <v>Tiana Major9</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L184" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:12</v>
+        <v>5:23</v>
       </c>
       <c r="H185" t="str">
-        <v>August Ponthier</v>
+        <v>BUNT.</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L185" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Killer Whale</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Killer Whale - Single</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:00</v>
+        <v>3:07</v>
       </c>
       <c r="H186" t="str">
-        <v>Hayden Everett</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L186" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Waits for Me</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>You’re Free to Go</v>
+        <v>The Elephant</v>
       </c>
       <c r="G187" t="str">
-        <v>2:46</v>
+        <v>3:28</v>
       </c>
       <c r="H187" t="str">
-        <v>Anjimile</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L187" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Man's World</v>
+        <v>Yes</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Mud Blood Bone</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G188" t="str">
-        <v>2:42</v>
+        <v>3:21</v>
       </c>
       <c r="H188" t="str">
-        <v>Cat Clyde</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L188" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>In the Middle of It</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:13</v>
+        <v>2:52</v>
       </c>
       <c r="H189" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>WesGhost</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L189" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Fleeting - EP</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G190" t="str">
-        <v>2:51</v>
+        <v>2:48</v>
       </c>
       <c r="H190" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Converge</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L190" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G191" t="str">
-        <v>5:23</v>
+        <v>4:00</v>
       </c>
       <c r="H191" t="str">
-        <v>BUNT.</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L191" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>I've Never Met Her</v>
+        <v>Angel Eyes</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>God Forgives - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:07</v>
+        <v>2:14</v>
       </c>
       <c r="H192" t="str">
-        <v>Ally Salort</v>
+        <v>Guilt Trip</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
       </c>
       <c r="L192" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>Angel Eyes - Guilt Trip</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Elephant</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G193" t="str">
-        <v>3:28</v>
+        <v>3:17</v>
       </c>
       <c r="H193" t="str">
-        <v>Ledbyher</v>
+        <v>Melvins</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
       <c r="L193" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
-      </c>
-      <c r="D194" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
-        <v>Just A Few Folk</v>
-      </c>
-      <c r="G194" t="str">
-        <v>3:21</v>
-      </c>
-      <c r="H194" t="str">
-        <v>JP Cooper</v>
-      </c>
-      <c r="I194" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
-      </c>
-      <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
-      </c>
-      <c r="L194" t="str">
-        <v>Yes - JP Cooper</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>CHOKEHOLD</v>
-      </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
-      </c>
-      <c r="D195" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
-        <v>CHOKEHOLD - Single</v>
-      </c>
-      <c r="G195" t="str">
-        <v>2:52</v>
-      </c>
-      <c r="H195" t="str">
-        <v>WesGhost</v>
-      </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
-      </c>
-      <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
-      </c>
-      <c r="L195" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Bad Faith</v>
-      </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
-      </c>
-      <c r="D196" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
-        <v>Love Is Not Enough</v>
-      </c>
-      <c r="G196" t="str">
-        <v>2:48</v>
-      </c>
-      <c r="H196" t="str">
-        <v>Converge</v>
-      </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
-      </c>
-      <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
-      </c>
-      <c r="L196" t="str">
-        <v>Bad Faith - Converge</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Gimme Some Moore</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>Good God / Baad Man</v>
-      </c>
-      <c r="G197" t="str">
-        <v>4:00</v>
-      </c>
-      <c r="H197" t="str">
-        <v>Corrosion of Conformity</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
-      </c>
-      <c r="L197" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>Angel Eyes</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>God Forgives - Single</v>
-      </c>
-      <c r="G198" t="str">
-        <v>2:14</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Guilt Trip</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
-      </c>
-      <c r="L198" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Tossing Coins Into The Fountain Of F**k</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G199" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
-      </c>
-      <c r="L199" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -705,7 +705,7 @@
         <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>7:48</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
@@ -1533,7 +1533,7 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>2 days ago</v>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
@@ -2529,7 +2529,7 @@
         <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B57" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:09</v>
@@ -3365,7 +3365,7 @@
         <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B79" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>10:57</v>

--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -1465,7 +1465,7 @@
         <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:17</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:21</v>
@@ -1533,7 +1533,7 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
@@ -1541,7 +1541,7 @@
         <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>6:58</v>
@@ -1579,7 +1579,7 @@
         <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:29</v>
@@ -1617,7 +1617,7 @@
         <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:14</v>
@@ -1655,7 +1655,7 @@
         <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:51</v>
@@ -1693,7 +1693,7 @@
         <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:10</v>
@@ -1731,7 +1731,7 @@
         <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:26</v>
@@ -1769,7 +1769,7 @@
         <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>2:51</v>
@@ -1807,7 +1807,7 @@
         <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:26</v>
@@ -1845,7 +1845,7 @@
         <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:06</v>
@@ -1883,7 +1883,7 @@
         <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:04</v>
@@ -1921,7 +1921,7 @@
         <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B41" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:03</v>
@@ -1959,7 +1959,7 @@
         <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:38</v>
@@ -1997,7 +1997,7 @@
         <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:29</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:32</v>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
@@ -2073,7 +2073,7 @@
         <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:32</v>
@@ -2111,7 +2111,7 @@
         <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>2:51</v>
@@ -2149,7 +2149,7 @@
         <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:38</v>
@@ -2187,7 +2187,7 @@
         <v>Nickless - As I Am</v>
       </c>
       <c r="B48" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:26</v>
@@ -2225,7 +2225,7 @@
         <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:57</v>
@@ -2263,7 +2263,7 @@
         <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:08</v>
@@ -2301,7 +2301,7 @@
         <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:53</v>
@@ -2339,7 +2339,7 @@
         <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:10</v>
@@ -2377,7 +2377,7 @@
         <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>2:58</v>
@@ -2415,7 +2415,7 @@
         <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>2:44</v>
@@ -2453,7 +2453,7 @@
         <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:25</v>
@@ -2491,7 +2491,7 @@
         <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>4:08</v>
@@ -2909,7 +2909,7 @@
         <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>2:33</v>
@@ -3289,7 +3289,7 @@
         <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:27</v>
@@ -3327,7 +3327,7 @@
         <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:25</v>
@@ -3631,7 +3631,7 @@
         <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>2:26</v>
@@ -4163,7 +4163,7 @@
         <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>3:06</v>
@@ -4201,7 +4201,7 @@
         <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B101" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:21</v>

--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>אופיר הדס – משוגע</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%94%d7%93%d7%a1-%d7%9e%d7%a9%d7%95%d7%92%d7%a2/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>“משוגע” של אופיר הדס הוא שיר עם לב כפול: מצד אחד – טקסט פנימי, כמעט קלסטרופובי, על אדם הסגור בתוך עצמו. מצד שני – עיבוד לטיני קצבי (בין סמבה לרומבה) שמניע את הגוף קדימה. הפער הזה הוא לא מקרי. הוא</v>
       </c>
       <c r="G2" t="str">
-        <v>5:31</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>אופיר הדס – משוגע</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-16</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:49</v>
+        <v>5:31</v>
       </c>
       <c r="H3" t="str">
-        <v>Mýa</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-16</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:03</v>
+        <v>2:49</v>
       </c>
       <c r="H4" t="str">
-        <v>Michael Bolton</v>
+        <v>Mýa</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-16</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:59</v>
+        <v>3:03</v>
       </c>
       <c r="H5" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-16</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H6" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-16</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H7" t="str">
-        <v>ENHYPEN</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-16</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H8" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>7:48</v>
+        <v>3:59</v>
       </c>
       <c r="H9" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-16</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:10</v>
+        <v>7:48</v>
       </c>
       <c r="H10" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-16</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>5:57</v>
+        <v>3:10</v>
       </c>
       <c r="H11" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-16</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:25</v>
+        <v>5:57</v>
       </c>
       <c r="H12" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-16</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:19</v>
+        <v>2:25</v>
       </c>
       <c r="H13" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-16</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:38</v>
+        <v>3:19</v>
       </c>
       <c r="H14" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-16</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:05</v>
+        <v>3:38</v>
       </c>
       <c r="H15" t="str">
-        <v>Dermot Kennedy</v>
+        <v>mgk</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-16</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>5:46</v>
+        <v>4:05</v>
       </c>
       <c r="H16" t="str">
-        <v>Jacob Collier</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-16</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:25</v>
+        <v>5:46</v>
       </c>
       <c r="H17" t="str">
-        <v>Victor Ray</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-16</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:11</v>
+        <v>3:25</v>
       </c>
       <c r="H18" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-16</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:55</v>
+        <v>5:11</v>
       </c>
       <c r="H19" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-16</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:54</v>
+        <v>2:55</v>
       </c>
       <c r="H20" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-16</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:01</v>
+        <v>4:54</v>
       </c>
       <c r="H21" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Offspring</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-16</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:55</v>
+        <v>5:01</v>
       </c>
       <c r="H22" t="str">
-        <v>HAUSER</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-16</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H23" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>HAUSER</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Jillian Jacquline - Another Lover (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H24" t="str">
-        <v>Ultra Records</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:30</v>
+        <v>2:53</v>
       </c>
       <c r="H25" t="str">
-        <v>Anja Kotar</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-16</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:37</v>
+        <v>3:30</v>
       </c>
       <c r="H26" t="str">
-        <v>Michael Bolton</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-16</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H27" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-16</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:06</v>
+        <v>4:10</v>
       </c>
       <c r="H28" t="str">
-        <v>Alan Walker</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-16</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:17</v>
+        <v>3:06</v>
       </c>
       <c r="H29" t="str">
-        <v>Bruno Mars</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-16</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H30" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-16</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>6:58</v>
+        <v>3:21</v>
       </c>
       <c r="H31" t="str">
-        <v>Eric Church</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-16</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:29</v>
+        <v>6:58</v>
       </c>
       <c r="H32" t="str">
-        <v>Meghan Trainor</v>
+        <v>Eric Church</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-16</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H33" t="str">
-        <v>Ally Salort</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-16</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:51</v>
+        <v>3:14</v>
       </c>
       <c r="H34" t="str">
-        <v>Will Swinton</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-16</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:10</v>
+        <v>3:51</v>
       </c>
       <c r="H35" t="str">
-        <v>elijah woods</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-16</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="H36" t="str">
-        <v>Jackson Dean</v>
+        <v>elijah woods</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-16</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H37" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-16</v>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H38" t="str">
-        <v>Neil Sedaka</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-16</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H39" t="str">
-        <v>Sofia Camara</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-16</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:04</v>
+        <v>3:06</v>
       </c>
       <c r="H40" t="str">
-        <v>Russell Dickerson</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-16</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H41" t="str">
-        <v>Celine Dion</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-16</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:38</v>
+        <v>3:03</v>
       </c>
       <c r="H42" t="str">
-        <v>Bebe Rexha</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-16</v>
@@ -2012,10 +2012,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:29</v>
+        <v>2:38</v>
       </c>
       <c r="H43" t="str">
-        <v>Caroline Jones</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-16</v>
@@ -2050,10 +2050,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:32</v>
+        <v>3:29</v>
       </c>
       <c r="H44" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-16</v>
@@ -2088,10 +2088,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>2:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Ingrid Andress</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-16</v>
@@ -2126,10 +2126,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:51</v>
+        <v>3:32</v>
       </c>
       <c r="H46" t="str">
-        <v>MusicByKnox</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B47" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-16</v>
@@ -2164,10 +2164,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H47" t="str">
-        <v>Ella Langley</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B48" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-16</v>
@@ -2202,10 +2202,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:26</v>
+        <v>3:38</v>
       </c>
       <c r="H48" t="str">
-        <v>Nickless</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B49" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-16</v>
@@ -2240,10 +2240,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:57</v>
+        <v>3:26</v>
       </c>
       <c r="H49" t="str">
-        <v>Caroline Jones</v>
+        <v>Nickless</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-16</v>
@@ -2278,10 +2278,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:08</v>
+        <v>3:57</v>
       </c>
       <c r="H50" t="str">
-        <v>elijah woods</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-16</v>
@@ -2316,10 +2316,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:53</v>
+        <v>3:08</v>
       </c>
       <c r="H51" t="str">
-        <v>August Ponthier</v>
+        <v>elijah woods</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B52" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-16</v>
@@ -2354,10 +2354,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:10</v>
+        <v>3:53</v>
       </c>
       <c r="H52" t="str">
-        <v>Charli xcx</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-16</v>
@@ -2392,10 +2392,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:58</v>
+        <v>3:10</v>
       </c>
       <c r="H53" t="str">
-        <v>Caroline Jones</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-16</v>
@@ -2430,10 +2430,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:44</v>
+        <v>2:58</v>
       </c>
       <c r="H54" t="str">
-        <v>Leah Kate</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-16</v>
@@ -2468,10 +2468,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:25</v>
+        <v>2:44</v>
       </c>
       <c r="H55" t="str">
-        <v>Troye Sivan</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-16</v>
@@ -2506,10 +2506,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:08</v>
+        <v>3:25</v>
       </c>
       <c r="H56" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-16</v>
@@ -2544,10 +2544,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:09</v>
+        <v>4:08</v>
       </c>
       <c r="H57" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B58" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-16</v>
@@ -2582,10 +2582,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:11</v>
+        <v>3:09</v>
       </c>
       <c r="H58" t="str">
-        <v>The Happy Fits</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-16</v>
@@ -2620,10 +2620,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:02</v>
+        <v>3:11</v>
       </c>
       <c r="H59" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B60" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-16</v>
@@ -2658,10 +2658,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:20</v>
+        <v>3:02</v>
       </c>
       <c r="H60" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B61" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-16</v>
@@ -2696,10 +2696,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:09</v>
+        <v>4:20</v>
       </c>
       <c r="H61" t="str">
-        <v>Quinn XCII</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B62" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-16</v>
@@ -2734,10 +2734,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:34</v>
+        <v>4:09</v>
       </c>
       <c r="H62" t="str">
-        <v>We Three</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B63" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-16</v>
@@ -2772,10 +2772,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:29</v>
+        <v>4:34</v>
       </c>
       <c r="H63" t="str">
-        <v>A Thousand Horses</v>
+        <v>We Three</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B64" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-16</v>
@@ -2810,10 +2810,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:51</v>
+        <v>3:29</v>
       </c>
       <c r="H64" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B65" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-16</v>
@@ -2848,10 +2848,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:56</v>
+        <v>2:51</v>
       </c>
       <c r="H65" t="str">
-        <v>Constant Smiles</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-16</v>
@@ -2886,10 +2886,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:25</v>
+        <v>2:56</v>
       </c>
       <c r="H66" t="str">
-        <v>P!NK</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-16</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:33</v>
+        <v>3:25</v>
       </c>
       <c r="H67" t="str">
-        <v>Bazzi</v>
+        <v>P!NK</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-16</v>
@@ -2962,10 +2962,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:18</v>
+        <v>2:33</v>
       </c>
       <c r="H68" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bazzi</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B69" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-16</v>
@@ -3000,7 +3000,7 @@
         <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:08</v>
+        <v>4:18</v>
       </c>
       <c r="H69" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B70" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-16</v>
@@ -3038,10 +3038,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:56</v>
+        <v>2:08</v>
       </c>
       <c r="H70" t="str">
-        <v>bleachers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-16</v>
@@ -3076,10 +3076,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:27</v>
+        <v>3:56</v>
       </c>
       <c r="H71" t="str">
-        <v>The Academic</v>
+        <v>bleachers</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-16</v>
@@ -3114,10 +3114,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:39</v>
+        <v>3:27</v>
       </c>
       <c r="H72" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Academic</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B73" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-16</v>
@@ -3152,10 +3152,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:54</v>
+        <v>2:39</v>
       </c>
       <c r="H73" t="str">
-        <v>Michael Bolton</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-16</v>
@@ -3190,10 +3190,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:47</v>
+        <v>3:54</v>
       </c>
       <c r="H74" t="str">
-        <v>Caroline Jones</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B75" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-16</v>
@@ -3228,10 +3228,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:07</v>
+        <v>3:47</v>
       </c>
       <c r="H75" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B76" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-16</v>
@@ -3266,10 +3266,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:00</v>
+        <v>4:07</v>
       </c>
       <c r="H76" t="str">
-        <v>Michael Bolton</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B77" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-16</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:27</v>
+        <v>5:00</v>
       </c>
       <c r="H77" t="str">
-        <v>Little Big Town</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B78" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-16</v>
@@ -3342,10 +3342,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H78" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-16</v>
@@ -3380,10 +3380,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>10:57</v>
+        <v>3:25</v>
       </c>
       <c r="H79" t="str">
-        <v>JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B80" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-16</v>
@@ -3418,10 +3418,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:14</v>
+        <v>10:57</v>
       </c>
       <c r="H80" t="str">
-        <v>Robert Grace</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B81" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-16</v>
@@ -3456,10 +3456,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:26</v>
+        <v>4:14</v>
       </c>
       <c r="H81" t="str">
-        <v>mgk</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-16</v>
@@ -3494,10 +3494,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:59</v>
+        <v>3:26</v>
       </c>
       <c r="H82" t="str">
-        <v>Victor Ray</v>
+        <v>mgk</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B83" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:46</v>
+        <v>5:59</v>
       </c>
       <c r="H83" t="str">
-        <v>Perrie</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-16</v>
@@ -3570,10 +3570,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:39</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Michael Bolton</v>
+        <v>Perrie</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B85" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-16</v>
@@ -3608,10 +3608,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:58</v>
+        <v>3:39</v>
       </c>
       <c r="H85" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B86" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:26</v>
+        <v>3:58</v>
       </c>
       <c r="H86" t="str">
-        <v>Mimi Webb</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-16</v>
@@ -3684,10 +3684,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:04</v>
+        <v>2:26</v>
       </c>
       <c r="H87" t="str">
-        <v>Olivia Dean</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B88" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-16</v>
@@ -3722,10 +3722,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>6:00</v>
+        <v>3:04</v>
       </c>
       <c r="H88" t="str">
-        <v>Taylor Swift</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-16</v>
@@ -3760,10 +3760,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:20</v>
+        <v>6:00</v>
       </c>
       <c r="H89" t="str">
-        <v>Michael Bolton</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-16</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:27</v>
+        <v>4:20</v>
       </c>
       <c r="H90" t="str">
-        <v>Mariah Carey</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B91" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-16</v>
@@ -3836,10 +3836,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:26</v>
+        <v>4:27</v>
       </c>
       <c r="H91" t="str">
-        <v>Netflix</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B92" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-16</v>
@@ -3874,10 +3874,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H92" t="str">
-        <v>Michael Bolton</v>
+        <v>Netflix</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-16</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H93" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-16</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:51</v>
+        <v>2:59</v>
       </c>
       <c r="H94" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>mgk</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B95" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-16</v>
@@ -3988,10 +3988,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:13</v>
+        <v>2:51</v>
       </c>
       <c r="H95" t="str">
-        <v>Michael Bolton</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B96" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-16</v>
@@ -4026,10 +4026,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:41</v>
+        <v>4:13</v>
       </c>
       <c r="H96" t="str">
-        <v>NICK JONAS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B97" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-16</v>
@@ -4064,10 +4064,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>7:03</v>
+        <v>4:41</v>
       </c>
       <c r="H97" t="str">
-        <v>Take That</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B98" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-16</v>
@@ -4102,10 +4102,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:37</v>
+        <v>7:03</v>
       </c>
       <c r="H98" t="str">
-        <v>Cliff Richard</v>
+        <v>Take That</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B99" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-16</v>
@@ -4140,10 +4140,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:54</v>
+        <v>4:37</v>
       </c>
       <c r="H99" t="str">
-        <v>Bryan Adams</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-16</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:06</v>
+        <v>3:54</v>
       </c>
       <c r="H100" t="str">
-        <v>Anna Graves</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-16</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H101" t="str">
-        <v>George Birge</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Always Everywhere</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Wuthering Heights</v>
+        <v>10 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H102" t="str">
-        <v>Charli xcx</v>
+        <v>George Birge</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Be Her</v>
+        <v>Always Everywhere</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Dandelion</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="G103" t="str">
-        <v>3:37</v>
+        <v>3:03</v>
       </c>
       <c r="H103" t="str">
-        <v>Ella Langley</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
       </c>
       <c r="L103" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>Always Everywhere - Charli xcx</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>other side.</v>
+        <v>Be Her</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Icon</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>3:15</v>
+        <v>3:37</v>
       </c>
       <c r="H104" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SHADOWS</v>
+        <v>other side.</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>SHADOWS - Single</v>
+        <v>Icon</v>
       </c>
       <c r="G105" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H105" t="str">
-        <v>John Summit</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L105" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:00</v>
+        <v>3:22</v>
       </c>
       <c r="H106" t="str">
-        <v>CORTIS</v>
+        <v>John Summit</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L106" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Trying Times</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G107" t="str">
-        <v>3:40</v>
+        <v>3:00</v>
       </c>
       <c r="H107" t="str">
-        <v>James Blake</v>
+        <v>CORTIS</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L107" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Let Me</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Let Me - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G108" t="str">
-        <v>4:51</v>
+        <v>3:40</v>
       </c>
       <c r="H108" t="str">
-        <v>Victoria Monét</v>
+        <v>James Blake</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L108" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H109" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L109" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H110" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L110" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G111" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H111" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L111" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H112" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L112" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H113" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L113" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H114" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L114" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H115" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L115" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G116" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H116" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L116" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G117" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L117" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G118" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H118" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L118" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H119" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L119" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H120" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L120" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G121" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H121" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L121" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H122" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L122" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G123" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H123" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L123" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G124" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H124" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L124" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H125" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L125" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G126" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H126" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L126" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H127" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L127" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H128" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L128" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L129" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G130" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H130" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L130" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G131" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H131" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L131" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L132" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G133" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H133" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L133" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H134" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L134" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H135" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L135" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H137" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L137" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G138" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H138" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L138" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H139" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L139" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H140" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L140" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H141" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L141" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H142" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L142" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G143" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H143" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L143" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H144" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L144" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G145" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H145" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L145" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G146" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H146" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L146" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H147" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L147" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L148" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G149" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H149" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L149" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G150" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H150" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L150" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H151" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L151" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H152" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L152" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G153" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H153" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L153" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G154" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H154" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L154" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H155" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L155" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H156" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L156" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H157" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L157" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H158" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L158" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H159" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L159" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H160" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L160" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H161" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L161" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L162" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G163" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L163" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G164" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H164" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L164" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G165" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H165" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L165" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H166" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L166" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H167" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L167" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L168" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H169" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L169" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H170" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L170" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H171" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L171" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H172" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L172" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G173" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H173" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L173" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H174" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L174" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G175" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H175" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L175" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H176" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L176" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H177" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L177" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L178" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G179" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H179" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L179" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G180" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H180" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L180" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H181" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L181" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G182" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H182" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L182" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G183" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H183" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L183" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H184" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L184" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H185" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L185" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H186" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L186" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H187" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L187" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G188" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H188" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L188" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G189" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H189" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L189" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H190" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L190" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G191" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H191" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L191" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-16</v>
@@ -7671,68 +7671,106 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G192" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H192" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L192" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B193" t="str">
+        <v/>
+      </c>
+      <c r="C193" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G193" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H193" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I193" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J193" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K193" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B193" t="str">
-        <v/>
-      </c>
-      <c r="C193" t="str">
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D193" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
+      <c r="D194" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G193" t="str">
+      <c r="G194" t="str">
         <v>3:17</v>
       </c>
-      <c r="H193" t="str">
+      <c r="H194" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I193" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J193" t="str">
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K193" t="str">
+      <c r="K194" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L193" t="str">
+      <c r="L194" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופיר הדס – משוגע</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-16</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%94%d7%93%d7%a1-%d7%9e%d7%a9%d7%95%d7%92%d7%a2/</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“משוגע” של אופיר הדס הוא שיר עם לב כפול: מצד אחד – טקסט פנימי, כמעט קלסטרופובי, על אדם הסגור בתוך עצמו. מצד שני – עיבוד לטיני קצבי (בין סמבה לרומבה) שמניע את הגוף קדימה. הפער הזה הוא לא מקרי. הוא</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>5:31</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופיר הדס – משוגע</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-16</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>5:31</v>
+        <v>2:49</v>
       </c>
       <c r="H3" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Mýa</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-16</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:49</v>
+        <v>3:03</v>
       </c>
       <c r="H4" t="str">
-        <v>Mýa</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-16</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:03</v>
+        <v>2:59</v>
       </c>
       <c r="H5" t="str">
-        <v>Michael Bolton</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-16</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H6" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-16</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H7" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-16</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:59</v>
+        <v>3:59</v>
       </c>
       <c r="H8" t="str">
-        <v>ENHYPEN</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:59</v>
+        <v>7:48</v>
       </c>
       <c r="H9" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-16</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>7:48</v>
+        <v>3:10</v>
       </c>
       <c r="H10" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-16</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:10</v>
+        <v>5:57</v>
       </c>
       <c r="H11" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-16</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:57</v>
+        <v>2:25</v>
       </c>
       <c r="H12" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-16</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:25</v>
+        <v>3:19</v>
       </c>
       <c r="H13" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-16</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:19</v>
+        <v>3:38</v>
       </c>
       <c r="H14" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-16</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:38</v>
+        <v>4:05</v>
       </c>
       <c r="H15" t="str">
-        <v>mgk</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-16</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:05</v>
+        <v>5:46</v>
       </c>
       <c r="H16" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-16</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>5:46</v>
+        <v>3:25</v>
       </c>
       <c r="H17" t="str">
-        <v>Jacob Collier</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-16</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:25</v>
+        <v>5:11</v>
       </c>
       <c r="H18" t="str">
-        <v>Victor Ray</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-16</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>5:11</v>
+        <v>2:55</v>
       </c>
       <c r="H19" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>The Warning</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-16</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:55</v>
+        <v>4:54</v>
       </c>
       <c r="H20" t="str">
-        <v>The Warning</v>
+        <v>The Offspring</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-16</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:54</v>
+        <v>5:01</v>
       </c>
       <c r="H21" t="str">
-        <v>The Offspring</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-16</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:01</v>
+        <v>3:55</v>
       </c>
       <c r="H22" t="str">
-        <v>Caitlyn Smith</v>
+        <v>HAUSER</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Jillian Jacquline - Another Lover (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-16</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:55</v>
+        <v>3:43</v>
       </c>
       <c r="H23" t="str">
-        <v>HAUSER</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H24" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:53</v>
+        <v>3:30</v>
       </c>
       <c r="H25" t="str">
-        <v>Ultra Records</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-16</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:30</v>
+        <v>3:37</v>
       </c>
       <c r="H26" t="str">
-        <v>Anja Kotar</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-16</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:37</v>
+        <v>4:10</v>
       </c>
       <c r="H27" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-16</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:10</v>
+        <v>3:06</v>
       </c>
       <c r="H28" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-16</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H29" t="str">
-        <v>Alan Walker</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-16</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H30" t="str">
-        <v>Bruno Mars</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-16</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:21</v>
+        <v>6:58</v>
       </c>
       <c r="H31" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Eric Church</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-16</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>6:58</v>
+        <v>3:29</v>
       </c>
       <c r="H32" t="str">
-        <v>Eric Church</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-16</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:29</v>
+        <v>3:14</v>
       </c>
       <c r="H33" t="str">
-        <v>Meghan Trainor</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-16</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:14</v>
+        <v>3:51</v>
       </c>
       <c r="H34" t="str">
-        <v>Ally Salort</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-16</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:51</v>
+        <v>3:10</v>
       </c>
       <c r="H35" t="str">
-        <v>Will Swinton</v>
+        <v>elijah woods</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-16</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:10</v>
+        <v>3:26</v>
       </c>
       <c r="H36" t="str">
-        <v>elijah woods</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-16</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H37" t="str">
-        <v>Jackson Dean</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-16</v>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H38" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-16</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H39" t="str">
-        <v>Neil Sedaka</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-16</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:06</v>
+        <v>3:04</v>
       </c>
       <c r="H40" t="str">
-        <v>Sofia Camara</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-16</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H41" t="str">
-        <v>Russell Dickerson</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-16</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:03</v>
+        <v>2:38</v>
       </c>
       <c r="H42" t="str">
-        <v>Celine Dion</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-16</v>
@@ -2012,10 +2012,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:38</v>
+        <v>3:29</v>
       </c>
       <c r="H43" t="str">
-        <v>Bebe Rexha</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-16</v>
@@ -2050,10 +2050,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:29</v>
+        <v>2:32</v>
       </c>
       <c r="H44" t="str">
-        <v>Caroline Jones</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-16</v>
@@ -2088,10 +2088,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:32</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-16</v>
@@ -2126,10 +2126,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:32</v>
+        <v>2:51</v>
       </c>
       <c r="H46" t="str">
-        <v>Ingrid Andress</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-16</v>
@@ -2164,10 +2164,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:51</v>
+        <v>3:38</v>
       </c>
       <c r="H47" t="str">
-        <v>MusicByKnox</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B48" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-16</v>
@@ -2202,10 +2202,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H48" t="str">
-        <v>Ella Langley</v>
+        <v>Nickless</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-16</v>
@@ -2240,10 +2240,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:26</v>
+        <v>3:57</v>
       </c>
       <c r="H49" t="str">
-        <v>Nickless</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-16</v>
@@ -2278,10 +2278,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:57</v>
+        <v>3:08</v>
       </c>
       <c r="H50" t="str">
-        <v>Caroline Jones</v>
+        <v>elijah woods</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-16</v>
@@ -2316,10 +2316,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:08</v>
+        <v>3:53</v>
       </c>
       <c r="H51" t="str">
-        <v>elijah woods</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-16</v>
@@ -2354,10 +2354,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:53</v>
+        <v>3:10</v>
       </c>
       <c r="H52" t="str">
-        <v>August Ponthier</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-16</v>
@@ -2392,10 +2392,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:10</v>
+        <v>2:58</v>
       </c>
       <c r="H53" t="str">
-        <v>Charli xcx</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-16</v>
@@ -2430,10 +2430,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:58</v>
+        <v>2:44</v>
       </c>
       <c r="H54" t="str">
-        <v>Caroline Jones</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-16</v>
@@ -2468,10 +2468,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:44</v>
+        <v>3:25</v>
       </c>
       <c r="H55" t="str">
-        <v>Leah Kate</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-16</v>
@@ -2506,10 +2506,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:25</v>
+        <v>4:08</v>
       </c>
       <c r="H56" t="str">
-        <v>Troye Sivan</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B57" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-16</v>
@@ -2544,10 +2544,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:08</v>
+        <v>3:09</v>
       </c>
       <c r="H57" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-16</v>
@@ -2582,10 +2582,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H58" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B59" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-16</v>
@@ -2620,10 +2620,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:11</v>
+        <v>3:02</v>
       </c>
       <c r="H59" t="str">
-        <v>The Happy Fits</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B60" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-16</v>
@@ -2658,10 +2658,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:02</v>
+        <v>4:20</v>
       </c>
       <c r="H60" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B61" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-16</v>
@@ -2696,10 +2696,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:20</v>
+        <v>4:09</v>
       </c>
       <c r="H61" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B62" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-16</v>
@@ -2734,10 +2734,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:09</v>
+        <v>4:34</v>
       </c>
       <c r="H62" t="str">
-        <v>Quinn XCII</v>
+        <v>We Three</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B63" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-16</v>
@@ -2772,10 +2772,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:34</v>
+        <v>3:29</v>
       </c>
       <c r="H63" t="str">
-        <v>We Three</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B64" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-16</v>
@@ -2810,10 +2810,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:29</v>
+        <v>2:51</v>
       </c>
       <c r="H64" t="str">
-        <v>A Thousand Horses</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-16</v>
@@ -2848,10 +2848,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H65" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B66" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-16</v>
@@ -2886,10 +2886,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:56</v>
+        <v>3:25</v>
       </c>
       <c r="H66" t="str">
-        <v>Constant Smiles</v>
+        <v>P!NK</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-16</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:25</v>
+        <v>2:33</v>
       </c>
       <c r="H67" t="str">
-        <v>P!NK</v>
+        <v>Bazzi</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B68" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-16</v>
@@ -2962,10 +2962,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:33</v>
+        <v>4:18</v>
       </c>
       <c r="H68" t="str">
-        <v>Bazzi</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B69" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-16</v>
@@ -3000,7 +3000,7 @@
         <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:18</v>
+        <v>2:08</v>
       </c>
       <c r="H69" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-16</v>
@@ -3038,10 +3038,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:08</v>
+        <v>3:56</v>
       </c>
       <c r="H70" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>bleachers</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-16</v>
@@ -3076,10 +3076,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:56</v>
+        <v>3:27</v>
       </c>
       <c r="H71" t="str">
-        <v>bleachers</v>
+        <v>The Academic</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-16</v>
@@ -3114,10 +3114,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:27</v>
+        <v>2:39</v>
       </c>
       <c r="H72" t="str">
-        <v>The Academic</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B73" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-16</v>
@@ -3152,10 +3152,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:39</v>
+        <v>3:54</v>
       </c>
       <c r="H73" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B74" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-16</v>
@@ -3190,10 +3190,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:54</v>
+        <v>3:47</v>
       </c>
       <c r="H74" t="str">
-        <v>Michael Bolton</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B75" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-16</v>
@@ -3228,10 +3228,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:47</v>
+        <v>4:07</v>
       </c>
       <c r="H75" t="str">
-        <v>Caroline Jones</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-16</v>
@@ -3266,10 +3266,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:07</v>
+        <v>5:00</v>
       </c>
       <c r="H76" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-16</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>5:00</v>
+        <v>3:27</v>
       </c>
       <c r="H77" t="str">
-        <v>Michael Bolton</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-16</v>
@@ -3342,10 +3342,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:27</v>
+        <v>3:25</v>
       </c>
       <c r="H78" t="str">
-        <v>Little Big Town</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B79" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-16</v>
@@ -3380,10 +3380,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:25</v>
+        <v>10:57</v>
       </c>
       <c r="H79" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B80" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-16</v>
@@ -3418,10 +3418,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>10:57</v>
+        <v>4:14</v>
       </c>
       <c r="H80" t="str">
-        <v>JavaJazzFest</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-16</v>
@@ -3456,10 +3456,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:14</v>
+        <v>3:26</v>
       </c>
       <c r="H81" t="str">
-        <v>Robert Grace</v>
+        <v>mgk</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B82" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-16</v>
@@ -3494,10 +3494,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:26</v>
+        <v>5:59</v>
       </c>
       <c r="H82" t="str">
-        <v>mgk</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>5:59</v>
+        <v>2:46</v>
       </c>
       <c r="H83" t="str">
-        <v>Victor Ray</v>
+        <v>Perrie</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-16</v>
@@ -3570,10 +3570,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:46</v>
+        <v>3:39</v>
       </c>
       <c r="H84" t="str">
-        <v>Perrie</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B85" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-16</v>
@@ -3608,10 +3608,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:39</v>
+        <v>3:58</v>
       </c>
       <c r="H85" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:58</v>
+        <v>2:26</v>
       </c>
       <c r="H86" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B87" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-16</v>
@@ -3684,10 +3684,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:26</v>
+        <v>3:04</v>
       </c>
       <c r="H87" t="str">
-        <v>Mimi Webb</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-16</v>
@@ -3722,10 +3722,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:04</v>
+        <v>6:00</v>
       </c>
       <c r="H88" t="str">
-        <v>Olivia Dean</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-16</v>
@@ -3760,10 +3760,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>6:00</v>
+        <v>4:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Taylor Swift</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B90" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-16</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:20</v>
+        <v>4:27</v>
       </c>
       <c r="H90" t="str">
-        <v>Michael Bolton</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B91" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-16</v>
@@ -3836,10 +3836,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:27</v>
+        <v>3:26</v>
       </c>
       <c r="H91" t="str">
-        <v>Mariah Carey</v>
+        <v>Netflix</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B92" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-16</v>
@@ -3874,10 +3874,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H92" t="str">
-        <v>Netflix</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-16</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:29</v>
+        <v>2:59</v>
       </c>
       <c r="H93" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-16</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:59</v>
+        <v>2:51</v>
       </c>
       <c r="H94" t="str">
-        <v>mgk</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-16</v>
@@ -3988,10 +3988,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:51</v>
+        <v>4:13</v>
       </c>
       <c r="H95" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B96" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-16</v>
@@ -4026,10 +4026,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:13</v>
+        <v>4:41</v>
       </c>
       <c r="H96" t="str">
-        <v>Michael Bolton</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B97" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-16</v>
@@ -4064,10 +4064,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:41</v>
+        <v>7:03</v>
       </c>
       <c r="H97" t="str">
-        <v>NICK JONAS</v>
+        <v>Take That</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B98" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-16</v>
@@ -4102,10 +4102,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>7:03</v>
+        <v>4:37</v>
       </c>
       <c r="H98" t="str">
-        <v>Take That</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B99" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-16</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:37</v>
+        <v>3:54</v>
       </c>
       <c r="H99" t="str">
-        <v>Cliff Richard</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-16</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:54</v>
+        <v>3:06</v>
       </c>
       <c r="H100" t="str">
-        <v>Bryan Adams</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-16</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H101" t="str">
-        <v>Anna Graves</v>
+        <v>George Birge</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Always Everywhere</v>
       </c>
       <c r="B102" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>10 days ago</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="G102" t="str">
-        <v>3:21</v>
+        <v>3:03</v>
       </c>
       <c r="H102" t="str">
-        <v>George Birge</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
       </c>
       <c r="L102" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Always Everywhere - Charli xcx</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Always Everywhere</v>
+        <v>Be Her</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Wuthering Heights</v>
+        <v>Dandelion</v>
       </c>
       <c r="G103" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H103" t="str">
-        <v>Charli xcx</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L103" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Be Her</v>
+        <v>other side.</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>Icon</v>
       </c>
       <c r="G104" t="str">
-        <v>3:37</v>
+        <v>3:15</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L104" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>other side.</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Icon</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H105" t="str">
-        <v>Brent Faiyaz</v>
+        <v>John Summit</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L105" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SHADOWS</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>SHADOWS - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G106" t="str">
-        <v>3:22</v>
+        <v>3:00</v>
       </c>
       <c r="H106" t="str">
-        <v>John Summit</v>
+        <v>CORTIS</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L106" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v>3:40</v>
       </c>
       <c r="H107" t="str">
-        <v>CORTIS</v>
+        <v>James Blake</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L107" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Let Me</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Trying Times</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:40</v>
+        <v>4:51</v>
       </c>
       <c r="H108" t="str">
-        <v>James Blake</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L108" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Let Me</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Let Me - Single</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>4:51</v>
+        <v>2:43</v>
       </c>
       <c r="H109" t="str">
-        <v>Victoria Monét</v>
+        <v>Perrie</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L109" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Woman In Love</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G110" t="str">
-        <v>2:43</v>
+        <v>4:03</v>
       </c>
       <c r="H110" t="str">
-        <v>Perrie</v>
+        <v>MUNA</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L110" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:03</v>
+        <v>3:18</v>
       </c>
       <c r="H111" t="str">
-        <v>MUNA</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L111" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:18</v>
+        <v>3:06</v>
       </c>
       <c r="H112" t="str">
-        <v>ATEEZ</v>
+        <v>Central Cee</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L112" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:06</v>
+        <v>3:59</v>
       </c>
       <c r="H113" t="str">
-        <v>Central Cee</v>
+        <v>Arcángel</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L113" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Mírame Baby</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:59</v>
+        <v>4:20</v>
       </c>
       <c r="H114" t="str">
-        <v>Arcángel</v>
+        <v>Fred again..</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L114" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Cerulean</v>
       </c>
       <c r="G115" t="str">
-        <v>4:20</v>
+        <v>3:52</v>
       </c>
       <c r="H115" t="str">
-        <v>Fred again..</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L115" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Two Hearts</v>
+        <v>Be By You</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Cerulean</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G116" t="str">
-        <v>3:52</v>
+        <v>3:17</v>
       </c>
       <c r="H116" t="str">
-        <v>Danny L Harle</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L116" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Be By You</v>
+        <v>you and forever</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Way I Am</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>3:54</v>
       </c>
       <c r="H117" t="str">
-        <v>Luke Combs</v>
+        <v>Bleachers</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L117" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>you and forever</v>
+        <v>ROOMS</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>everyone for ten minutes</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:54</v>
+        <v>3:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Bleachers</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L118" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ROOMS</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>ROOMS - Single</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:52</v>
+        <v>3:16</v>
       </c>
       <c r="H119" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L119" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G120" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H120" t="str">
-        <v>Bruno Mars</v>
+        <v>Junior H</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L120" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:11</v>
+        <v>3:09</v>
       </c>
       <c r="H121" t="str">
-        <v>Junior H</v>
+        <v>Maluma</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L121" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Con el Corazón</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G122" t="str">
-        <v>3:09</v>
+        <v>3:26</v>
       </c>
       <c r="H122" t="str">
-        <v>Maluma</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L122" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Get In Girl</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Toy With Me</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G123" t="str">
-        <v>3:26</v>
+        <v>3:21</v>
       </c>
       <c r="H123" t="str">
-        <v>Meghan Trainor</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L123" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>London Foolishly</v>
+        <v>Thorns</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H124" t="str">
-        <v>Nick Jonas</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L124" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thorns</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Thorns - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G125" t="str">
-        <v>3:10</v>
+        <v>4:10</v>
       </c>
       <c r="H125" t="str">
-        <v>Jelly Roll</v>
+        <v>Flea</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L125" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Thinkin Bout You</v>
+        <v>JUICY</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Honora</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:10</v>
+        <v>3:31</v>
       </c>
       <c r="H126" t="str">
-        <v>Flea</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L126" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>JUICY</v>
+        <v>All They Type</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>JUICY - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:31</v>
+        <v>2:52</v>
       </c>
       <c r="H127" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L127" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>All They Type</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>All They Type - Single</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:52</v>
+        <v>4:05</v>
       </c>
       <c r="H128" t="str">
-        <v>Keke Palmer</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L128" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>More Than A Lover</v>
+        <v>City</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>My Lover</v>
       </c>
       <c r="G129" t="str">
-        <v>4:05</v>
+        <v>3:16</v>
       </c>
       <c r="H129" t="str">
-        <v>Mary J. Blige</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L129" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>City</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>My Lover</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G130" t="str">
-        <v>3:16</v>
+        <v>2:25</v>
       </c>
       <c r="H130" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L130" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Eyes Closed</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:25</v>
+        <v>2:50</v>
       </c>
       <c r="H131" t="str">
-        <v>Mimi Webb</v>
+        <v>Knox</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L131" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Go For Broke</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Go For Broke - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>3:10</v>
       </c>
       <c r="H132" t="str">
-        <v>Knox</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L132" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:10</v>
+        <v>3:38</v>
       </c>
       <c r="H133" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L133" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Kentucky Too Long</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:38</v>
+        <v>2:57</v>
       </c>
       <c r="H134" t="str">
-        <v>Charley Crockett</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L134" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:57</v>
+        <v>2:58</v>
       </c>
       <c r="H135" t="str">
-        <v>Mon Rovîa</v>
+        <v>IVE</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L135" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>BANG BANG</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>BANG BANG - Single</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:58</v>
+        <v>3:15</v>
       </c>
       <c r="H136" t="str">
-        <v>IVE</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L136" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G137" t="str">
-        <v>3:15</v>
+        <v>5:21</v>
       </c>
       <c r="H137" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>Don Broco</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L137" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Nightmare Tripping</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Nightmare Tripping</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>5:21</v>
+        <v>3:26</v>
       </c>
       <c r="H138" t="str">
-        <v>Don Broco</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L138" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>for your love</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:26</v>
+        <v>3:05</v>
       </c>
       <c r="H139" t="str">
-        <v>Knocked Loose</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L139" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>for your love</v>
+        <v>Somebody</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>for your love - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:05</v>
+        <v>3:23</v>
       </c>
       <c r="H140" t="str">
-        <v>Cruz Beckham</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L140" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Somebody</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Somebody - Single</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:23</v>
+        <v>1:55</v>
       </c>
       <c r="H141" t="str">
-        <v>Jamie Foxx</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L141" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>On and On</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G142" t="str">
-        <v>1:55</v>
+        <v>3:43</v>
       </c>
       <c r="H142" t="str">
-        <v>BKTHERULA</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L142" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>On and On</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Work of Heart</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G143" t="str">
-        <v>3:43</v>
+        <v>2:44</v>
       </c>
       <c r="H143" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L143" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Push My Luck</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>2:44</v>
+        <v>2:46</v>
       </c>
       <c r="H144" t="str">
-        <v>Cold War Kids</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L144" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Memphis Players</v>
+        <v>Somebody</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G145" t="str">
-        <v>2:46</v>
+        <v>2:49</v>
       </c>
       <c r="H145" t="str">
-        <v>Anish Kumar</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L145" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Somebody</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:49</v>
+        <v>3:28</v>
       </c>
       <c r="H146" t="str">
-        <v>Good Neighbours</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L146" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L147" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Seven Seas</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Seven Seas - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G148" t="str">
-        <v>3:01</v>
+        <v>4:04</v>
       </c>
       <c r="H148" t="str">
-        <v>Dirty Heads</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L148" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>1000 Ways</v>
+        <v>Beatback</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>A Love For Strangers</v>
+        <v>Ö</v>
       </c>
       <c r="G149" t="str">
-        <v>4:04</v>
+        <v>2:19</v>
       </c>
       <c r="H149" t="str">
-        <v>Chet Faker</v>
+        <v>Fcukers</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L149" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Beatback</v>
+        <v>GANG</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ö</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:19</v>
+        <v>3:44</v>
       </c>
       <c r="H150" t="str">
-        <v>Fcukers</v>
+        <v>Tink</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L150" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>GANG</v>
+        <v>a love song for u</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>GANG - Single</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>3:44</v>
+        <v>1:40</v>
       </c>
       <c r="H151" t="str">
-        <v>Tink</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L151" t="str">
-        <v>GANG - Tink</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>a love song for u</v>
+        <v>See Through</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>a love song for u - EP</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G152" t="str">
-        <v>1:40</v>
+        <v>2:38</v>
       </c>
       <c r="H152" t="str">
-        <v>Eem Triplin</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L152" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>See Through</v>
+        <v>be the girl!</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G153" t="str">
-        <v>2:38</v>
+        <v>5:33</v>
       </c>
       <c r="H153" t="str">
-        <v>Story of the Year</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L153" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>be the girl!</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>the apple tree under the sea</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>5:33</v>
+        <v>3:33</v>
       </c>
       <c r="H154" t="str">
-        <v>hemlocke springs</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L154" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:33</v>
+        <v>3:40</v>
       </c>
       <c r="H155" t="str">
-        <v>Erin LeCount</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L155" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>ARCADE</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:40</v>
+        <v>2:52</v>
       </c>
       <c r="H156" t="str">
-        <v>Kid Sistr</v>
+        <v>Deb Never</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L156" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>ARCADE</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>ARCADE - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>2:52</v>
+        <v>2:16</v>
       </c>
       <c r="H157" t="str">
-        <v>Deb Never</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L157" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Girls Just Wanna</v>
+        <v>you special.</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Girlhood - EP</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:16</v>
+        <v>2:08</v>
       </c>
       <c r="H158" t="str">
-        <v>Morgan St. Jean</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L158" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>you special.</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>you special. - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:08</v>
+        <v>3:38</v>
       </c>
       <c r="H159" t="str">
-        <v>YFN Lucci</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L159" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Bass Dhol</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:38</v>
+        <v>3:31</v>
       </c>
       <c r="H160" t="str">
-        <v>Ahadadream</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L160" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:31</v>
+        <v>2:43</v>
       </c>
       <c r="H161" t="str">
-        <v>Charles Kelley</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L161" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>If I See Her Again</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G162" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Maddox Batson</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L162" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>To B Honest</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Under The Sun</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G163" t="str">
-        <v>4:43</v>
+        <v>4:30</v>
       </c>
       <c r="H163" t="str">
-        <v>Sun-El Musician</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L163" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>To B Honest</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>To Whom This May Concern</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G164" t="str">
-        <v>4:30</v>
+        <v>2:41</v>
       </c>
       <c r="H164" t="str">
-        <v>Jill Scott</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L164" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>lil xan goes to washington</v>
+        <v>Koneko</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>the beltway is burning</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:41</v>
+        <v>4:08</v>
       </c>
       <c r="H165" t="str">
-        <v>Ekko Astral</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L165" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Koneko</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Kurage - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:08</v>
+        <v>2:58</v>
       </c>
       <c r="H166" t="str">
-        <v>Liana Flores</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L166" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Cupid's Call</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:58</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>Dizzy Fae</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L167" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Pop Off</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:13</v>
+        <v>3:16</v>
       </c>
       <c r="H168" t="str">
-        <v>Chloé Caillet</v>
+        <v>GRiZ</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L168" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Pop Off</v>
+        <v>dreams</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Pop Off - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:16</v>
+        <v>3:31</v>
       </c>
       <c r="H169" t="str">
-        <v>GRiZ</v>
+        <v>Azzecca</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L169" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>dreams</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>dreams - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:31</v>
+        <v>2:55</v>
       </c>
       <c r="H170" t="str">
-        <v>Azzecca</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L170" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Love Hate Love</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:55</v>
+        <v>2:52</v>
       </c>
       <c r="H171" t="str">
-        <v>Owen Riegling</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L171" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Do It All Alone</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G172" t="str">
-        <v>2:52</v>
+        <v>2:58</v>
       </c>
       <c r="H172" t="str">
-        <v>Rend Collective</v>
+        <v>Cardinals</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L172" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>She Makes Me Real</v>
+        <v>Steady</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Masquerade</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:58</v>
+        <v>3:26</v>
       </c>
       <c r="H173" t="str">
-        <v>Cardinals</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L173" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Steady</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G174" t="str">
-        <v>3:26</v>
+        <v>2:20</v>
       </c>
       <c r="H174" t="str">
-        <v>Bella Kay</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L174" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>DIRTY TECH</v>
+        <v>Nada Más</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>PLAY ME</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:20</v>
+        <v>2:19</v>
       </c>
       <c r="H175" t="str">
-        <v>Kim Gordon</v>
+        <v>Tombochio</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L175" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Nada Más</v>
+        <v>Friends Again</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Nada Más - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:19</v>
+        <v>3:38</v>
       </c>
       <c r="H176" t="str">
-        <v>Tombochio</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L176" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Friends Again</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Friends Again - Single</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:38</v>
+        <v>3:22</v>
       </c>
       <c r="H177" t="str">
-        <v>Baby Rose</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L177" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>W.T.A.</v>
+        <v>desire.</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>W.T.A. - Single</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G178" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H178" t="str">
-        <v>Isaia Huron</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L178" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>desire.</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>November Scorpio</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G179" t="str">
-        <v>3:15</v>
+        <v>3:12</v>
       </c>
       <c r="H179" t="str">
-        <v>Tiana Major9</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L179" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:12</v>
+        <v>4:00</v>
       </c>
       <c r="H180" t="str">
-        <v>August Ponthier</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L180" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Killer Whale</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Killer Whale - Single</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G181" t="str">
-        <v>4:00</v>
+        <v>2:46</v>
       </c>
       <c r="H181" t="str">
-        <v>Hayden Everett</v>
+        <v>Anjimile</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L181" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Waits for Me</v>
+        <v>Man's World</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>You’re Free to Go</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G182" t="str">
-        <v>2:46</v>
+        <v>2:42</v>
       </c>
       <c r="H182" t="str">
-        <v>Anjimile</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L182" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Man's World</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Mud Blood Bone</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:42</v>
+        <v>3:13</v>
       </c>
       <c r="H183" t="str">
-        <v>Cat Clyde</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L183" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>In the Middle of It</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>3:13</v>
+        <v>2:51</v>
       </c>
       <c r="H184" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L184" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Fleeting - EP</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:51</v>
+        <v>5:23</v>
       </c>
       <c r="H185" t="str">
-        <v>Sarah Kinsley</v>
+        <v>BUNT.</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L185" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>5:23</v>
+        <v>3:07</v>
       </c>
       <c r="H186" t="str">
-        <v>BUNT.</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L186" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>I've Never Met Her</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>The Elephant</v>
       </c>
       <c r="G187" t="str">
-        <v>3:07</v>
+        <v>3:28</v>
       </c>
       <c r="H187" t="str">
-        <v>Ally Salort</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L187" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>Yes</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>The Elephant</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G188" t="str">
-        <v>3:28</v>
+        <v>3:21</v>
       </c>
       <c r="H188" t="str">
-        <v>Ledbyher</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L188" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Yes</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Just A Few Folk</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:21</v>
+        <v>2:52</v>
       </c>
       <c r="H189" t="str">
-        <v>JP Cooper</v>
+        <v>WesGhost</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L189" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G190" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H190" t="str">
-        <v>WesGhost</v>
+        <v>Converge</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L190" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Bad Faith</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Love Is Not Enough</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G191" t="str">
-        <v>2:48</v>
+        <v>4:00</v>
       </c>
       <c r="H191" t="str">
-        <v>Converge</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L191" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Angel Eyes</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-16</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Good God / Baad Man</v>
+        <v>God Forgives - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:00</v>
+        <v>2:14</v>
       </c>
       <c r="H192" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Guilt Trip</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
       </c>
       <c r="L192" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Angel Eyes - Guilt Trip</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Angel Eyes</v>
+        <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-16</v>
@@ -7709,68 +7709,30 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>God Forgives - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G193" t="str">
-        <v>2:14</v>
+        <v>3:17</v>
       </c>
       <c r="H193" t="str">
-        <v>Guilt Trip</v>
+        <v>Melvins</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
       <c r="L193" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>Tossing Coins Into The Fountain Of F**k</v>
-      </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
-      </c>
-      <c r="D194" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G194" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H194" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I194" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
-      </c>
-      <c r="L194" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>פטרושקה – גלוחי העורף</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%95%d7%a9%d7%a7%d7%94-%d7%92%d7%9c%d7%95%d7%97%d7%99-%d7%94%d7%a2%d7%95%d7%a8%d7%a3/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>"גלוחי העורף" של עידו פטרושקה הוא שיר עירוני לא “על העיר” אלא מתוכה.. אין כאן עמדה מוסרית ברורה, אין פתרון, אין סיפור שלם. יש אוסף מבטים קצרים, כמעט תיעודיים, שמרחפים בין חמלה לאדישות. הקול המחוספס והמקצב  הסימטרי יוצרים תחושת הליכה</v>
       </c>
       <c r="G2" t="str">
-        <v>5:31</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>פטרושקה – גלוחי העורף</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-16</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:49</v>
+        <v>5:31</v>
       </c>
       <c r="H3" t="str">
-        <v>Mýa</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-16</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:03</v>
+        <v>2:49</v>
       </c>
       <c r="H4" t="str">
-        <v>Michael Bolton</v>
+        <v>Mýa</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-16</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:59</v>
+        <v>3:03</v>
       </c>
       <c r="H5" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-16</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H6" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-16</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H7" t="str">
-        <v>ENHYPEN</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-16</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H8" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>7:48</v>
+        <v>3:59</v>
       </c>
       <c r="H9" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-16</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:10</v>
+        <v>7:48</v>
       </c>
       <c r="H10" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-16</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>5:57</v>
+        <v>3:10</v>
       </c>
       <c r="H11" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-16</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:25</v>
+        <v>5:57</v>
       </c>
       <c r="H12" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-16</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:19</v>
+        <v>2:25</v>
       </c>
       <c r="H13" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-16</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:38</v>
+        <v>3:19</v>
       </c>
       <c r="H14" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-16</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:05</v>
+        <v>3:38</v>
       </c>
       <c r="H15" t="str">
-        <v>Dermot Kennedy</v>
+        <v>mgk</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-16</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>5:46</v>
+        <v>4:05</v>
       </c>
       <c r="H16" t="str">
-        <v>Jacob Collier</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-16</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:25</v>
+        <v>5:46</v>
       </c>
       <c r="H17" t="str">
-        <v>Victor Ray</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-16</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:11</v>
+        <v>3:25</v>
       </c>
       <c r="H18" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-16</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:55</v>
+        <v>5:11</v>
       </c>
       <c r="H19" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-16</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:54</v>
+        <v>2:55</v>
       </c>
       <c r="H20" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-16</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:01</v>
+        <v>4:54</v>
       </c>
       <c r="H21" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Offspring</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-16</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:55</v>
+        <v>5:01</v>
       </c>
       <c r="H22" t="str">
-        <v>HAUSER</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-16</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H23" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>HAUSER</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Jillian Jacquline - Another Lover (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H24" t="str">
-        <v>Ultra Records</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:30</v>
+        <v>2:53</v>
       </c>
       <c r="H25" t="str">
-        <v>Anja Kotar</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-16</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:37</v>
+        <v>3:30</v>
       </c>
       <c r="H26" t="str">
-        <v>Michael Bolton</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-16</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H27" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-16</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:06</v>
+        <v>4:10</v>
       </c>
       <c r="H28" t="str">
-        <v>Alan Walker</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-16</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:17</v>
+        <v>3:06</v>
       </c>
       <c r="H29" t="str">
-        <v>Bruno Mars</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-16</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H30" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-16</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>6:58</v>
+        <v>3:21</v>
       </c>
       <c r="H31" t="str">
-        <v>Eric Church</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-16</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:29</v>
+        <v>6:58</v>
       </c>
       <c r="H32" t="str">
-        <v>Meghan Trainor</v>
+        <v>Eric Church</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-16</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H33" t="str">
-        <v>Ally Salort</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-16</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:51</v>
+        <v>3:14</v>
       </c>
       <c r="H34" t="str">
-        <v>Will Swinton</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-16</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:10</v>
+        <v>3:51</v>
       </c>
       <c r="H35" t="str">
-        <v>elijah woods</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-16</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="H36" t="str">
-        <v>Jackson Dean</v>
+        <v>elijah woods</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-16</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H37" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-16</v>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H38" t="str">
-        <v>Neil Sedaka</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-16</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H39" t="str">
-        <v>Sofia Camara</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-16</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:04</v>
+        <v>3:06</v>
       </c>
       <c r="H40" t="str">
-        <v>Russell Dickerson</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-16</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H41" t="str">
-        <v>Celine Dion</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-16</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:38</v>
+        <v>3:03</v>
       </c>
       <c r="H42" t="str">
-        <v>Bebe Rexha</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-16</v>
@@ -2012,10 +2012,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:29</v>
+        <v>2:38</v>
       </c>
       <c r="H43" t="str">
-        <v>Caroline Jones</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-16</v>
@@ -2050,10 +2050,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:32</v>
+        <v>3:29</v>
       </c>
       <c r="H44" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-16</v>
@@ -2088,10 +2088,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>2:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Ingrid Andress</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-16</v>
@@ -2126,10 +2126,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:51</v>
+        <v>3:32</v>
       </c>
       <c r="H46" t="str">
-        <v>MusicByKnox</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B47" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-16</v>
@@ -2164,10 +2164,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H47" t="str">
-        <v>Ella Langley</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B48" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-16</v>
@@ -2202,10 +2202,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:26</v>
+        <v>3:38</v>
       </c>
       <c r="H48" t="str">
-        <v>Nickless</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B49" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-16</v>
@@ -2240,10 +2240,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:57</v>
+        <v>3:26</v>
       </c>
       <c r="H49" t="str">
-        <v>Caroline Jones</v>
+        <v>Nickless</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-16</v>
@@ -2278,10 +2278,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:08</v>
+        <v>3:57</v>
       </c>
       <c r="H50" t="str">
-        <v>elijah woods</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-16</v>
@@ -2316,10 +2316,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:53</v>
+        <v>3:08</v>
       </c>
       <c r="H51" t="str">
-        <v>August Ponthier</v>
+        <v>elijah woods</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B52" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-16</v>
@@ -2354,10 +2354,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:10</v>
+        <v>3:53</v>
       </c>
       <c r="H52" t="str">
-        <v>Charli xcx</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-16</v>
@@ -2392,10 +2392,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:58</v>
+        <v>3:10</v>
       </c>
       <c r="H53" t="str">
-        <v>Caroline Jones</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-16</v>
@@ -2430,10 +2430,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:44</v>
+        <v>2:58</v>
       </c>
       <c r="H54" t="str">
-        <v>Leah Kate</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-16</v>
@@ -2468,10 +2468,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:25</v>
+        <v>2:44</v>
       </c>
       <c r="H55" t="str">
-        <v>Troye Sivan</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-16</v>
@@ -2506,10 +2506,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:08</v>
+        <v>3:25</v>
       </c>
       <c r="H56" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-16</v>
@@ -2544,10 +2544,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:09</v>
+        <v>4:08</v>
       </c>
       <c r="H57" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B58" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-16</v>
@@ -2582,10 +2582,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:11</v>
+        <v>3:09</v>
       </c>
       <c r="H58" t="str">
-        <v>The Happy Fits</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-16</v>
@@ -2620,10 +2620,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:02</v>
+        <v>3:11</v>
       </c>
       <c r="H59" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B60" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-16</v>
@@ -2658,10 +2658,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:20</v>
+        <v>3:02</v>
       </c>
       <c r="H60" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B61" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-16</v>
@@ -2696,10 +2696,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:09</v>
+        <v>4:20</v>
       </c>
       <c r="H61" t="str">
-        <v>Quinn XCII</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B62" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-16</v>
@@ -2734,10 +2734,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:34</v>
+        <v>4:09</v>
       </c>
       <c r="H62" t="str">
-        <v>We Three</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B63" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-16</v>
@@ -2772,10 +2772,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:29</v>
+        <v>4:34</v>
       </c>
       <c r="H63" t="str">
-        <v>A Thousand Horses</v>
+        <v>We Three</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B64" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-16</v>
@@ -2810,10 +2810,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:51</v>
+        <v>3:29</v>
       </c>
       <c r="H64" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B65" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-16</v>
@@ -2848,10 +2848,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:56</v>
+        <v>2:51</v>
       </c>
       <c r="H65" t="str">
-        <v>Constant Smiles</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-16</v>
@@ -2886,10 +2886,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:25</v>
+        <v>2:56</v>
       </c>
       <c r="H66" t="str">
-        <v>P!NK</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-16</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:33</v>
+        <v>3:25</v>
       </c>
       <c r="H67" t="str">
-        <v>Bazzi</v>
+        <v>P!NK</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-16</v>
@@ -2962,10 +2962,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:18</v>
+        <v>2:33</v>
       </c>
       <c r="H68" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bazzi</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B69" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-16</v>
@@ -3000,7 +3000,7 @@
         <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:08</v>
+        <v>4:18</v>
       </c>
       <c r="H69" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B70" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-16</v>
@@ -3038,10 +3038,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:56</v>
+        <v>2:08</v>
       </c>
       <c r="H70" t="str">
-        <v>bleachers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-16</v>
@@ -3076,10 +3076,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:27</v>
+        <v>3:56</v>
       </c>
       <c r="H71" t="str">
-        <v>The Academic</v>
+        <v>bleachers</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-16</v>
@@ -3114,10 +3114,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:39</v>
+        <v>3:27</v>
       </c>
       <c r="H72" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Academic</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B73" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-16</v>
@@ -3152,10 +3152,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:54</v>
+        <v>2:39</v>
       </c>
       <c r="H73" t="str">
-        <v>Michael Bolton</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-16</v>
@@ -3190,10 +3190,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:47</v>
+        <v>3:54</v>
       </c>
       <c r="H74" t="str">
-        <v>Caroline Jones</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B75" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-16</v>
@@ -3228,10 +3228,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:07</v>
+        <v>3:47</v>
       </c>
       <c r="H75" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B76" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-16</v>
@@ -3266,10 +3266,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:00</v>
+        <v>4:07</v>
       </c>
       <c r="H76" t="str">
-        <v>Michael Bolton</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B77" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-16</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:27</v>
+        <v>5:00</v>
       </c>
       <c r="H77" t="str">
-        <v>Little Big Town</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B78" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-16</v>
@@ -3342,10 +3342,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H78" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-16</v>
@@ -3380,10 +3380,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>10:57</v>
+        <v>3:25</v>
       </c>
       <c r="H79" t="str">
-        <v>JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B80" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-16</v>
@@ -3418,10 +3418,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:14</v>
+        <v>10:57</v>
       </c>
       <c r="H80" t="str">
-        <v>Robert Grace</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B81" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-16</v>
@@ -3456,10 +3456,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:26</v>
+        <v>4:14</v>
       </c>
       <c r="H81" t="str">
-        <v>mgk</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-16</v>
@@ -3494,10 +3494,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:59</v>
+        <v>3:26</v>
       </c>
       <c r="H82" t="str">
-        <v>Victor Ray</v>
+        <v>mgk</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B83" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:46</v>
+        <v>5:59</v>
       </c>
       <c r="H83" t="str">
-        <v>Perrie</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-16</v>
@@ -3570,10 +3570,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:39</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Michael Bolton</v>
+        <v>Perrie</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B85" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-16</v>
@@ -3608,10 +3608,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:58</v>
+        <v>3:39</v>
       </c>
       <c r="H85" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B86" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:26</v>
+        <v>3:58</v>
       </c>
       <c r="H86" t="str">
-        <v>Mimi Webb</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-16</v>
@@ -3684,10 +3684,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:04</v>
+        <v>2:26</v>
       </c>
       <c r="H87" t="str">
-        <v>Olivia Dean</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B88" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-16</v>
@@ -3722,10 +3722,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>6:00</v>
+        <v>3:04</v>
       </c>
       <c r="H88" t="str">
-        <v>Taylor Swift</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-16</v>
@@ -3760,10 +3760,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:20</v>
+        <v>6:00</v>
       </c>
       <c r="H89" t="str">
-        <v>Michael Bolton</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-16</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:27</v>
+        <v>4:20</v>
       </c>
       <c r="H90" t="str">
-        <v>Mariah Carey</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B91" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-16</v>
@@ -3836,10 +3836,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:26</v>
+        <v>4:27</v>
       </c>
       <c r="H91" t="str">
-        <v>Netflix</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B92" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-16</v>
@@ -3874,10 +3874,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H92" t="str">
-        <v>Michael Bolton</v>
+        <v>Netflix</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-16</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H93" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-16</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:51</v>
+        <v>2:59</v>
       </c>
       <c r="H94" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>mgk</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B95" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-16</v>
@@ -3988,10 +3988,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:13</v>
+        <v>2:51</v>
       </c>
       <c r="H95" t="str">
-        <v>Michael Bolton</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B96" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-16</v>
@@ -4026,10 +4026,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:41</v>
+        <v>4:13</v>
       </c>
       <c r="H96" t="str">
-        <v>NICK JONAS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B97" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-16</v>
@@ -4064,10 +4064,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>7:03</v>
+        <v>4:41</v>
       </c>
       <c r="H97" t="str">
-        <v>Take That</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B98" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-16</v>
@@ -4102,10 +4102,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:37</v>
+        <v>7:03</v>
       </c>
       <c r="H98" t="str">
-        <v>Cliff Richard</v>
+        <v>Take That</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-16</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:54</v>
+        <v>4:37</v>
       </c>
       <c r="H99" t="str">
-        <v>Bryan Adams</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-16</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:06</v>
+        <v>3:54</v>
       </c>
       <c r="H100" t="str">
-        <v>Anna Graves</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-16</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H101" t="str">
-        <v>George Birge</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Always Everywhere</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Wuthering Heights</v>
+        <v>10 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H102" t="str">
-        <v>Charli xcx</v>
+        <v>George Birge</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Be Her</v>
+        <v>Always Everywhere</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Dandelion</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="G103" t="str">
-        <v>3:37</v>
+        <v>3:03</v>
       </c>
       <c r="H103" t="str">
-        <v>Ella Langley</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
       </c>
       <c r="L103" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>Always Everywhere - Charli xcx</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>other side.</v>
+        <v>Be Her</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Icon</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>3:15</v>
+        <v>3:37</v>
       </c>
       <c r="H104" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SHADOWS</v>
+        <v>other side.</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>SHADOWS - Single</v>
+        <v>Icon</v>
       </c>
       <c r="G105" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H105" t="str">
-        <v>John Summit</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L105" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:00</v>
+        <v>3:22</v>
       </c>
       <c r="H106" t="str">
-        <v>CORTIS</v>
+        <v>John Summit</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L106" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Trying Times</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G107" t="str">
-        <v>3:40</v>
+        <v>3:00</v>
       </c>
       <c r="H107" t="str">
-        <v>James Blake</v>
+        <v>CORTIS</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L107" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Let Me</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Let Me - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G108" t="str">
-        <v>4:51</v>
+        <v>3:40</v>
       </c>
       <c r="H108" t="str">
-        <v>Victoria Monét</v>
+        <v>James Blake</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L108" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H109" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L109" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H110" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L110" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G111" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H111" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L111" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H112" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L112" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H113" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L113" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H114" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L114" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H115" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L115" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G116" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H116" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L116" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G117" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L117" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G118" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H118" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L118" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H119" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L119" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H120" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L120" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G121" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H121" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L121" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H122" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L122" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G123" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H123" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L123" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G124" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H124" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L124" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H125" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L125" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G126" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H126" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L126" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H127" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L127" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H128" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L128" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L129" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G130" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H130" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L130" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G131" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H131" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L131" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L132" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G133" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H133" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L133" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H134" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L134" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H135" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L135" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H137" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L137" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G138" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H138" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L138" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H139" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L139" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H140" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L140" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H141" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L141" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H142" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L142" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G143" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H143" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L143" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H144" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L144" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G145" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H145" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L145" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G146" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H146" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L146" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H147" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L147" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L148" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G149" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H149" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L149" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G150" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H150" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L150" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H151" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L151" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H152" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L152" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G153" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H153" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L153" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G154" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H154" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L154" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H155" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L155" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H156" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L156" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H157" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L157" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H158" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L158" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H159" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L159" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H160" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L160" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H161" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L161" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L162" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G163" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L163" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G164" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H164" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L164" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G165" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H165" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L165" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H166" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L166" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H167" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L167" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L168" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H169" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L169" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H170" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L170" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H171" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L171" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H172" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L172" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G173" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H173" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L173" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H174" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L174" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G175" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H175" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L175" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H176" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L176" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H177" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L177" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L178" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G179" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H179" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L179" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G180" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H180" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L180" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H181" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L181" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G182" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H182" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L182" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G183" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H183" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L183" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H184" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L184" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H185" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L185" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H186" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L186" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H187" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L187" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G188" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H188" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L188" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G189" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H189" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L189" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H190" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L190" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G191" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H191" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L191" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-16</v>
@@ -7671,68 +7671,106 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G192" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H192" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L192" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B193" t="str">
+        <v/>
+      </c>
+      <c r="C193" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G193" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H193" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I193" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J193" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K193" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B193" t="str">
-        <v/>
-      </c>
-      <c r="C193" t="str">
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D193" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
+      <c r="D194" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G193" t="str">
+      <c r="G194" t="str">
         <v>3:17</v>
       </c>
-      <c r="H193" t="str">
+      <c r="H194" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I193" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J193" t="str">
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K193" t="str">
+      <c r="K194" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L193" t="str">
+      <c r="L194" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פטרושקה – גלוחי העורף</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-16</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%95%d7%a9%d7%a7%d7%94-%d7%92%d7%9c%d7%95%d7%97%d7%99-%d7%94%d7%a2%d7%95%d7%a8%d7%a3/</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"גלוחי העורף" של עידו פטרושקה הוא שיר עירוני לא “על העיר” אלא מתוכה.. אין כאן עמדה מוסרית ברורה, אין פתרון, אין סיפור שלם. יש אוסף מבטים קצרים, כמעט תיעודיים, שמרחפים בין חמלה לאדישות. הקול המחוספס והמקצב  הסימטרי יוצרים תחושת הליכה</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>5:31</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פטרושקה – גלוחי העורף</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-16</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>5:31</v>
+        <v>2:49</v>
       </c>
       <c r="H3" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Mýa</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-16</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:49</v>
+        <v>3:03</v>
       </c>
       <c r="H4" t="str">
-        <v>Mýa</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-16</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:03</v>
+        <v>2:59</v>
       </c>
       <c r="H5" t="str">
-        <v>Michael Bolton</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-16</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H6" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-16</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H7" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-16</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:59</v>
+        <v>3:59</v>
       </c>
       <c r="H8" t="str">
-        <v>ENHYPEN</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:59</v>
+        <v>7:48</v>
       </c>
       <c r="H9" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-16</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>7:48</v>
+        <v>3:10</v>
       </c>
       <c r="H10" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-16</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:10</v>
+        <v>5:57</v>
       </c>
       <c r="H11" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-16</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:57</v>
+        <v>2:25</v>
       </c>
       <c r="H12" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-16</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:25</v>
+        <v>3:19</v>
       </c>
       <c r="H13" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-16</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:19</v>
+        <v>3:38</v>
       </c>
       <c r="H14" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-16</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:38</v>
+        <v>4:05</v>
       </c>
       <c r="H15" t="str">
-        <v>mgk</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-16</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:05</v>
+        <v>5:46</v>
       </c>
       <c r="H16" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-16</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>5:46</v>
+        <v>3:25</v>
       </c>
       <c r="H17" t="str">
-        <v>Jacob Collier</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-16</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:25</v>
+        <v>5:11</v>
       </c>
       <c r="H18" t="str">
-        <v>Victor Ray</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-16</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>5:11</v>
+        <v>2:55</v>
       </c>
       <c r="H19" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>The Warning</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-16</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:55</v>
+        <v>4:54</v>
       </c>
       <c r="H20" t="str">
-        <v>The Warning</v>
+        <v>The Offspring</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-16</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:54</v>
+        <v>5:01</v>
       </c>
       <c r="H21" t="str">
-        <v>The Offspring</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-16</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:01</v>
+        <v>3:55</v>
       </c>
       <c r="H22" t="str">
-        <v>Caitlyn Smith</v>
+        <v>HAUSER</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Jillian Jacquline - Another Lover (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-16</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:55</v>
+        <v>3:43</v>
       </c>
       <c r="H23" t="str">
-        <v>HAUSER</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H24" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:53</v>
+        <v>3:30</v>
       </c>
       <c r="H25" t="str">
-        <v>Ultra Records</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:30</v>
+        <v>3:37</v>
       </c>
       <c r="H26" t="str">
-        <v>Anja Kotar</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-16</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:37</v>
+        <v>4:10</v>
       </c>
       <c r="H27" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-16</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:10</v>
+        <v>3:06</v>
       </c>
       <c r="H28" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-16</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H29" t="str">
-        <v>Alan Walker</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-16</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H30" t="str">
-        <v>Bruno Mars</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-16</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:21</v>
+        <v>6:58</v>
       </c>
       <c r="H31" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Eric Church</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-16</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>6:58</v>
+        <v>3:29</v>
       </c>
       <c r="H32" t="str">
-        <v>Eric Church</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-16</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:29</v>
+        <v>3:14</v>
       </c>
       <c r="H33" t="str">
-        <v>Meghan Trainor</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-16</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:14</v>
+        <v>3:51</v>
       </c>
       <c r="H34" t="str">
-        <v>Ally Salort</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-16</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:51</v>
+        <v>3:10</v>
       </c>
       <c r="H35" t="str">
-        <v>Will Swinton</v>
+        <v>elijah woods</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-16</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:10</v>
+        <v>3:26</v>
       </c>
       <c r="H36" t="str">
-        <v>elijah woods</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-16</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H37" t="str">
-        <v>Jackson Dean</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-16</v>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H38" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-16</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H39" t="str">
-        <v>Neil Sedaka</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-16</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:06</v>
+        <v>3:04</v>
       </c>
       <c r="H40" t="str">
-        <v>Sofia Camara</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-16</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H41" t="str">
-        <v>Russell Dickerson</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-16</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:03</v>
+        <v>2:38</v>
       </c>
       <c r="H42" t="str">
-        <v>Celine Dion</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-16</v>
@@ -2012,10 +2012,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:38</v>
+        <v>3:29</v>
       </c>
       <c r="H43" t="str">
-        <v>Bebe Rexha</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-16</v>
@@ -2050,10 +2050,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:29</v>
+        <v>2:32</v>
       </c>
       <c r="H44" t="str">
-        <v>Caroline Jones</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-16</v>
@@ -2088,10 +2088,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:32</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-16</v>
@@ -2126,10 +2126,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:32</v>
+        <v>2:51</v>
       </c>
       <c r="H46" t="str">
-        <v>Ingrid Andress</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-16</v>
@@ -2164,10 +2164,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:51</v>
+        <v>3:38</v>
       </c>
       <c r="H47" t="str">
-        <v>MusicByKnox</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B48" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-16</v>
@@ -2202,10 +2202,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H48" t="str">
-        <v>Ella Langley</v>
+        <v>Nickless</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-16</v>
@@ -2240,10 +2240,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:26</v>
+        <v>3:57</v>
       </c>
       <c r="H49" t="str">
-        <v>Nickless</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-16</v>
@@ -2278,10 +2278,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:57</v>
+        <v>3:08</v>
       </c>
       <c r="H50" t="str">
-        <v>Caroline Jones</v>
+        <v>elijah woods</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-16</v>
@@ -2316,10 +2316,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:08</v>
+        <v>3:53</v>
       </c>
       <c r="H51" t="str">
-        <v>elijah woods</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-16</v>
@@ -2354,10 +2354,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:53</v>
+        <v>3:10</v>
       </c>
       <c r="H52" t="str">
-        <v>August Ponthier</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-16</v>
@@ -2392,10 +2392,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:10</v>
+        <v>2:58</v>
       </c>
       <c r="H53" t="str">
-        <v>Charli xcx</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-16</v>
@@ -2430,10 +2430,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:58</v>
+        <v>2:44</v>
       </c>
       <c r="H54" t="str">
-        <v>Caroline Jones</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-16</v>
@@ -2468,10 +2468,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:44</v>
+        <v>3:25</v>
       </c>
       <c r="H55" t="str">
-        <v>Leah Kate</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-16</v>
@@ -2506,10 +2506,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:25</v>
+        <v>4:08</v>
       </c>
       <c r="H56" t="str">
-        <v>Troye Sivan</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B57" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-16</v>
@@ -2544,10 +2544,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:08</v>
+        <v>3:09</v>
       </c>
       <c r="H57" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-16</v>
@@ -2582,10 +2582,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H58" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B59" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-16</v>
@@ -2620,10 +2620,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:11</v>
+        <v>3:02</v>
       </c>
       <c r="H59" t="str">
-        <v>The Happy Fits</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B60" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-16</v>
@@ -2658,10 +2658,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:02</v>
+        <v>4:20</v>
       </c>
       <c r="H60" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B61" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-16</v>
@@ -2696,10 +2696,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:20</v>
+        <v>4:09</v>
       </c>
       <c r="H61" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B62" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-16</v>
@@ -2734,10 +2734,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:09</v>
+        <v>4:34</v>
       </c>
       <c r="H62" t="str">
-        <v>Quinn XCII</v>
+        <v>We Three</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B63" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-16</v>
@@ -2772,10 +2772,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:34</v>
+        <v>3:29</v>
       </c>
       <c r="H63" t="str">
-        <v>We Three</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B64" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-16</v>
@@ -2810,10 +2810,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:29</v>
+        <v>2:51</v>
       </c>
       <c r="H64" t="str">
-        <v>A Thousand Horses</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-16</v>
@@ -2848,10 +2848,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H65" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B66" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-16</v>
@@ -2886,10 +2886,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:56</v>
+        <v>3:25</v>
       </c>
       <c r="H66" t="str">
-        <v>Constant Smiles</v>
+        <v>P!NK</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-16</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:25</v>
+        <v>2:33</v>
       </c>
       <c r="H67" t="str">
-        <v>P!NK</v>
+        <v>Bazzi</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B68" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-16</v>
@@ -2962,10 +2962,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:33</v>
+        <v>4:18</v>
       </c>
       <c r="H68" t="str">
-        <v>Bazzi</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B69" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-16</v>
@@ -3000,7 +3000,7 @@
         <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:18</v>
+        <v>2:08</v>
       </c>
       <c r="H69" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-16</v>
@@ -3038,10 +3038,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:08</v>
+        <v>3:56</v>
       </c>
       <c r="H70" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>bleachers</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-16</v>
@@ -3076,10 +3076,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:56</v>
+        <v>3:27</v>
       </c>
       <c r="H71" t="str">
-        <v>bleachers</v>
+        <v>The Academic</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-16</v>
@@ -3114,10 +3114,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:27</v>
+        <v>2:39</v>
       </c>
       <c r="H72" t="str">
-        <v>The Academic</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B73" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-16</v>
@@ -3152,10 +3152,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:39</v>
+        <v>3:54</v>
       </c>
       <c r="H73" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B74" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-16</v>
@@ -3190,10 +3190,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:54</v>
+        <v>3:47</v>
       </c>
       <c r="H74" t="str">
-        <v>Michael Bolton</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B75" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-16</v>
@@ -3228,10 +3228,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:47</v>
+        <v>4:07</v>
       </c>
       <c r="H75" t="str">
-        <v>Caroline Jones</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-16</v>
@@ -3266,10 +3266,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:07</v>
+        <v>5:00</v>
       </c>
       <c r="H76" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-16</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>5:00</v>
+        <v>3:27</v>
       </c>
       <c r="H77" t="str">
-        <v>Michael Bolton</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-16</v>
@@ -3342,10 +3342,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:27</v>
+        <v>3:25</v>
       </c>
       <c r="H78" t="str">
-        <v>Little Big Town</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B79" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-16</v>
@@ -3380,10 +3380,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:25</v>
+        <v>10:57</v>
       </c>
       <c r="H79" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B80" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-16</v>
@@ -3418,10 +3418,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>10:57</v>
+        <v>4:14</v>
       </c>
       <c r="H80" t="str">
-        <v>JavaJazzFest</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-16</v>
@@ -3456,10 +3456,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:14</v>
+        <v>3:26</v>
       </c>
       <c r="H81" t="str">
-        <v>Robert Grace</v>
+        <v>mgk</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B82" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-16</v>
@@ -3494,10 +3494,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:26</v>
+        <v>5:59</v>
       </c>
       <c r="H82" t="str">
-        <v>mgk</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>5:59</v>
+        <v>2:46</v>
       </c>
       <c r="H83" t="str">
-        <v>Victor Ray</v>
+        <v>Perrie</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-16</v>
@@ -3570,10 +3570,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:46</v>
+        <v>3:39</v>
       </c>
       <c r="H84" t="str">
-        <v>Perrie</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B85" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-16</v>
@@ -3608,10 +3608,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:39</v>
+        <v>3:58</v>
       </c>
       <c r="H85" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:58</v>
+        <v>2:26</v>
       </c>
       <c r="H86" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B87" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-16</v>
@@ -3684,10 +3684,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:26</v>
+        <v>3:04</v>
       </c>
       <c r="H87" t="str">
-        <v>Mimi Webb</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-16</v>
@@ -3722,10 +3722,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:04</v>
+        <v>6:00</v>
       </c>
       <c r="H88" t="str">
-        <v>Olivia Dean</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-16</v>
@@ -3760,10 +3760,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>6:00</v>
+        <v>4:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Taylor Swift</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B90" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-16</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:20</v>
+        <v>4:27</v>
       </c>
       <c r="H90" t="str">
-        <v>Michael Bolton</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B91" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-16</v>
@@ -3836,10 +3836,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:27</v>
+        <v>3:26</v>
       </c>
       <c r="H91" t="str">
-        <v>Mariah Carey</v>
+        <v>Netflix</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B92" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-16</v>
@@ -3874,10 +3874,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H92" t="str">
-        <v>Netflix</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-16</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:29</v>
+        <v>2:59</v>
       </c>
       <c r="H93" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-16</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:59</v>
+        <v>2:51</v>
       </c>
       <c r="H94" t="str">
-        <v>mgk</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-16</v>
@@ -3988,10 +3988,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:51</v>
+        <v>4:13</v>
       </c>
       <c r="H95" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B96" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-16</v>
@@ -4026,10 +4026,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:13</v>
+        <v>4:41</v>
       </c>
       <c r="H96" t="str">
-        <v>Michael Bolton</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B97" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-16</v>
@@ -4064,10 +4064,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:41</v>
+        <v>7:03</v>
       </c>
       <c r="H97" t="str">
-        <v>NICK JONAS</v>
+        <v>Take That</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B98" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-16</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>7:03</v>
+        <v>4:37</v>
       </c>
       <c r="H98" t="str">
-        <v>Take That</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-16</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:37</v>
+        <v>3:54</v>
       </c>
       <c r="H99" t="str">
-        <v>Cliff Richard</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-16</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:54</v>
+        <v>3:06</v>
       </c>
       <c r="H100" t="str">
-        <v>Bryan Adams</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-16</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H101" t="str">
-        <v>Anna Graves</v>
+        <v>George Birge</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Always Everywhere</v>
       </c>
       <c r="B102" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>10 days ago</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="G102" t="str">
-        <v>3:21</v>
+        <v>3:03</v>
       </c>
       <c r="H102" t="str">
-        <v>George Birge</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
       </c>
       <c r="L102" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Always Everywhere - Charli xcx</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Always Everywhere</v>
+        <v>Be Her</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Wuthering Heights</v>
+        <v>Dandelion</v>
       </c>
       <c r="G103" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H103" t="str">
-        <v>Charli xcx</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L103" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Be Her</v>
+        <v>other side.</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>Icon</v>
       </c>
       <c r="G104" t="str">
-        <v>3:37</v>
+        <v>3:15</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L104" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>other side.</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Icon</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H105" t="str">
-        <v>Brent Faiyaz</v>
+        <v>John Summit</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L105" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SHADOWS</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>SHADOWS - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G106" t="str">
-        <v>3:22</v>
+        <v>3:00</v>
       </c>
       <c r="H106" t="str">
-        <v>John Summit</v>
+        <v>CORTIS</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L106" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v>3:40</v>
       </c>
       <c r="H107" t="str">
-        <v>CORTIS</v>
+        <v>James Blake</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L107" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Let Me</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Trying Times</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:40</v>
+        <v>4:51</v>
       </c>
       <c r="H108" t="str">
-        <v>James Blake</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L108" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Let Me</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Let Me - Single</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>4:51</v>
+        <v>2:43</v>
       </c>
       <c r="H109" t="str">
-        <v>Victoria Monét</v>
+        <v>Perrie</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L109" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Woman In Love</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G110" t="str">
-        <v>2:43</v>
+        <v>4:03</v>
       </c>
       <c r="H110" t="str">
-        <v>Perrie</v>
+        <v>MUNA</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L110" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:03</v>
+        <v>3:18</v>
       </c>
       <c r="H111" t="str">
-        <v>MUNA</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L111" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:18</v>
+        <v>3:06</v>
       </c>
       <c r="H112" t="str">
-        <v>ATEEZ</v>
+        <v>Central Cee</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L112" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:06</v>
+        <v>3:59</v>
       </c>
       <c r="H113" t="str">
-        <v>Central Cee</v>
+        <v>Arcángel</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L113" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Mírame Baby</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:59</v>
+        <v>4:20</v>
       </c>
       <c r="H114" t="str">
-        <v>Arcángel</v>
+        <v>Fred again..</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L114" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Cerulean</v>
       </c>
       <c r="G115" t="str">
-        <v>4:20</v>
+        <v>3:52</v>
       </c>
       <c r="H115" t="str">
-        <v>Fred again..</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L115" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Two Hearts</v>
+        <v>Be By You</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Cerulean</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G116" t="str">
-        <v>3:52</v>
+        <v>3:17</v>
       </c>
       <c r="H116" t="str">
-        <v>Danny L Harle</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L116" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Be By You</v>
+        <v>you and forever</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Way I Am</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>3:54</v>
       </c>
       <c r="H117" t="str">
-        <v>Luke Combs</v>
+        <v>Bleachers</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L117" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>you and forever</v>
+        <v>ROOMS</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>everyone for ten minutes</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:54</v>
+        <v>3:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Bleachers</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L118" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ROOMS</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>ROOMS - Single</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:52</v>
+        <v>3:16</v>
       </c>
       <c r="H119" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L119" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G120" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H120" t="str">
-        <v>Bruno Mars</v>
+        <v>Junior H</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L120" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:11</v>
+        <v>3:09</v>
       </c>
       <c r="H121" t="str">
-        <v>Junior H</v>
+        <v>Maluma</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L121" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Con el Corazón</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G122" t="str">
-        <v>3:09</v>
+        <v>3:26</v>
       </c>
       <c r="H122" t="str">
-        <v>Maluma</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L122" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Get In Girl</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Toy With Me</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G123" t="str">
-        <v>3:26</v>
+        <v>3:21</v>
       </c>
       <c r="H123" t="str">
-        <v>Meghan Trainor</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L123" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>London Foolishly</v>
+        <v>Thorns</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H124" t="str">
-        <v>Nick Jonas</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L124" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thorns</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Thorns - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G125" t="str">
-        <v>3:10</v>
+        <v>4:10</v>
       </c>
       <c r="H125" t="str">
-        <v>Jelly Roll</v>
+        <v>Flea</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L125" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Thinkin Bout You</v>
+        <v>JUICY</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Honora</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:10</v>
+        <v>3:31</v>
       </c>
       <c r="H126" t="str">
-        <v>Flea</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L126" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>JUICY</v>
+        <v>All They Type</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>JUICY - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:31</v>
+        <v>2:52</v>
       </c>
       <c r="H127" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L127" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>All They Type</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>All They Type - Single</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:52</v>
+        <v>4:05</v>
       </c>
       <c r="H128" t="str">
-        <v>Keke Palmer</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L128" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>More Than A Lover</v>
+        <v>City</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>My Lover</v>
       </c>
       <c r="G129" t="str">
-        <v>4:05</v>
+        <v>3:16</v>
       </c>
       <c r="H129" t="str">
-        <v>Mary J. Blige</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L129" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>City</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>My Lover</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G130" t="str">
-        <v>3:16</v>
+        <v>2:25</v>
       </c>
       <c r="H130" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L130" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Eyes Closed</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:25</v>
+        <v>2:50</v>
       </c>
       <c r="H131" t="str">
-        <v>Mimi Webb</v>
+        <v>Knox</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L131" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Go For Broke</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Go For Broke - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>3:10</v>
       </c>
       <c r="H132" t="str">
-        <v>Knox</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L132" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:10</v>
+        <v>3:38</v>
       </c>
       <c r="H133" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L133" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Kentucky Too Long</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:38</v>
+        <v>2:57</v>
       </c>
       <c r="H134" t="str">
-        <v>Charley Crockett</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L134" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:57</v>
+        <v>2:58</v>
       </c>
       <c r="H135" t="str">
-        <v>Mon Rovîa</v>
+        <v>IVE</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L135" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>BANG BANG</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>BANG BANG - Single</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:58</v>
+        <v>3:15</v>
       </c>
       <c r="H136" t="str">
-        <v>IVE</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L136" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G137" t="str">
-        <v>3:15</v>
+        <v>5:21</v>
       </c>
       <c r="H137" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>Don Broco</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L137" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Nightmare Tripping</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Nightmare Tripping</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>5:21</v>
+        <v>3:26</v>
       </c>
       <c r="H138" t="str">
-        <v>Don Broco</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L138" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>for your love</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:26</v>
+        <v>3:05</v>
       </c>
       <c r="H139" t="str">
-        <v>Knocked Loose</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L139" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>for your love</v>
+        <v>Somebody</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>for your love - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:05</v>
+        <v>3:23</v>
       </c>
       <c r="H140" t="str">
-        <v>Cruz Beckham</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L140" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Somebody</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Somebody - Single</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:23</v>
+        <v>1:55</v>
       </c>
       <c r="H141" t="str">
-        <v>Jamie Foxx</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L141" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>On and On</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G142" t="str">
-        <v>1:55</v>
+        <v>3:43</v>
       </c>
       <c r="H142" t="str">
-        <v>BKTHERULA</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L142" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>On and On</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Work of Heart</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G143" t="str">
-        <v>3:43</v>
+        <v>2:44</v>
       </c>
       <c r="H143" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L143" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Push My Luck</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>2:44</v>
+        <v>2:46</v>
       </c>
       <c r="H144" t="str">
-        <v>Cold War Kids</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L144" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Memphis Players</v>
+        <v>Somebody</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G145" t="str">
-        <v>2:46</v>
+        <v>2:49</v>
       </c>
       <c r="H145" t="str">
-        <v>Anish Kumar</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L145" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Somebody</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:49</v>
+        <v>3:28</v>
       </c>
       <c r="H146" t="str">
-        <v>Good Neighbours</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L146" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L147" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Seven Seas</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Seven Seas - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G148" t="str">
-        <v>3:01</v>
+        <v>4:04</v>
       </c>
       <c r="H148" t="str">
-        <v>Dirty Heads</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L148" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>1000 Ways</v>
+        <v>Beatback</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>A Love For Strangers</v>
+        <v>Ö</v>
       </c>
       <c r="G149" t="str">
-        <v>4:04</v>
+        <v>2:19</v>
       </c>
       <c r="H149" t="str">
-        <v>Chet Faker</v>
+        <v>Fcukers</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L149" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Beatback</v>
+        <v>GANG</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ö</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:19</v>
+        <v>3:44</v>
       </c>
       <c r="H150" t="str">
-        <v>Fcukers</v>
+        <v>Tink</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L150" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>GANG</v>
+        <v>a love song for u</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>GANG - Single</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>3:44</v>
+        <v>1:40</v>
       </c>
       <c r="H151" t="str">
-        <v>Tink</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L151" t="str">
-        <v>GANG - Tink</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>a love song for u</v>
+        <v>See Through</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>a love song for u - EP</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G152" t="str">
-        <v>1:40</v>
+        <v>2:38</v>
       </c>
       <c r="H152" t="str">
-        <v>Eem Triplin</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L152" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>See Through</v>
+        <v>be the girl!</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G153" t="str">
-        <v>2:38</v>
+        <v>5:33</v>
       </c>
       <c r="H153" t="str">
-        <v>Story of the Year</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L153" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>be the girl!</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>the apple tree under the sea</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>5:33</v>
+        <v>3:33</v>
       </c>
       <c r="H154" t="str">
-        <v>hemlocke springs</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L154" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:33</v>
+        <v>3:40</v>
       </c>
       <c r="H155" t="str">
-        <v>Erin LeCount</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L155" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>ARCADE</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:40</v>
+        <v>2:52</v>
       </c>
       <c r="H156" t="str">
-        <v>Kid Sistr</v>
+        <v>Deb Never</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L156" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>ARCADE</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>ARCADE - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>2:52</v>
+        <v>2:16</v>
       </c>
       <c r="H157" t="str">
-        <v>Deb Never</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L157" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Girls Just Wanna</v>
+        <v>you special.</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Girlhood - EP</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:16</v>
+        <v>2:08</v>
       </c>
       <c r="H158" t="str">
-        <v>Morgan St. Jean</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L158" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>you special.</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>you special. - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:08</v>
+        <v>3:38</v>
       </c>
       <c r="H159" t="str">
-        <v>YFN Lucci</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L159" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Bass Dhol</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:38</v>
+        <v>3:31</v>
       </c>
       <c r="H160" t="str">
-        <v>Ahadadream</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L160" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:31</v>
+        <v>2:43</v>
       </c>
       <c r="H161" t="str">
-        <v>Charles Kelley</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L161" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>If I See Her Again</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G162" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Maddox Batson</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L162" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>To B Honest</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Under The Sun</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G163" t="str">
-        <v>4:43</v>
+        <v>4:30</v>
       </c>
       <c r="H163" t="str">
-        <v>Sun-El Musician</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L163" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>To B Honest</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>To Whom This May Concern</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G164" t="str">
-        <v>4:30</v>
+        <v>2:41</v>
       </c>
       <c r="H164" t="str">
-        <v>Jill Scott</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L164" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>lil xan goes to washington</v>
+        <v>Koneko</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>the beltway is burning</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:41</v>
+        <v>4:08</v>
       </c>
       <c r="H165" t="str">
-        <v>Ekko Astral</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L165" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Koneko</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Kurage - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:08</v>
+        <v>2:58</v>
       </c>
       <c r="H166" t="str">
-        <v>Liana Flores</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L166" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Cupid's Call</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:58</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>Dizzy Fae</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L167" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Pop Off</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:13</v>
+        <v>3:16</v>
       </c>
       <c r="H168" t="str">
-        <v>Chloé Caillet</v>
+        <v>GRiZ</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L168" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Pop Off</v>
+        <v>dreams</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Pop Off - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:16</v>
+        <v>3:31</v>
       </c>
       <c r="H169" t="str">
-        <v>GRiZ</v>
+        <v>Azzecca</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L169" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>dreams</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>dreams - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:31</v>
+        <v>2:55</v>
       </c>
       <c r="H170" t="str">
-        <v>Azzecca</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L170" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Love Hate Love</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:55</v>
+        <v>2:52</v>
       </c>
       <c r="H171" t="str">
-        <v>Owen Riegling</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L171" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Do It All Alone</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G172" t="str">
-        <v>2:52</v>
+        <v>2:58</v>
       </c>
       <c r="H172" t="str">
-        <v>Rend Collective</v>
+        <v>Cardinals</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L172" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>She Makes Me Real</v>
+        <v>Steady</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Masquerade</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:58</v>
+        <v>3:26</v>
       </c>
       <c r="H173" t="str">
-        <v>Cardinals</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L173" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Steady</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G174" t="str">
-        <v>3:26</v>
+        <v>2:20</v>
       </c>
       <c r="H174" t="str">
-        <v>Bella Kay</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L174" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>DIRTY TECH</v>
+        <v>Nada Más</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>PLAY ME</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:20</v>
+        <v>2:19</v>
       </c>
       <c r="H175" t="str">
-        <v>Kim Gordon</v>
+        <v>Tombochio</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L175" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Nada Más</v>
+        <v>Friends Again</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Nada Más - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:19</v>
+        <v>3:38</v>
       </c>
       <c r="H176" t="str">
-        <v>Tombochio</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L176" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Friends Again</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Friends Again - Single</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:38</v>
+        <v>3:22</v>
       </c>
       <c r="H177" t="str">
-        <v>Baby Rose</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L177" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>W.T.A.</v>
+        <v>desire.</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>W.T.A. - Single</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G178" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H178" t="str">
-        <v>Isaia Huron</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L178" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>desire.</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>November Scorpio</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G179" t="str">
-        <v>3:15</v>
+        <v>3:12</v>
       </c>
       <c r="H179" t="str">
-        <v>Tiana Major9</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L179" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:12</v>
+        <v>4:00</v>
       </c>
       <c r="H180" t="str">
-        <v>August Ponthier</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L180" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Killer Whale</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Killer Whale - Single</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G181" t="str">
-        <v>4:00</v>
+        <v>2:46</v>
       </c>
       <c r="H181" t="str">
-        <v>Hayden Everett</v>
+        <v>Anjimile</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L181" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Waits for Me</v>
+        <v>Man's World</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>You’re Free to Go</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G182" t="str">
-        <v>2:46</v>
+        <v>2:42</v>
       </c>
       <c r="H182" t="str">
-        <v>Anjimile</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L182" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Man's World</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Mud Blood Bone</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:42</v>
+        <v>3:13</v>
       </c>
       <c r="H183" t="str">
-        <v>Cat Clyde</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L183" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>In the Middle of It</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>3:13</v>
+        <v>2:51</v>
       </c>
       <c r="H184" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L184" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Fleeting - EP</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:51</v>
+        <v>5:23</v>
       </c>
       <c r="H185" t="str">
-        <v>Sarah Kinsley</v>
+        <v>BUNT.</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L185" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>5:23</v>
+        <v>3:07</v>
       </c>
       <c r="H186" t="str">
-        <v>BUNT.</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L186" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>I've Never Met Her</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>The Elephant</v>
       </c>
       <c r="G187" t="str">
-        <v>3:07</v>
+        <v>3:28</v>
       </c>
       <c r="H187" t="str">
-        <v>Ally Salort</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L187" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>Yes</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>The Elephant</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G188" t="str">
-        <v>3:28</v>
+        <v>3:21</v>
       </c>
       <c r="H188" t="str">
-        <v>Ledbyher</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L188" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Yes</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Just A Few Folk</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:21</v>
+        <v>2:52</v>
       </c>
       <c r="H189" t="str">
-        <v>JP Cooper</v>
+        <v>WesGhost</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L189" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G190" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H190" t="str">
-        <v>WesGhost</v>
+        <v>Converge</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L190" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Bad Faith</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Love Is Not Enough</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G191" t="str">
-        <v>2:48</v>
+        <v>4:00</v>
       </c>
       <c r="H191" t="str">
-        <v>Converge</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L191" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Angel Eyes</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-16</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Good God / Baad Man</v>
+        <v>God Forgives - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:00</v>
+        <v>2:14</v>
       </c>
       <c r="H192" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Guilt Trip</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
       </c>
       <c r="L192" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Angel Eyes - Guilt Trip</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Angel Eyes</v>
+        <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-16</v>
@@ -7709,68 +7709,30 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>God Forgives - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G193" t="str">
-        <v>2:14</v>
+        <v>3:17</v>
       </c>
       <c r="H193" t="str">
-        <v>Guilt Trip</v>
+        <v>Melvins</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
       <c r="L193" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>Tossing Coins Into The Fountain Of F**k</v>
-      </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
-      </c>
-      <c r="D194" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G194" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H194" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I194" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
-      </c>
-      <c r="L194" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>נטע ברזילי – סרנדה</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%a1%d7%a8%d7%a0%d7%93%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>“סרנדה” ששרה נטע ברזילי היא בלדה אמוציונלית שמצליחה לעשות מהלך עדין מאוד: להישמע כמו שיר אהבה,  אבל בפועל להיות שיר על חוסר אונים בתוך אהבה. שיר של שחיקה איטית שהופך דרמה נואשת. הפער הראשון בשיר הוא פער תקשורתי: "אני יכולה לספור</v>
       </c>
       <c r="G2" t="str">
-        <v>5:31</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>נטע ברזילי – סרנדה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-16</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:49</v>
+        <v>5:31</v>
       </c>
       <c r="H3" t="str">
-        <v>Mýa</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-16</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:03</v>
+        <v>2:49</v>
       </c>
       <c r="H4" t="str">
-        <v>Michael Bolton</v>
+        <v>Mýa</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-16</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:59</v>
+        <v>3:03</v>
       </c>
       <c r="H5" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-16</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H6" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-16</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H7" t="str">
-        <v>ENHYPEN</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-16</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H8" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>7:48</v>
+        <v>3:59</v>
       </c>
       <c r="H9" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-16</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:10</v>
+        <v>7:48</v>
       </c>
       <c r="H10" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-16</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>5:57</v>
+        <v>3:10</v>
       </c>
       <c r="H11" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-16</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:25</v>
+        <v>5:57</v>
       </c>
       <c r="H12" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-16</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:19</v>
+        <v>2:25</v>
       </c>
       <c r="H13" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-16</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:38</v>
+        <v>3:19</v>
       </c>
       <c r="H14" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-16</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:05</v>
+        <v>3:38</v>
       </c>
       <c r="H15" t="str">
-        <v>Dermot Kennedy</v>
+        <v>mgk</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-16</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>5:46</v>
+        <v>4:05</v>
       </c>
       <c r="H16" t="str">
-        <v>Jacob Collier</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-16</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:25</v>
+        <v>5:46</v>
       </c>
       <c r="H17" t="str">
-        <v>Victor Ray</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-16</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:11</v>
+        <v>3:25</v>
       </c>
       <c r="H18" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-16</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:55</v>
+        <v>5:11</v>
       </c>
       <c r="H19" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-16</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:54</v>
+        <v>2:55</v>
       </c>
       <c r="H20" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-16</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:01</v>
+        <v>4:54</v>
       </c>
       <c r="H21" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Offspring</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-16</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:55</v>
+        <v>5:01</v>
       </c>
       <c r="H22" t="str">
-        <v>HAUSER</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-16</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H23" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>HAUSER</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Jillian Jacquline - Another Lover (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H24" t="str">
-        <v>Ultra Records</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:30</v>
+        <v>2:53</v>
       </c>
       <c r="H25" t="str">
-        <v>Anja Kotar</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:37</v>
+        <v>3:30</v>
       </c>
       <c r="H26" t="str">
-        <v>Michael Bolton</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-16</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H27" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-16</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:06</v>
+        <v>4:10</v>
       </c>
       <c r="H28" t="str">
-        <v>Alan Walker</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-16</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:17</v>
+        <v>3:06</v>
       </c>
       <c r="H29" t="str">
-        <v>Bruno Mars</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-16</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H30" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-16</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>6:58</v>
+        <v>3:21</v>
       </c>
       <c r="H31" t="str">
-        <v>Eric Church</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-16</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:29</v>
+        <v>6:58</v>
       </c>
       <c r="H32" t="str">
-        <v>Meghan Trainor</v>
+        <v>Eric Church</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-16</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H33" t="str">
-        <v>Ally Salort</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-16</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:51</v>
+        <v>3:14</v>
       </c>
       <c r="H34" t="str">
-        <v>Will Swinton</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-16</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:10</v>
+        <v>3:51</v>
       </c>
       <c r="H35" t="str">
-        <v>elijah woods</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-16</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="H36" t="str">
-        <v>Jackson Dean</v>
+        <v>elijah woods</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-16</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H37" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-16</v>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H38" t="str">
-        <v>Neil Sedaka</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-16</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H39" t="str">
-        <v>Sofia Camara</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-16</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:04</v>
+        <v>3:06</v>
       </c>
       <c r="H40" t="str">
-        <v>Russell Dickerson</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-16</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H41" t="str">
-        <v>Celine Dion</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-16</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:38</v>
+        <v>3:03</v>
       </c>
       <c r="H42" t="str">
-        <v>Bebe Rexha</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-16</v>
@@ -2012,10 +2012,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:29</v>
+        <v>2:38</v>
       </c>
       <c r="H43" t="str">
-        <v>Caroline Jones</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-16</v>
@@ -2050,10 +2050,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:32</v>
+        <v>3:29</v>
       </c>
       <c r="H44" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-16</v>
@@ -2088,10 +2088,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>2:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Ingrid Andress</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-16</v>
@@ -2126,10 +2126,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:51</v>
+        <v>3:32</v>
       </c>
       <c r="H46" t="str">
-        <v>MusicByKnox</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B47" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-16</v>
@@ -2164,10 +2164,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H47" t="str">
-        <v>Ella Langley</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B48" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-16</v>
@@ -2202,10 +2202,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:26</v>
+        <v>3:38</v>
       </c>
       <c r="H48" t="str">
-        <v>Nickless</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B49" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-16</v>
@@ -2240,10 +2240,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:57</v>
+        <v>3:26</v>
       </c>
       <c r="H49" t="str">
-        <v>Caroline Jones</v>
+        <v>Nickless</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-16</v>
@@ -2278,10 +2278,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:08</v>
+        <v>3:57</v>
       </c>
       <c r="H50" t="str">
-        <v>elijah woods</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-16</v>
@@ -2316,10 +2316,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:53</v>
+        <v>3:08</v>
       </c>
       <c r="H51" t="str">
-        <v>August Ponthier</v>
+        <v>elijah woods</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B52" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-16</v>
@@ -2354,10 +2354,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:10</v>
+        <v>3:53</v>
       </c>
       <c r="H52" t="str">
-        <v>Charli xcx</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-16</v>
@@ -2392,10 +2392,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:58</v>
+        <v>3:10</v>
       </c>
       <c r="H53" t="str">
-        <v>Caroline Jones</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-16</v>
@@ -2430,10 +2430,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:44</v>
+        <v>2:58</v>
       </c>
       <c r="H54" t="str">
-        <v>Leah Kate</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-16</v>
@@ -2468,10 +2468,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:25</v>
+        <v>2:44</v>
       </c>
       <c r="H55" t="str">
-        <v>Troye Sivan</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-16</v>
@@ -2506,10 +2506,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:08</v>
+        <v>3:25</v>
       </c>
       <c r="H56" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-16</v>
@@ -2544,10 +2544,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:09</v>
+        <v>4:08</v>
       </c>
       <c r="H57" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B58" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-16</v>
@@ -2582,10 +2582,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:11</v>
+        <v>3:09</v>
       </c>
       <c r="H58" t="str">
-        <v>The Happy Fits</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-16</v>
@@ -2620,10 +2620,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:02</v>
+        <v>3:11</v>
       </c>
       <c r="H59" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B60" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-16</v>
@@ -2658,10 +2658,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:20</v>
+        <v>3:02</v>
       </c>
       <c r="H60" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B61" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-16</v>
@@ -2696,10 +2696,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:09</v>
+        <v>4:20</v>
       </c>
       <c r="H61" t="str">
-        <v>Quinn XCII</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B62" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-16</v>
@@ -2734,10 +2734,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:34</v>
+        <v>4:09</v>
       </c>
       <c r="H62" t="str">
-        <v>We Three</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B63" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-16</v>
@@ -2772,10 +2772,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:29</v>
+        <v>4:34</v>
       </c>
       <c r="H63" t="str">
-        <v>A Thousand Horses</v>
+        <v>We Three</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B64" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-16</v>
@@ -2810,10 +2810,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:51</v>
+        <v>3:29</v>
       </c>
       <c r="H64" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B65" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-16</v>
@@ -2848,10 +2848,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:56</v>
+        <v>2:51</v>
       </c>
       <c r="H65" t="str">
-        <v>Constant Smiles</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-16</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:25</v>
+        <v>2:56</v>
       </c>
       <c r="H66" t="str">
-        <v>P!NK</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B67" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-16</v>
@@ -2924,10 +2924,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:33</v>
+        <v>3:25</v>
       </c>
       <c r="H67" t="str">
-        <v>Bazzi</v>
+        <v>P!NK</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-16</v>
@@ -2962,10 +2962,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:18</v>
+        <v>2:33</v>
       </c>
       <c r="H68" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bazzi</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B69" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-16</v>
@@ -3000,7 +3000,7 @@
         <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:08</v>
+        <v>4:18</v>
       </c>
       <c r="H69" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B70" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-16</v>
@@ -3038,10 +3038,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:56</v>
+        <v>2:08</v>
       </c>
       <c r="H70" t="str">
-        <v>bleachers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-16</v>
@@ -3076,10 +3076,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:27</v>
+        <v>3:56</v>
       </c>
       <c r="H71" t="str">
-        <v>The Academic</v>
+        <v>bleachers</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-16</v>
@@ -3114,10 +3114,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:39</v>
+        <v>3:27</v>
       </c>
       <c r="H72" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Academic</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B73" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-16</v>
@@ -3152,10 +3152,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:54</v>
+        <v>2:39</v>
       </c>
       <c r="H73" t="str">
-        <v>Michael Bolton</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-16</v>
@@ -3190,10 +3190,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:47</v>
+        <v>3:54</v>
       </c>
       <c r="H74" t="str">
-        <v>Caroline Jones</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B75" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-16</v>
@@ -3228,10 +3228,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:07</v>
+        <v>3:47</v>
       </c>
       <c r="H75" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B76" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-16</v>
@@ -3266,10 +3266,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:00</v>
+        <v>4:07</v>
       </c>
       <c r="H76" t="str">
-        <v>Michael Bolton</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B77" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-16</v>
@@ -3304,10 +3304,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:27</v>
+        <v>5:00</v>
       </c>
       <c r="H77" t="str">
-        <v>Little Big Town</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B78" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-16</v>
@@ -3342,10 +3342,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H78" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-16</v>
@@ -3380,10 +3380,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>10:57</v>
+        <v>3:25</v>
       </c>
       <c r="H79" t="str">
-        <v>JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B80" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-16</v>
@@ -3418,10 +3418,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:14</v>
+        <v>10:57</v>
       </c>
       <c r="H80" t="str">
-        <v>Robert Grace</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B81" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-16</v>
@@ -3456,10 +3456,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:26</v>
+        <v>4:14</v>
       </c>
       <c r="H81" t="str">
-        <v>mgk</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-16</v>
@@ -3494,10 +3494,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:59</v>
+        <v>3:26</v>
       </c>
       <c r="H82" t="str">
-        <v>Victor Ray</v>
+        <v>mgk</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B83" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:46</v>
+        <v>5:59</v>
       </c>
       <c r="H83" t="str">
-        <v>Perrie</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-16</v>
@@ -3570,10 +3570,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:39</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Michael Bolton</v>
+        <v>Perrie</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B85" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-16</v>
@@ -3608,10 +3608,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:58</v>
+        <v>3:39</v>
       </c>
       <c r="H85" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B86" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:26</v>
+        <v>3:58</v>
       </c>
       <c r="H86" t="str">
-        <v>Mimi Webb</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-16</v>
@@ -3684,10 +3684,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:04</v>
+        <v>2:26</v>
       </c>
       <c r="H87" t="str">
-        <v>Olivia Dean</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B88" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-16</v>
@@ -3722,10 +3722,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>6:00</v>
+        <v>3:04</v>
       </c>
       <c r="H88" t="str">
-        <v>Taylor Swift</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-16</v>
@@ -3760,10 +3760,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:20</v>
+        <v>6:00</v>
       </c>
       <c r="H89" t="str">
-        <v>Michael Bolton</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-16</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:27</v>
+        <v>4:20</v>
       </c>
       <c r="H90" t="str">
-        <v>Mariah Carey</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B91" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-16</v>
@@ -3836,10 +3836,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:26</v>
+        <v>4:27</v>
       </c>
       <c r="H91" t="str">
-        <v>Netflix</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B92" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-16</v>
@@ -3874,10 +3874,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H92" t="str">
-        <v>Michael Bolton</v>
+        <v>Netflix</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-16</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H93" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-16</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:51</v>
+        <v>2:59</v>
       </c>
       <c r="H94" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>mgk</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B95" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-16</v>
@@ -3988,10 +3988,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:13</v>
+        <v>2:51</v>
       </c>
       <c r="H95" t="str">
-        <v>Michael Bolton</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B96" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-16</v>
@@ -4026,10 +4026,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:41</v>
+        <v>4:13</v>
       </c>
       <c r="H96" t="str">
-        <v>NICK JONAS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B97" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-16</v>
@@ -4064,10 +4064,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>7:03</v>
+        <v>4:41</v>
       </c>
       <c r="H97" t="str">
-        <v>Take That</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-16</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:37</v>
+        <v>7:03</v>
       </c>
       <c r="H98" t="str">
-        <v>Cliff Richard</v>
+        <v>Take That</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-16</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:54</v>
+        <v>4:37</v>
       </c>
       <c r="H99" t="str">
-        <v>Bryan Adams</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-16</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:06</v>
+        <v>3:54</v>
       </c>
       <c r="H100" t="str">
-        <v>Anna Graves</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-16</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H101" t="str">
-        <v>George Birge</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Always Everywhere</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Wuthering Heights</v>
+        <v>10 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H102" t="str">
-        <v>Charli xcx</v>
+        <v>George Birge</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Be Her</v>
+        <v>Always Everywhere</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Dandelion</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="G103" t="str">
-        <v>3:37</v>
+        <v>3:03</v>
       </c>
       <c r="H103" t="str">
-        <v>Ella Langley</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
       </c>
       <c r="L103" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>Always Everywhere - Charli xcx</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>other side.</v>
+        <v>Be Her</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Icon</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>3:15</v>
+        <v>3:37</v>
       </c>
       <c r="H104" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SHADOWS</v>
+        <v>other side.</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>SHADOWS - Single</v>
+        <v>Icon</v>
       </c>
       <c r="G105" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H105" t="str">
-        <v>John Summit</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L105" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:00</v>
+        <v>3:22</v>
       </c>
       <c r="H106" t="str">
-        <v>CORTIS</v>
+        <v>John Summit</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L106" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Trying Times</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G107" t="str">
-        <v>3:40</v>
+        <v>3:00</v>
       </c>
       <c r="H107" t="str">
-        <v>James Blake</v>
+        <v>CORTIS</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L107" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Let Me</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Let Me - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G108" t="str">
-        <v>4:51</v>
+        <v>3:40</v>
       </c>
       <c r="H108" t="str">
-        <v>Victoria Monét</v>
+        <v>James Blake</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L108" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H109" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L109" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H110" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L110" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G111" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H111" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L111" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H112" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L112" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H113" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L113" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H114" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L114" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H115" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L115" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G116" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H116" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L116" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G117" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L117" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G118" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H118" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L118" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H119" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L119" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H120" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L120" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G121" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H121" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L121" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H122" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L122" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G123" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H123" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L123" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G124" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H124" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L124" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H125" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L125" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G126" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H126" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L126" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H127" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L127" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H128" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L128" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L129" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G130" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H130" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L130" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G131" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H131" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L131" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L132" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G133" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H133" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L133" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H134" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L134" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H135" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L135" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H137" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L137" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G138" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H138" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L138" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H139" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L139" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H140" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L140" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H141" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L141" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H142" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L142" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G143" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H143" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L143" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H144" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L144" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G145" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H145" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L145" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G146" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H146" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L146" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H147" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L147" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L148" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G149" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H149" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L149" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G150" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H150" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L150" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H151" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L151" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H152" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L152" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G153" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H153" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L153" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G154" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H154" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L154" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H155" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L155" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H156" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L156" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H157" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L157" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H158" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L158" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H159" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L159" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H160" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L160" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H161" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L161" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L162" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G163" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L163" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G164" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H164" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L164" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G165" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H165" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L165" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H166" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L166" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H167" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L167" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L168" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H169" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L169" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H170" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L170" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H171" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L171" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H172" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L172" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G173" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H173" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L173" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H174" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L174" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G175" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H175" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L175" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H176" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L176" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H177" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L177" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L178" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G179" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H179" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L179" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G180" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H180" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L180" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H181" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L181" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G182" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H182" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L182" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G183" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H183" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L183" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H184" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L184" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H185" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L185" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H186" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L186" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H187" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L187" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G188" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H188" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L188" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G189" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H189" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L189" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H190" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L190" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G191" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H191" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L191" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-16</v>
@@ -7671,68 +7671,106 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G192" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H192" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L192" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B193" t="str">
+        <v/>
+      </c>
+      <c r="C193" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G193" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H193" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I193" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J193" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K193" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B193" t="str">
-        <v/>
-      </c>
-      <c r="C193" t="str">
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D193" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
+      <c r="D194" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G193" t="str">
+      <c r="G194" t="str">
         <v>3:17</v>
       </c>
-      <c r="H193" t="str">
+      <c r="H194" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I193" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J193" t="str">
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K193" t="str">
+      <c r="K194" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L193" t="str">
+      <c r="L194" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week03/titles.xlsx
+++ b/data/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נטע ברזילי – סרנדה</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-16</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%a1%d7%a8%d7%a0%d7%93%d7%94/</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“סרנדה” ששרה נטע ברזילי היא בלדה אמוציונלית שמצליחה לעשות מהלך עדין מאוד: להישמע כמו שיר אהבה,  אבל בפועל להיות שיר על חוסר אונים בתוך אהבה. שיר של שחיקה איטית שהופך דרמה נואשת. הפער הראשון בשיר הוא פער תקשורתי: "אני יכולה לספור</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>5:31</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נטע ברזילי – סרנדה</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-16</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>5:31</v>
+        <v>2:49</v>
       </c>
       <c r="H3" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Mýa</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-16</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:49</v>
+        <v>3:03</v>
       </c>
       <c r="H4" t="str">
-        <v>Mýa</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-16</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:03</v>
+        <v>2:59</v>
       </c>
       <c r="H5" t="str">
-        <v>Michael Bolton</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-16</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H6" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-16</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H7" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-16</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:59</v>
+        <v>3:59</v>
       </c>
       <c r="H8" t="str">
-        <v>ENHYPEN</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:59</v>
+        <v>7:48</v>
       </c>
       <c r="H9" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-16</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>7:48</v>
+        <v>3:10</v>
       </c>
       <c r="H10" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-16</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:10</v>
+        <v>5:57</v>
       </c>
       <c r="H11" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-16</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:57</v>
+        <v>2:25</v>
       </c>
       <c r="H12" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-16</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:25</v>
+        <v>3:19</v>
       </c>
       <c r="H13" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-16</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:19</v>
+        <v>3:38</v>
       </c>
       <c r="H14" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-16</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:38</v>
+        <v>4:05</v>
       </c>
       <c r="H15" t="str">
-        <v>mgk</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-16</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:05</v>
+        <v>5:46</v>
       </c>
       <c r="H16" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-16</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>5:46</v>
+        <v>3:25</v>
       </c>
       <c r="H17" t="str">
-        <v>Jacob Collier</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-16</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:25</v>
+        <v>5:11</v>
       </c>
       <c r="H18" t="str">
-        <v>Victor Ray</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-16</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>5:11</v>
+        <v>2:55</v>
       </c>
       <c r="H19" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>The Warning</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-16</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:55</v>
+        <v>4:54</v>
       </c>
       <c r="H20" t="str">
-        <v>The Warning</v>
+        <v>The Offspring</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-16</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:54</v>
+        <v>5:01</v>
       </c>
       <c r="H21" t="str">
-        <v>The Offspring</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-16</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:01</v>
+        <v>3:55</v>
       </c>
       <c r="H22" t="str">
-        <v>Caitlyn Smith</v>
+        <v>HAUSER</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Jillian Jacquline - Another Lover (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-16</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:55</v>
+        <v>3:43</v>
       </c>
       <c r="H23" t="str">
-        <v>HAUSER</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H24" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:53</v>
+        <v>3:30</v>
       </c>
       <c r="H25" t="str">
-        <v>Ultra Records</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:30</v>
+        <v>3:37</v>
       </c>
       <c r="H26" t="str">
-        <v>Anja Kotar</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-16</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:37</v>
+        <v>4:10</v>
       </c>
       <c r="H27" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-16</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:10</v>
+        <v>3:06</v>
       </c>
       <c r="H28" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-16</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H29" t="str">
-        <v>Alan Walker</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-16</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H30" t="str">
-        <v>Bruno Mars</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-16</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:21</v>
+        <v>6:58</v>
       </c>
       <c r="H31" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Eric Church</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-16</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>6:58</v>
+        <v>3:29</v>
       </c>
       <c r="H32" t="str">
-        <v>Eric Church</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-16</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:29</v>
+        <v>3:14</v>
       </c>
       <c r="H33" t="str">
-        <v>Meghan Trainor</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-16</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:14</v>
+        <v>3:51</v>
       </c>
       <c r="H34" t="str">
-        <v>Ally Salort</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-16</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:51</v>
+        <v>3:10</v>
       </c>
       <c r="H35" t="str">
-        <v>Will Swinton</v>
+        <v>elijah woods</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-16</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:10</v>
+        <v>3:26</v>
       </c>
       <c r="H36" t="str">
-        <v>elijah woods</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-16</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H37" t="str">
-        <v>Jackson Dean</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-16</v>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H38" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-16</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H39" t="str">
-        <v>Neil Sedaka</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-16</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:06</v>
+        <v>3:04</v>
       </c>
       <c r="H40" t="str">
-        <v>Sofia Camara</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-16</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H41" t="str">
-        <v>Russell Dickerson</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-16</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:03</v>
+        <v>2:38</v>
       </c>
       <c r="H42" t="str">
-        <v>Celine Dion</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-16</v>
@@ -2012,10 +2012,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:38</v>
+        <v>3:29</v>
       </c>
       <c r="H43" t="str">
-        <v>Bebe Rexha</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-16</v>
@@ -2050,10 +2050,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:29</v>
+        <v>2:32</v>
       </c>
       <c r="H44" t="str">
-        <v>Caroline Jones</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-16</v>
@@ -2088,10 +2088,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:32</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-16</v>
@@ -2126,10 +2126,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:32</v>
+        <v>2:51</v>
       </c>
       <c r="H46" t="str">
-        <v>Ingrid Andress</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-16</v>
@@ -2164,10 +2164,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:51</v>
+        <v>3:38</v>
       </c>
       <c r="H47" t="str">
-        <v>MusicByKnox</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B48" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-16</v>
@@ -2202,10 +2202,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H48" t="str">
-        <v>Ella Langley</v>
+        <v>Nickless</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-16</v>
@@ -2240,10 +2240,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:26</v>
+        <v>3:57</v>
       </c>
       <c r="H49" t="str">
-        <v>Nickless</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-16</v>
@@ -2278,10 +2278,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:57</v>
+        <v>3:08</v>
       </c>
       <c r="H50" t="str">
-        <v>Caroline Jones</v>
+        <v>elijah woods</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-16</v>
@@ -2316,10 +2316,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:08</v>
+        <v>3:53</v>
       </c>
       <c r="H51" t="str">
-        <v>elijah woods</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-16</v>
@@ -2354,10 +2354,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:53</v>
+        <v>3:10</v>
       </c>
       <c r="H52" t="str">
-        <v>August Ponthier</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-16</v>
@@ -2392,10 +2392,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:10</v>
+        <v>2:58</v>
       </c>
       <c r="H53" t="str">
-        <v>Charli xcx</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-16</v>
@@ -2430,10 +2430,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:58</v>
+        <v>2:44</v>
       </c>
       <c r="H54" t="str">
-        <v>Caroline Jones</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-16</v>
@@ -2468,10 +2468,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:44</v>
+        <v>3:25</v>
       </c>
       <c r="H55" t="str">
-        <v>Leah Kate</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-16</v>
@@ -2506,10 +2506,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:25</v>
+        <v>4:08</v>
       </c>
       <c r="H56" t="str">
-        <v>Troye Sivan</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B57" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-16</v>
@@ -2544,10 +2544,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:08</v>
+        <v>3:09</v>
       </c>
       <c r="H57" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-16</v>
@@ -2582,10 +2582,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H58" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Happy F